--- a/スケジュール_365日.xlsx
+++ b/スケジュール_365日.xlsx
@@ -16,10 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy/m/d"/>
-    <numFmt numFmtId="165" formatCode="d"/>
-    <numFmt numFmtId="166" formatCode="m/d"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy/m/d"/>
+    <numFmt numFmtId="166" formatCode="d"/>
+    <numFmt numFmtId="167" formatCode="m/d"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -87,7 +88,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -109,44 +110,11 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -155,7 +123,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -168,7 +136,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -180,24 +148,13 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -220,7 +177,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00EFEFF4"/>
+          <fgColor rgb="00E4E7F0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -590,11 +547,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
     <col width="5" customWidth="1" min="7" max="7"/>
     <col width="2.6" customWidth="1" min="8" max="8"/>
     <col width="2.6" customWidth="1" min="9" max="9"/>
@@ -981,12 +938,12 @@
           <t>基準日(開始)→</t>
         </is>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="D2" s="4" t="n">
         <v>46113</v>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>← ここを変えると下の日付が動きます</t>
+          <t>←変更で日付が動きます</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
@@ -995,7 +952,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="15" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>No</t>
@@ -1031,4414 +988,4400 @@
           <t>区分</t>
         </is>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="8" t="str">
         <f>TEXT(H4,"yyyy/m")</f>
-        <v/>
-      </c>
-      <c r="I3" s="8">
+        <v>2026/4</v>
+      </c>
+      <c r="I3" s="8" t="str">
         <f>IF(DAY(I4)=1,TEXT(I4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="J3" s="8">
+      <c r="J3" s="8" t="str">
         <f>IF(DAY(J4)=1,TEXT(J4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="K3" s="8">
+      <c r="K3" s="8" t="str">
         <f>IF(DAY(K4)=1,TEXT(K4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="L3" s="8">
+      <c r="L3" s="8" t="str">
         <f>IF(DAY(L4)=1,TEXT(L4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="M3" s="8">
+      <c r="M3" s="8" t="str">
         <f>IF(DAY(M4)=1,TEXT(M4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="N3" s="8">
+      <c r="N3" s="8" t="str">
         <f>IF(DAY(N4)=1,TEXT(N4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="O3" s="8">
+      <c r="O3" s="8" t="str">
         <f>IF(DAY(O4)=1,TEXT(O4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="P3" s="8">
+      <c r="P3" s="8" t="str">
         <f>IF(DAY(P4)=1,TEXT(P4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="Q3" s="8">
+      <c r="Q3" s="8" t="str">
         <f>IF(DAY(Q4)=1,TEXT(Q4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="R3" s="8">
+      <c r="R3" s="8" t="str">
         <f>IF(DAY(R4)=1,TEXT(R4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="S3" s="8">
+      <c r="S3" s="8" t="str">
         <f>IF(DAY(S4)=1,TEXT(S4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="T3" s="8">
+      <c r="T3" s="8" t="str">
         <f>IF(DAY(T4)=1,TEXT(T4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="U3" s="8">
+      <c r="U3" s="8" t="str">
         <f>IF(DAY(U4)=1,TEXT(U4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="V3" s="8">
+      <c r="V3" s="8" t="str">
         <f>IF(DAY(V4)=1,TEXT(V4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="W3" s="8">
+      <c r="W3" s="8" t="str">
         <f>IF(DAY(W4)=1,TEXT(W4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="X3" s="8">
+      <c r="X3" s="8" t="str">
         <f>IF(DAY(X4)=1,TEXT(X4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="Y3" s="8">
+      <c r="Y3" s="8" t="str">
         <f>IF(DAY(Y4)=1,TEXT(Y4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="Z3" s="8">
+      <c r="Z3" s="8" t="str">
         <f>IF(DAY(Z4)=1,TEXT(Z4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="AA3" s="8">
+      <c r="AA3" s="8" t="str">
         <f>IF(DAY(AA4)=1,TEXT(AA4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="AB3" s="8">
+      <c r="AB3" s="8" t="str">
         <f>IF(DAY(AB4)=1,TEXT(AB4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="AC3" s="8">
+      <c r="AC3" s="8" t="str">
         <f>IF(DAY(AC4)=1,TEXT(AC4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="8">
+      <c r="AD3" s="8" t="str">
         <f>IF(DAY(AD4)=1,TEXT(AD4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="AE3" s="8">
+      <c r="AE3" s="8" t="str">
         <f>IF(DAY(AE4)=1,TEXT(AE4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="AF3" s="8">
+      <c r="AF3" s="8" t="str">
         <f>IF(DAY(AF4)=1,TEXT(AF4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="AG3" s="8">
+      <c r="AG3" s="8" t="str">
         <f>IF(DAY(AG4)=1,TEXT(AG4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="8">
+      <c r="AH3" s="8" t="str">
         <f>IF(DAY(AH4)=1,TEXT(AH4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="AI3" s="8">
+      <c r="AI3" s="8" t="str">
         <f>IF(DAY(AI4)=1,TEXT(AI4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="AJ3" s="8">
+      <c r="AJ3" s="8" t="str">
         <f>IF(DAY(AJ4)=1,TEXT(AJ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="AK3" s="8">
+      <c r="AK3" s="8" t="str">
         <f>IF(DAY(AK4)=1,TEXT(AK4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="AL3" s="8">
+      <c r="AL3" s="8" t="str">
         <f>IF(DAY(AL4)=1,TEXT(AL4,"m月"),"")</f>
-        <v/>
-      </c>
-      <c r="AM3" s="8">
+        <v>5月</v>
+      </c>
+      <c r="AM3" s="8" t="str">
         <f>IF(DAY(AM4)=1,TEXT(AM4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="AN3" s="8">
+      <c r="AN3" s="8" t="str">
         <f>IF(DAY(AN4)=1,TEXT(AN4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="AO3" s="8">
+      <c r="AO3" s="8" t="str">
         <f>IF(DAY(AO4)=1,TEXT(AO4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="AP3" s="8">
+      <c r="AP3" s="8" t="str">
         <f>IF(DAY(AP4)=1,TEXT(AP4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="AQ3" s="8">
+      <c r="AQ3" s="8" t="str">
         <f>IF(DAY(AQ4)=1,TEXT(AQ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="AR3" s="8">
+      <c r="AR3" s="8" t="str">
         <f>IF(DAY(AR4)=1,TEXT(AR4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="AS3" s="8">
+      <c r="AS3" s="8" t="str">
         <f>IF(DAY(AS4)=1,TEXT(AS4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="AT3" s="8">
+      <c r="AT3" s="8" t="str">
         <f>IF(DAY(AT4)=1,TEXT(AT4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="AU3" s="8">
+      <c r="AU3" s="8" t="str">
         <f>IF(DAY(AU4)=1,TEXT(AU4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="AV3" s="8">
+      <c r="AV3" s="8" t="str">
         <f>IF(DAY(AV4)=1,TEXT(AV4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="AW3" s="8">
+      <c r="AW3" s="8" t="str">
         <f>IF(DAY(AW4)=1,TEXT(AW4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="AX3" s="8">
+      <c r="AX3" s="8" t="str">
         <f>IF(DAY(AX4)=1,TEXT(AX4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="AY3" s="8">
+      <c r="AY3" s="8" t="str">
         <f>IF(DAY(AY4)=1,TEXT(AY4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="AZ3" s="8">
+      <c r="AZ3" s="8" t="str">
         <f>IF(DAY(AZ4)=1,TEXT(AZ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="BA3" s="8">
+      <c r="BA3" s="8" t="str">
         <f>IF(DAY(BA4)=1,TEXT(BA4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="BB3" s="8">
+      <c r="BB3" s="8" t="str">
         <f>IF(DAY(BB4)=1,TEXT(BB4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="BC3" s="8">
+      <c r="BC3" s="8" t="str">
         <f>IF(DAY(BC4)=1,TEXT(BC4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="BD3" s="8">
+      <c r="BD3" s="8" t="str">
         <f>IF(DAY(BD4)=1,TEXT(BD4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="BE3" s="8">
+      <c r="BE3" s="8" t="str">
         <f>IF(DAY(BE4)=1,TEXT(BE4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="BF3" s="8">
+      <c r="BF3" s="8" t="str">
         <f>IF(DAY(BF4)=1,TEXT(BF4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="BG3" s="8">
+      <c r="BG3" s="8" t="str">
         <f>IF(DAY(BG4)=1,TEXT(BG4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="BH3" s="8">
+      <c r="BH3" s="8" t="str">
         <f>IF(DAY(BH4)=1,TEXT(BH4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="BI3" s="8">
+      <c r="BI3" s="8" t="str">
         <f>IF(DAY(BI4)=1,TEXT(BI4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="BJ3" s="8">
+      <c r="BJ3" s="8" t="str">
         <f>IF(DAY(BJ4)=1,TEXT(BJ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="BK3" s="8">
+      <c r="BK3" s="8" t="str">
         <f>IF(DAY(BK4)=1,TEXT(BK4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="BL3" s="8">
+      <c r="BL3" s="8" t="str">
         <f>IF(DAY(BL4)=1,TEXT(BL4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="BM3" s="8">
+      <c r="BM3" s="8" t="str">
         <f>IF(DAY(BM4)=1,TEXT(BM4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="BN3" s="8">
+      <c r="BN3" s="8" t="str">
         <f>IF(DAY(BN4)=1,TEXT(BN4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="BO3" s="8">
+      <c r="BO3" s="8" t="str">
         <f>IF(DAY(BO4)=1,TEXT(BO4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="BP3" s="8">
+      <c r="BP3" s="8" t="str">
         <f>IF(DAY(BP4)=1,TEXT(BP4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="BQ3" s="8">
+      <c r="BQ3" s="8" t="str">
         <f>IF(DAY(BQ4)=1,TEXT(BQ4,"m月"),"")</f>
-        <v/>
-      </c>
-      <c r="BR3" s="8">
+        <v>6月</v>
+      </c>
+      <c r="BR3" s="8" t="str">
         <f>IF(DAY(BR4)=1,TEXT(BR4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="BS3" s="8">
+      <c r="BS3" s="8" t="str">
         <f>IF(DAY(BS4)=1,TEXT(BS4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="BT3" s="8">
+      <c r="BT3" s="8" t="str">
         <f>IF(DAY(BT4)=1,TEXT(BT4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="BU3" s="8">
+      <c r="BU3" s="8" t="str">
         <f>IF(DAY(BU4)=1,TEXT(BU4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="BV3" s="8">
+      <c r="BV3" s="8" t="str">
         <f>IF(DAY(BV4)=1,TEXT(BV4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="BW3" s="8">
+      <c r="BW3" s="8" t="str">
         <f>IF(DAY(BW4)=1,TEXT(BW4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="BX3" s="8">
+      <c r="BX3" s="8" t="str">
         <f>IF(DAY(BX4)=1,TEXT(BX4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="BY3" s="8">
+      <c r="BY3" s="8" t="str">
         <f>IF(DAY(BY4)=1,TEXT(BY4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="BZ3" s="8">
+      <c r="BZ3" s="8" t="str">
         <f>IF(DAY(BZ4)=1,TEXT(BZ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="CA3" s="8">
+      <c r="CA3" s="8" t="str">
         <f>IF(DAY(CA4)=1,TEXT(CA4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="CB3" s="8">
+      <c r="CB3" s="8" t="str">
         <f>IF(DAY(CB4)=1,TEXT(CB4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="CC3" s="8">
+      <c r="CC3" s="8" t="str">
         <f>IF(DAY(CC4)=1,TEXT(CC4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="CD3" s="8">
+      <c r="CD3" s="8" t="str">
         <f>IF(DAY(CD4)=1,TEXT(CD4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="CE3" s="8">
+      <c r="CE3" s="8" t="str">
         <f>IF(DAY(CE4)=1,TEXT(CE4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="CF3" s="8">
+      <c r="CF3" s="8" t="str">
         <f>IF(DAY(CF4)=1,TEXT(CF4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="CG3" s="8">
+      <c r="CG3" s="8" t="str">
         <f>IF(DAY(CG4)=1,TEXT(CG4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="CH3" s="8">
+      <c r="CH3" s="8" t="str">
         <f>IF(DAY(CH4)=1,TEXT(CH4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="CI3" s="8">
+      <c r="CI3" s="8" t="str">
         <f>IF(DAY(CI4)=1,TEXT(CI4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="CJ3" s="8">
+      <c r="CJ3" s="8" t="str">
         <f>IF(DAY(CJ4)=1,TEXT(CJ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="CK3" s="8">
+      <c r="CK3" s="8" t="str">
         <f>IF(DAY(CK4)=1,TEXT(CK4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="CL3" s="8">
+      <c r="CL3" s="8" t="str">
         <f>IF(DAY(CL4)=1,TEXT(CL4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="CM3" s="8">
+      <c r="CM3" s="8" t="str">
         <f>IF(DAY(CM4)=1,TEXT(CM4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="CN3" s="8">
+      <c r="CN3" s="8" t="str">
         <f>IF(DAY(CN4)=1,TEXT(CN4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="CO3" s="8">
+      <c r="CO3" s="8" t="str">
         <f>IF(DAY(CO4)=1,TEXT(CO4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="CP3" s="8">
+      <c r="CP3" s="8" t="str">
         <f>IF(DAY(CP4)=1,TEXT(CP4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="CQ3" s="8">
+      <c r="CQ3" s="8" t="str">
         <f>IF(DAY(CQ4)=1,TEXT(CQ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="CR3" s="8">
+      <c r="CR3" s="8" t="str">
         <f>IF(DAY(CR4)=1,TEXT(CR4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="CS3" s="8">
+      <c r="CS3" s="8" t="str">
         <f>IF(DAY(CS4)=1,TEXT(CS4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="CT3" s="8">
+      <c r="CT3" s="8" t="str">
         <f>IF(DAY(CT4)=1,TEXT(CT4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="CU3" s="8">
+      <c r="CU3" s="8" t="str">
         <f>IF(DAY(CU4)=1,TEXT(CU4,"m月"),"")</f>
-        <v/>
-      </c>
-      <c r="CV3" s="8">
+        <v>7月</v>
+      </c>
+      <c r="CV3" s="8" t="str">
         <f>IF(DAY(CV4)=1,TEXT(CV4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="CW3" s="8">
+      <c r="CW3" s="8" t="str">
         <f>IF(DAY(CW4)=1,TEXT(CW4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="CX3" s="8">
+      <c r="CX3" s="8" t="str">
         <f>IF(DAY(CX4)=1,TEXT(CX4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="CY3" s="8">
+      <c r="CY3" s="8" t="str">
         <f>IF(DAY(CY4)=1,TEXT(CY4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="CZ3" s="8">
+      <c r="CZ3" s="8" t="str">
         <f>IF(DAY(CZ4)=1,TEXT(CZ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="DA3" s="8">
+      <c r="DA3" s="8" t="str">
         <f>IF(DAY(DA4)=1,TEXT(DA4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="DB3" s="8">
+      <c r="DB3" s="8" t="str">
         <f>IF(DAY(DB4)=1,TEXT(DB4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="DC3" s="8">
+      <c r="DC3" s="8" t="str">
         <f>IF(DAY(DC4)=1,TEXT(DC4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="DD3" s="8">
+      <c r="DD3" s="8" t="str">
         <f>IF(DAY(DD4)=1,TEXT(DD4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="DE3" s="8">
+      <c r="DE3" s="8" t="str">
         <f>IF(DAY(DE4)=1,TEXT(DE4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="DF3" s="8">
+      <c r="DF3" s="8" t="str">
         <f>IF(DAY(DF4)=1,TEXT(DF4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="DG3" s="8">
+      <c r="DG3" s="8" t="str">
         <f>IF(DAY(DG4)=1,TEXT(DG4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="DH3" s="8">
+      <c r="DH3" s="8" t="str">
         <f>IF(DAY(DH4)=1,TEXT(DH4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="DI3" s="8">
+      <c r="DI3" s="8" t="str">
         <f>IF(DAY(DI4)=1,TEXT(DI4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="DJ3" s="8">
+      <c r="DJ3" s="8" t="str">
         <f>IF(DAY(DJ4)=1,TEXT(DJ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="DK3" s="8">
+      <c r="DK3" s="8" t="str">
         <f>IF(DAY(DK4)=1,TEXT(DK4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="DL3" s="8">
+      <c r="DL3" s="8" t="str">
         <f>IF(DAY(DL4)=1,TEXT(DL4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="DM3" s="8">
+      <c r="DM3" s="8" t="str">
         <f>IF(DAY(DM4)=1,TEXT(DM4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="DN3" s="8">
+      <c r="DN3" s="8" t="str">
         <f>IF(DAY(DN4)=1,TEXT(DN4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="DO3" s="8">
+      <c r="DO3" s="8" t="str">
         <f>IF(DAY(DO4)=1,TEXT(DO4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="DP3" s="8">
+      <c r="DP3" s="8" t="str">
         <f>IF(DAY(DP4)=1,TEXT(DP4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="DQ3" s="8">
+      <c r="DQ3" s="8" t="str">
         <f>IF(DAY(DQ4)=1,TEXT(DQ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="DR3" s="8">
+      <c r="DR3" s="8" t="str">
         <f>IF(DAY(DR4)=1,TEXT(DR4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="DS3" s="8">
+      <c r="DS3" s="8" t="str">
         <f>IF(DAY(DS4)=1,TEXT(DS4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="DT3" s="8">
+      <c r="DT3" s="8" t="str">
         <f>IF(DAY(DT4)=1,TEXT(DT4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="DU3" s="8">
+      <c r="DU3" s="8" t="str">
         <f>IF(DAY(DU4)=1,TEXT(DU4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="DV3" s="8">
+      <c r="DV3" s="8" t="str">
         <f>IF(DAY(DV4)=1,TEXT(DV4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="DW3" s="8">
+      <c r="DW3" s="8" t="str">
         <f>IF(DAY(DW4)=1,TEXT(DW4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="DX3" s="8">
+      <c r="DX3" s="8" t="str">
         <f>IF(DAY(DX4)=1,TEXT(DX4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="DY3" s="8">
+      <c r="DY3" s="8" t="str">
         <f>IF(DAY(DY4)=1,TEXT(DY4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="DZ3" s="8">
+      <c r="DZ3" s="8" t="str">
         <f>IF(DAY(DZ4)=1,TEXT(DZ4,"m月"),"")</f>
-        <v/>
-      </c>
-      <c r="EA3" s="8">
+        <v>8月</v>
+      </c>
+      <c r="EA3" s="8" t="str">
         <f>IF(DAY(EA4)=1,TEXT(EA4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="EB3" s="8">
+      <c r="EB3" s="8" t="str">
         <f>IF(DAY(EB4)=1,TEXT(EB4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="EC3" s="8">
+      <c r="EC3" s="8" t="str">
         <f>IF(DAY(EC4)=1,TEXT(EC4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="ED3" s="8">
+      <c r="ED3" s="8" t="str">
         <f>IF(DAY(ED4)=1,TEXT(ED4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="EE3" s="8">
+      <c r="EE3" s="8" t="str">
         <f>IF(DAY(EE4)=1,TEXT(EE4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="EF3" s="8">
+      <c r="EF3" s="8" t="str">
         <f>IF(DAY(EF4)=1,TEXT(EF4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="EG3" s="8">
+      <c r="EG3" s="8" t="str">
         <f>IF(DAY(EG4)=1,TEXT(EG4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="EH3" s="8">
+      <c r="EH3" s="8" t="str">
         <f>IF(DAY(EH4)=1,TEXT(EH4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="EI3" s="8">
+      <c r="EI3" s="8" t="str">
         <f>IF(DAY(EI4)=1,TEXT(EI4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="EJ3" s="8">
+      <c r="EJ3" s="8" t="str">
         <f>IF(DAY(EJ4)=1,TEXT(EJ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="EK3" s="8">
+      <c r="EK3" s="8" t="str">
         <f>IF(DAY(EK4)=1,TEXT(EK4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="EL3" s="8">
+      <c r="EL3" s="8" t="str">
         <f>IF(DAY(EL4)=1,TEXT(EL4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="EM3" s="8">
+      <c r="EM3" s="8" t="str">
         <f>IF(DAY(EM4)=1,TEXT(EM4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="EN3" s="8">
+      <c r="EN3" s="8" t="str">
         <f>IF(DAY(EN4)=1,TEXT(EN4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="EO3" s="8">
+      <c r="EO3" s="8" t="str">
         <f>IF(DAY(EO4)=1,TEXT(EO4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="EP3" s="8">
+      <c r="EP3" s="8" t="str">
         <f>IF(DAY(EP4)=1,TEXT(EP4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="EQ3" s="8">
+      <c r="EQ3" s="8" t="str">
         <f>IF(DAY(EQ4)=1,TEXT(EQ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="ER3" s="8">
+      <c r="ER3" s="8" t="str">
         <f>IF(DAY(ER4)=1,TEXT(ER4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="ES3" s="8">
+      <c r="ES3" s="8" t="str">
         <f>IF(DAY(ES4)=1,TEXT(ES4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="ET3" s="8">
+      <c r="ET3" s="8" t="str">
         <f>IF(DAY(ET4)=1,TEXT(ET4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="EU3" s="8">
+      <c r="EU3" s="8" t="str">
         <f>IF(DAY(EU4)=1,TEXT(EU4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="EV3" s="8">
+      <c r="EV3" s="8" t="str">
         <f>IF(DAY(EV4)=1,TEXT(EV4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="EW3" s="8">
+      <c r="EW3" s="8" t="str">
         <f>IF(DAY(EW4)=1,TEXT(EW4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="EX3" s="8">
+      <c r="EX3" s="8" t="str">
         <f>IF(DAY(EX4)=1,TEXT(EX4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="EY3" s="8">
+      <c r="EY3" s="8" t="str">
         <f>IF(DAY(EY4)=1,TEXT(EY4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="EZ3" s="8">
+      <c r="EZ3" s="8" t="str">
         <f>IF(DAY(EZ4)=1,TEXT(EZ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="FA3" s="8">
+      <c r="FA3" s="8" t="str">
         <f>IF(DAY(FA4)=1,TEXT(FA4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="FB3" s="8">
+      <c r="FB3" s="8" t="str">
         <f>IF(DAY(FB4)=1,TEXT(FB4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="FC3" s="8">
+      <c r="FC3" s="8" t="str">
         <f>IF(DAY(FC4)=1,TEXT(FC4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="FD3" s="8">
+      <c r="FD3" s="8" t="str">
         <f>IF(DAY(FD4)=1,TEXT(FD4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="FE3" s="8">
+      <c r="FE3" s="8" t="str">
         <f>IF(DAY(FE4)=1,TEXT(FE4,"m月"),"")</f>
-        <v/>
-      </c>
-      <c r="FF3" s="8">
+        <v>9月</v>
+      </c>
+      <c r="FF3" s="8" t="str">
         <f>IF(DAY(FF4)=1,TEXT(FF4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="FG3" s="8">
+      <c r="FG3" s="8" t="str">
         <f>IF(DAY(FG4)=1,TEXT(FG4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="FH3" s="8">
+      <c r="FH3" s="8" t="str">
         <f>IF(DAY(FH4)=1,TEXT(FH4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="FI3" s="8">
+      <c r="FI3" s="8" t="str">
         <f>IF(DAY(FI4)=1,TEXT(FI4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="FJ3" s="8">
+      <c r="FJ3" s="8" t="str">
         <f>IF(DAY(FJ4)=1,TEXT(FJ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="FK3" s="8">
+      <c r="FK3" s="8" t="str">
         <f>IF(DAY(FK4)=1,TEXT(FK4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="FL3" s="8">
+      <c r="FL3" s="8" t="str">
         <f>IF(DAY(FL4)=1,TEXT(FL4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="FM3" s="8">
+      <c r="FM3" s="8" t="str">
         <f>IF(DAY(FM4)=1,TEXT(FM4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="FN3" s="8">
+      <c r="FN3" s="8" t="str">
         <f>IF(DAY(FN4)=1,TEXT(FN4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="FO3" s="8">
+      <c r="FO3" s="8" t="str">
         <f>IF(DAY(FO4)=1,TEXT(FO4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="FP3" s="8">
+      <c r="FP3" s="8" t="str">
         <f>IF(DAY(FP4)=1,TEXT(FP4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="FQ3" s="8">
+      <c r="FQ3" s="8" t="str">
         <f>IF(DAY(FQ4)=1,TEXT(FQ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="FR3" s="8">
+      <c r="FR3" s="8" t="str">
         <f>IF(DAY(FR4)=1,TEXT(FR4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="FS3" s="8">
+      <c r="FS3" s="8" t="str">
         <f>IF(DAY(FS4)=1,TEXT(FS4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="FT3" s="8">
+      <c r="FT3" s="8" t="str">
         <f>IF(DAY(FT4)=1,TEXT(FT4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="FU3" s="8">
+      <c r="FU3" s="8" t="str">
         <f>IF(DAY(FU4)=1,TEXT(FU4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="FV3" s="8">
+      <c r="FV3" s="8" t="str">
         <f>IF(DAY(FV4)=1,TEXT(FV4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="FW3" s="8">
+      <c r="FW3" s="8" t="str">
         <f>IF(DAY(FW4)=1,TEXT(FW4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="FX3" s="8">
+      <c r="FX3" s="8" t="str">
         <f>IF(DAY(FX4)=1,TEXT(FX4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="FY3" s="8">
+      <c r="FY3" s="8" t="str">
         <f>IF(DAY(FY4)=1,TEXT(FY4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="FZ3" s="8">
+      <c r="FZ3" s="8" t="str">
         <f>IF(DAY(FZ4)=1,TEXT(FZ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="GA3" s="8">
+      <c r="GA3" s="8" t="str">
         <f>IF(DAY(GA4)=1,TEXT(GA4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="GB3" s="8">
+      <c r="GB3" s="8" t="str">
         <f>IF(DAY(GB4)=1,TEXT(GB4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="GC3" s="8">
+      <c r="GC3" s="8" t="str">
         <f>IF(DAY(GC4)=1,TEXT(GC4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="GD3" s="8">
+      <c r="GD3" s="8" t="str">
         <f>IF(DAY(GD4)=1,TEXT(GD4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="GE3" s="8">
+      <c r="GE3" s="8" t="str">
         <f>IF(DAY(GE4)=1,TEXT(GE4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="GF3" s="8">
+      <c r="GF3" s="8" t="str">
         <f>IF(DAY(GF4)=1,TEXT(GF4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="GG3" s="8">
+      <c r="GG3" s="8" t="str">
         <f>IF(DAY(GG4)=1,TEXT(GG4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="GH3" s="8">
+      <c r="GH3" s="8" t="str">
         <f>IF(DAY(GH4)=1,TEXT(GH4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="GI3" s="8">
+      <c r="GI3" s="8" t="str">
         <f>IF(DAY(GI4)=1,TEXT(GI4,"m月"),"")</f>
-        <v/>
-      </c>
-      <c r="GJ3" s="8">
+        <v>10月</v>
+      </c>
+      <c r="GJ3" s="8" t="str">
         <f>IF(DAY(GJ4)=1,TEXT(GJ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="GK3" s="8">
+      <c r="GK3" s="8" t="str">
         <f>IF(DAY(GK4)=1,TEXT(GK4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="GL3" s="8">
+      <c r="GL3" s="8" t="str">
         <f>IF(DAY(GL4)=1,TEXT(GL4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="GM3" s="8">
+      <c r="GM3" s="8" t="str">
         <f>IF(DAY(GM4)=1,TEXT(GM4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="GN3" s="8">
+      <c r="GN3" s="8" t="str">
         <f>IF(DAY(GN4)=1,TEXT(GN4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="GO3" s="8">
+      <c r="GO3" s="8" t="str">
         <f>IF(DAY(GO4)=1,TEXT(GO4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="GP3" s="8">
+      <c r="GP3" s="8" t="str">
         <f>IF(DAY(GP4)=1,TEXT(GP4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="GQ3" s="8">
+      <c r="GQ3" s="8" t="str">
         <f>IF(DAY(GQ4)=1,TEXT(GQ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="GR3" s="8">
+      <c r="GR3" s="8" t="str">
         <f>IF(DAY(GR4)=1,TEXT(GR4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="GS3" s="8">
+      <c r="GS3" s="8" t="str">
         <f>IF(DAY(GS4)=1,TEXT(GS4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="GT3" s="8">
+      <c r="GT3" s="8" t="str">
         <f>IF(DAY(GT4)=1,TEXT(GT4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="GU3" s="8">
+      <c r="GU3" s="8" t="str">
         <f>IF(DAY(GU4)=1,TEXT(GU4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="GV3" s="8">
+      <c r="GV3" s="8" t="str">
         <f>IF(DAY(GV4)=1,TEXT(GV4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="GW3" s="8">
+      <c r="GW3" s="8" t="str">
         <f>IF(DAY(GW4)=1,TEXT(GW4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="GX3" s="8">
+      <c r="GX3" s="8" t="str">
         <f>IF(DAY(GX4)=1,TEXT(GX4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="GY3" s="8">
+      <c r="GY3" s="8" t="str">
         <f>IF(DAY(GY4)=1,TEXT(GY4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="GZ3" s="8">
+      <c r="GZ3" s="8" t="str">
         <f>IF(DAY(GZ4)=1,TEXT(GZ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="HA3" s="8">
+      <c r="HA3" s="8" t="str">
         <f>IF(DAY(HA4)=1,TEXT(HA4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="HB3" s="8">
+      <c r="HB3" s="8" t="str">
         <f>IF(DAY(HB4)=1,TEXT(HB4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="HC3" s="8">
+      <c r="HC3" s="8" t="str">
         <f>IF(DAY(HC4)=1,TEXT(HC4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="HD3" s="8">
+      <c r="HD3" s="8" t="str">
         <f>IF(DAY(HD4)=1,TEXT(HD4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="HE3" s="8">
+      <c r="HE3" s="8" t="str">
         <f>IF(DAY(HE4)=1,TEXT(HE4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="HF3" s="8">
+      <c r="HF3" s="8" t="str">
         <f>IF(DAY(HF4)=1,TEXT(HF4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="HG3" s="8">
+      <c r="HG3" s="8" t="str">
         <f>IF(DAY(HG4)=1,TEXT(HG4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="HH3" s="8">
+      <c r="HH3" s="8" t="str">
         <f>IF(DAY(HH4)=1,TEXT(HH4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="HI3" s="8">
+      <c r="HI3" s="8" t="str">
         <f>IF(DAY(HI4)=1,TEXT(HI4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="HJ3" s="8">
+      <c r="HJ3" s="8" t="str">
         <f>IF(DAY(HJ4)=1,TEXT(HJ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="HK3" s="8">
+      <c r="HK3" s="8" t="str">
         <f>IF(DAY(HK4)=1,TEXT(HK4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="HL3" s="8">
+      <c r="HL3" s="8" t="str">
         <f>IF(DAY(HL4)=1,TEXT(HL4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="HM3" s="8">
+      <c r="HM3" s="8" t="str">
         <f>IF(DAY(HM4)=1,TEXT(HM4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="HN3" s="8">
+      <c r="HN3" s="8" t="str">
         <f>IF(DAY(HN4)=1,TEXT(HN4,"m月"),"")</f>
-        <v/>
-      </c>
-      <c r="HO3" s="8">
+        <v>11月</v>
+      </c>
+      <c r="HO3" s="8" t="str">
         <f>IF(DAY(HO4)=1,TEXT(HO4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="HP3" s="8">
+      <c r="HP3" s="8" t="str">
         <f>IF(DAY(HP4)=1,TEXT(HP4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="HQ3" s="8">
+      <c r="HQ3" s="8" t="str">
         <f>IF(DAY(HQ4)=1,TEXT(HQ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="HR3" s="8">
+      <c r="HR3" s="8" t="str">
         <f>IF(DAY(HR4)=1,TEXT(HR4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="HS3" s="8">
+      <c r="HS3" s="8" t="str">
         <f>IF(DAY(HS4)=1,TEXT(HS4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="HT3" s="8">
+      <c r="HT3" s="8" t="str">
         <f>IF(DAY(HT4)=1,TEXT(HT4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="HU3" s="8">
+      <c r="HU3" s="8" t="str">
         <f>IF(DAY(HU4)=1,TEXT(HU4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="HV3" s="8">
+      <c r="HV3" s="8" t="str">
         <f>IF(DAY(HV4)=1,TEXT(HV4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="HW3" s="8">
+      <c r="HW3" s="8" t="str">
         <f>IF(DAY(HW4)=1,TEXT(HW4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="HX3" s="8">
+      <c r="HX3" s="8" t="str">
         <f>IF(DAY(HX4)=1,TEXT(HX4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="HY3" s="8">
+      <c r="HY3" s="8" t="str">
         <f>IF(DAY(HY4)=1,TEXT(HY4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="HZ3" s="8">
+      <c r="HZ3" s="8" t="str">
         <f>IF(DAY(HZ4)=1,TEXT(HZ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="IA3" s="8">
+      <c r="IA3" s="8" t="str">
         <f>IF(DAY(IA4)=1,TEXT(IA4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="IB3" s="8">
+      <c r="IB3" s="8" t="str">
         <f>IF(DAY(IB4)=1,TEXT(IB4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="IC3" s="8">
+      <c r="IC3" s="8" t="str">
         <f>IF(DAY(IC4)=1,TEXT(IC4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="ID3" s="8">
+      <c r="ID3" s="8" t="str">
         <f>IF(DAY(ID4)=1,TEXT(ID4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="IE3" s="8">
+      <c r="IE3" s="8" t="str">
         <f>IF(DAY(IE4)=1,TEXT(IE4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="IF3" s="8">
+      <c r="IF3" s="8" t="str">
         <f>IF(DAY(IF4)=1,TEXT(IF4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="IG3" s="8">
+      <c r="IG3" s="8" t="str">
         <f>IF(DAY(IG4)=1,TEXT(IG4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="IH3" s="8">
+      <c r="IH3" s="8" t="str">
         <f>IF(DAY(IH4)=1,TEXT(IH4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="II3" s="8">
+      <c r="II3" s="8" t="str">
         <f>IF(DAY(II4)=1,TEXT(II4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="IJ3" s="8">
+      <c r="IJ3" s="8" t="str">
         <f>IF(DAY(IJ4)=1,TEXT(IJ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="IK3" s="8">
+      <c r="IK3" s="8" t="str">
         <f>IF(DAY(IK4)=1,TEXT(IK4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="IL3" s="8">
+      <c r="IL3" s="8" t="str">
         <f>IF(DAY(IL4)=1,TEXT(IL4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="IM3" s="8">
+      <c r="IM3" s="8" t="str">
         <f>IF(DAY(IM4)=1,TEXT(IM4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="IN3" s="8">
+      <c r="IN3" s="8" t="str">
         <f>IF(DAY(IN4)=1,TEXT(IN4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="IO3" s="8">
+      <c r="IO3" s="8" t="str">
         <f>IF(DAY(IO4)=1,TEXT(IO4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="IP3" s="8">
+      <c r="IP3" s="8" t="str">
         <f>IF(DAY(IP4)=1,TEXT(IP4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="IQ3" s="8">
+      <c r="IQ3" s="8" t="str">
         <f>IF(DAY(IQ4)=1,TEXT(IQ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="IR3" s="8">
+      <c r="IR3" s="8" t="str">
         <f>IF(DAY(IR4)=1,TEXT(IR4,"m月"),"")</f>
-        <v/>
-      </c>
-      <c r="IS3" s="8">
+        <v>12月</v>
+      </c>
+      <c r="IS3" s="8" t="str">
         <f>IF(DAY(IS4)=1,TEXT(IS4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="IT3" s="8">
+      <c r="IT3" s="8" t="str">
         <f>IF(DAY(IT4)=1,TEXT(IT4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="IU3" s="8">
+      <c r="IU3" s="8" t="str">
         <f>IF(DAY(IU4)=1,TEXT(IU4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="IV3" s="8">
+      <c r="IV3" s="8" t="str">
         <f>IF(DAY(IV4)=1,TEXT(IV4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="IW3" s="8">
+      <c r="IW3" s="8" t="str">
         <f>IF(DAY(IW4)=1,TEXT(IW4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="IX3" s="8">
+      <c r="IX3" s="8" t="str">
         <f>IF(DAY(IX4)=1,TEXT(IX4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="IY3" s="8">
+      <c r="IY3" s="8" t="str">
         <f>IF(DAY(IY4)=1,TEXT(IY4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="IZ3" s="8">
+      <c r="IZ3" s="8" t="str">
         <f>IF(DAY(IZ4)=1,TEXT(IZ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="JA3" s="8">
+      <c r="JA3" s="8" t="str">
         <f>IF(DAY(JA4)=1,TEXT(JA4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="JB3" s="8">
+      <c r="JB3" s="8" t="str">
         <f>IF(DAY(JB4)=1,TEXT(JB4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="JC3" s="8">
+      <c r="JC3" s="8" t="str">
         <f>IF(DAY(JC4)=1,TEXT(JC4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="JD3" s="8">
+      <c r="JD3" s="8" t="str">
         <f>IF(DAY(JD4)=1,TEXT(JD4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="JE3" s="8">
+      <c r="JE3" s="8" t="str">
         <f>IF(DAY(JE4)=1,TEXT(JE4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="JF3" s="8">
+      <c r="JF3" s="8" t="str">
         <f>IF(DAY(JF4)=1,TEXT(JF4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="JG3" s="8">
+      <c r="JG3" s="8" t="str">
         <f>IF(DAY(JG4)=1,TEXT(JG4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="JH3" s="8">
+      <c r="JH3" s="8" t="str">
         <f>IF(DAY(JH4)=1,TEXT(JH4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="JI3" s="8">
+      <c r="JI3" s="8" t="str">
         <f>IF(DAY(JI4)=1,TEXT(JI4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="JJ3" s="8">
+      <c r="JJ3" s="8" t="str">
         <f>IF(DAY(JJ4)=1,TEXT(JJ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="JK3" s="8">
+      <c r="JK3" s="8" t="str">
         <f>IF(DAY(JK4)=1,TEXT(JK4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="JL3" s="8">
+      <c r="JL3" s="8" t="str">
         <f>IF(DAY(JL4)=1,TEXT(JL4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="JM3" s="8">
+      <c r="JM3" s="8" t="str">
         <f>IF(DAY(JM4)=1,TEXT(JM4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="JN3" s="8">
+      <c r="JN3" s="8" t="str">
         <f>IF(DAY(JN4)=1,TEXT(JN4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="JO3" s="8">
+      <c r="JO3" s="8" t="str">
         <f>IF(DAY(JO4)=1,TEXT(JO4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="JP3" s="8">
+      <c r="JP3" s="8" t="str">
         <f>IF(DAY(JP4)=1,TEXT(JP4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="JQ3" s="8">
+      <c r="JQ3" s="8" t="str">
         <f>IF(DAY(JQ4)=1,TEXT(JQ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="JR3" s="8">
+      <c r="JR3" s="8" t="str">
         <f>IF(DAY(JR4)=1,TEXT(JR4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="JS3" s="8">
+      <c r="JS3" s="8" t="str">
         <f>IF(DAY(JS4)=1,TEXT(JS4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="JT3" s="8">
+      <c r="JT3" s="8" t="str">
         <f>IF(DAY(JT4)=1,TEXT(JT4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="JU3" s="8">
+      <c r="JU3" s="8" t="str">
         <f>IF(DAY(JU4)=1,TEXT(JU4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="JV3" s="8">
+      <c r="JV3" s="8" t="str">
         <f>IF(DAY(JV4)=1,TEXT(JV4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="JW3" s="8">
+      <c r="JW3" s="8" t="str">
         <f>IF(DAY(JW4)=1,TEXT(JW4,"m月"),"")</f>
-        <v/>
-      </c>
-      <c r="JX3" s="8">
+        <v>1月</v>
+      </c>
+      <c r="JX3" s="8" t="str">
         <f>IF(DAY(JX4)=1,TEXT(JX4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="JY3" s="8">
+      <c r="JY3" s="8" t="str">
         <f>IF(DAY(JY4)=1,TEXT(JY4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="JZ3" s="8">
+      <c r="JZ3" s="8" t="str">
         <f>IF(DAY(JZ4)=1,TEXT(JZ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="KA3" s="8">
+      <c r="KA3" s="8" t="str">
         <f>IF(DAY(KA4)=1,TEXT(KA4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="KB3" s="8">
+      <c r="KB3" s="8" t="str">
         <f>IF(DAY(KB4)=1,TEXT(KB4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="KC3" s="8">
+      <c r="KC3" s="8" t="str">
         <f>IF(DAY(KC4)=1,TEXT(KC4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="KD3" s="8">
+      <c r="KD3" s="8" t="str">
         <f>IF(DAY(KD4)=1,TEXT(KD4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="KE3" s="8">
+      <c r="KE3" s="8" t="str">
         <f>IF(DAY(KE4)=1,TEXT(KE4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="KF3" s="8">
+      <c r="KF3" s="8" t="str">
         <f>IF(DAY(KF4)=1,TEXT(KF4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="KG3" s="8">
+      <c r="KG3" s="8" t="str">
         <f>IF(DAY(KG4)=1,TEXT(KG4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="KH3" s="8">
+      <c r="KH3" s="8" t="str">
         <f>IF(DAY(KH4)=1,TEXT(KH4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="KI3" s="8">
+      <c r="KI3" s="8" t="str">
         <f>IF(DAY(KI4)=1,TEXT(KI4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="KJ3" s="8">
+      <c r="KJ3" s="8" t="str">
         <f>IF(DAY(KJ4)=1,TEXT(KJ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="KK3" s="8">
+      <c r="KK3" s="8" t="str">
         <f>IF(DAY(KK4)=1,TEXT(KK4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="KL3" s="8">
+      <c r="KL3" s="8" t="str">
         <f>IF(DAY(KL4)=1,TEXT(KL4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="KM3" s="8">
+      <c r="KM3" s="8" t="str">
         <f>IF(DAY(KM4)=1,TEXT(KM4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="KN3" s="8">
+      <c r="KN3" s="8" t="str">
         <f>IF(DAY(KN4)=1,TEXT(KN4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="KO3" s="8">
+      <c r="KO3" s="8" t="str">
         <f>IF(DAY(KO4)=1,TEXT(KO4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="KP3" s="8">
+      <c r="KP3" s="8" t="str">
         <f>IF(DAY(KP4)=1,TEXT(KP4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="KQ3" s="8">
+      <c r="KQ3" s="8" t="str">
         <f>IF(DAY(KQ4)=1,TEXT(KQ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="KR3" s="8">
+      <c r="KR3" s="8" t="str">
         <f>IF(DAY(KR4)=1,TEXT(KR4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="KS3" s="8">
+      <c r="KS3" s="8" t="str">
         <f>IF(DAY(KS4)=1,TEXT(KS4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="KT3" s="8">
+      <c r="KT3" s="8" t="str">
         <f>IF(DAY(KT4)=1,TEXT(KT4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="KU3" s="8">
+      <c r="KU3" s="8" t="str">
         <f>IF(DAY(KU4)=1,TEXT(KU4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="KV3" s="8">
+      <c r="KV3" s="8" t="str">
         <f>IF(DAY(KV4)=1,TEXT(KV4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="KW3" s="8">
+      <c r="KW3" s="8" t="str">
         <f>IF(DAY(KW4)=1,TEXT(KW4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="KX3" s="8">
+      <c r="KX3" s="8" t="str">
         <f>IF(DAY(KX4)=1,TEXT(KX4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="KY3" s="8">
+      <c r="KY3" s="8" t="str">
         <f>IF(DAY(KY4)=1,TEXT(KY4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="KZ3" s="8">
+      <c r="KZ3" s="8" t="str">
         <f>IF(DAY(KZ4)=1,TEXT(KZ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="LA3" s="8">
+      <c r="LA3" s="8" t="str">
         <f>IF(DAY(LA4)=1,TEXT(LA4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="LB3" s="8">
+      <c r="LB3" s="8" t="str">
         <f>IF(DAY(LB4)=1,TEXT(LB4,"m月"),"")</f>
-        <v/>
-      </c>
-      <c r="LC3" s="8">
+        <v>2月</v>
+      </c>
+      <c r="LC3" s="8" t="str">
         <f>IF(DAY(LC4)=1,TEXT(LC4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="LD3" s="8">
+      <c r="LD3" s="8" t="str">
         <f>IF(DAY(LD4)=1,TEXT(LD4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="LE3" s="8">
+      <c r="LE3" s="8" t="str">
         <f>IF(DAY(LE4)=1,TEXT(LE4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="LF3" s="8">
+      <c r="LF3" s="8" t="str">
         <f>IF(DAY(LF4)=1,TEXT(LF4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="LG3" s="8">
+      <c r="LG3" s="8" t="str">
         <f>IF(DAY(LG4)=1,TEXT(LG4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="LH3" s="8">
+      <c r="LH3" s="8" t="str">
         <f>IF(DAY(LH4)=1,TEXT(LH4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="LI3" s="8">
+      <c r="LI3" s="8" t="str">
         <f>IF(DAY(LI4)=1,TEXT(LI4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="LJ3" s="8">
+      <c r="LJ3" s="8" t="str">
         <f>IF(DAY(LJ4)=1,TEXT(LJ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="LK3" s="8">
+      <c r="LK3" s="8" t="str">
         <f>IF(DAY(LK4)=1,TEXT(LK4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="LL3" s="8">
+      <c r="LL3" s="8" t="str">
         <f>IF(DAY(LL4)=1,TEXT(LL4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="LM3" s="8">
+      <c r="LM3" s="8" t="str">
         <f>IF(DAY(LM4)=1,TEXT(LM4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="LN3" s="8">
+      <c r="LN3" s="8" t="str">
         <f>IF(DAY(LN4)=1,TEXT(LN4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="LO3" s="8">
+      <c r="LO3" s="8" t="str">
         <f>IF(DAY(LO4)=1,TEXT(LO4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="LP3" s="8">
+      <c r="LP3" s="8" t="str">
         <f>IF(DAY(LP4)=1,TEXT(LP4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="LQ3" s="8">
+      <c r="LQ3" s="8" t="str">
         <f>IF(DAY(LQ4)=1,TEXT(LQ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="LR3" s="8">
+      <c r="LR3" s="8" t="str">
         <f>IF(DAY(LR4)=1,TEXT(LR4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="LS3" s="8">
+      <c r="LS3" s="8" t="str">
         <f>IF(DAY(LS4)=1,TEXT(LS4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="LT3" s="8">
+      <c r="LT3" s="8" t="str">
         <f>IF(DAY(LT4)=1,TEXT(LT4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="LU3" s="8">
+      <c r="LU3" s="8" t="str">
         <f>IF(DAY(LU4)=1,TEXT(LU4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="LV3" s="8">
+      <c r="LV3" s="8" t="str">
         <f>IF(DAY(LV4)=1,TEXT(LV4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="LW3" s="8">
+      <c r="LW3" s="8" t="str">
         <f>IF(DAY(LW4)=1,TEXT(LW4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="LX3" s="8">
+      <c r="LX3" s="8" t="str">
         <f>IF(DAY(LX4)=1,TEXT(LX4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="LY3" s="8">
+      <c r="LY3" s="8" t="str">
         <f>IF(DAY(LY4)=1,TEXT(LY4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="LZ3" s="8">
+      <c r="LZ3" s="8" t="str">
         <f>IF(DAY(LZ4)=1,TEXT(LZ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="MA3" s="8">
+      <c r="MA3" s="8" t="str">
         <f>IF(DAY(MA4)=1,TEXT(MA4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="MB3" s="8">
+      <c r="MB3" s="8" t="str">
         <f>IF(DAY(MB4)=1,TEXT(MB4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="MC3" s="8">
+      <c r="MC3" s="8" t="str">
         <f>IF(DAY(MC4)=1,TEXT(MC4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="MD3" s="8">
+      <c r="MD3" s="8" t="str">
         <f>IF(DAY(MD4)=1,TEXT(MD4,"m月"),"")</f>
-        <v/>
-      </c>
-      <c r="ME3" s="8">
+        <v>3月</v>
+      </c>
+      <c r="ME3" s="8" t="str">
         <f>IF(DAY(ME4)=1,TEXT(ME4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="MF3" s="8">
+      <c r="MF3" s="8" t="str">
         <f>IF(DAY(MF4)=1,TEXT(MF4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="MG3" s="8">
+      <c r="MG3" s="8" t="str">
         <f>IF(DAY(MG4)=1,TEXT(MG4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="MH3" s="8">
+      <c r="MH3" s="8" t="str">
         <f>IF(DAY(MH4)=1,TEXT(MH4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="MI3" s="8">
+      <c r="MI3" s="8" t="str">
         <f>IF(DAY(MI4)=1,TEXT(MI4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="MJ3" s="8">
+      <c r="MJ3" s="8" t="str">
         <f>IF(DAY(MJ4)=1,TEXT(MJ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="MK3" s="8">
+      <c r="MK3" s="8" t="str">
         <f>IF(DAY(MK4)=1,TEXT(MK4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="ML3" s="8">
+      <c r="ML3" s="8" t="str">
         <f>IF(DAY(ML4)=1,TEXT(ML4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="MM3" s="8">
+      <c r="MM3" s="8" t="str">
         <f>IF(DAY(MM4)=1,TEXT(MM4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="MN3" s="8">
+      <c r="MN3" s="8" t="str">
         <f>IF(DAY(MN4)=1,TEXT(MN4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="MO3" s="8">
+      <c r="MO3" s="8" t="str">
         <f>IF(DAY(MO4)=1,TEXT(MO4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="MP3" s="8">
+      <c r="MP3" s="8" t="str">
         <f>IF(DAY(MP4)=1,TEXT(MP4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="MQ3" s="8">
+      <c r="MQ3" s="8" t="str">
         <f>IF(DAY(MQ4)=1,TEXT(MQ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="MR3" s="8">
+      <c r="MR3" s="8" t="str">
         <f>IF(DAY(MR4)=1,TEXT(MR4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="MS3" s="8">
+      <c r="MS3" s="8" t="str">
         <f>IF(DAY(MS4)=1,TEXT(MS4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="MT3" s="8">
+      <c r="MT3" s="8" t="str">
         <f>IF(DAY(MT4)=1,TEXT(MT4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="MU3" s="8">
+      <c r="MU3" s="8" t="str">
         <f>IF(DAY(MU4)=1,TEXT(MU4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="MV3" s="8">
+      <c r="MV3" s="8" t="str">
         <f>IF(DAY(MV4)=1,TEXT(MV4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="MW3" s="8">
+      <c r="MW3" s="8" t="str">
         <f>IF(DAY(MW4)=1,TEXT(MW4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="MX3" s="8">
+      <c r="MX3" s="8" t="str">
         <f>IF(DAY(MX4)=1,TEXT(MX4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="MY3" s="8">
+      <c r="MY3" s="8" t="str">
         <f>IF(DAY(MY4)=1,TEXT(MY4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="MZ3" s="8">
+      <c r="MZ3" s="8" t="str">
         <f>IF(DAY(MZ4)=1,TEXT(MZ4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="NA3" s="8">
+      <c r="NA3" s="8" t="str">
         <f>IF(DAY(NA4)=1,TEXT(NA4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="NB3" s="8">
+      <c r="NB3" s="8" t="str">
         <f>IF(DAY(NB4)=1,TEXT(NB4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="NC3" s="8">
+      <c r="NC3" s="8" t="str">
         <f>IF(DAY(NC4)=1,TEXT(NC4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="ND3" s="8">
+      <c r="ND3" s="8" t="str">
         <f>IF(DAY(ND4)=1,TEXT(ND4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="NE3" s="8">
+      <c r="NE3" s="8" t="str">
         <f>IF(DAY(NE4)=1,TEXT(NE4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="NF3" s="8">
+      <c r="NF3" s="8" t="str">
         <f>IF(DAY(NF4)=1,TEXT(NF4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="NG3" s="8">
+      <c r="NG3" s="8" t="str">
         <f>IF(DAY(NG4)=1,TEXT(NG4,"m月"),"")</f>
         <v/>
       </c>
-      <c r="NH3" s="8">
+      <c r="NH3" s="8" t="str">
         <f>IF(DAY(NH4)=1,TEXT(NH4,"m月"),"")</f>
         <v/>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="17" t="n"/>
-      <c r="B4" s="17" t="n"/>
-      <c r="C4" s="17" t="n"/>
-      <c r="D4" s="17" t="n"/>
-      <c r="E4" s="17" t="n"/>
-      <c r="F4" s="17" t="n"/>
-      <c r="G4" s="17" t="n"/>
-      <c r="H4" s="18">
+    <row r="4" ht="15" customHeight="1">
+      <c r="H4" s="9">
         <f>$D$2</f>
-        <v/>
-      </c>
-      <c r="I4" s="18">
+        <v>46113.0</v>
+      </c>
+      <c r="I4" s="9">
         <f>H4+1</f>
-        <v/>
-      </c>
-      <c r="J4" s="18">
+        <v>46114.0</v>
+      </c>
+      <c r="J4" s="9">
         <f>I4+1</f>
-        <v/>
-      </c>
-      <c r="K4" s="18">
+        <v>46115.0</v>
+      </c>
+      <c r="K4" s="9">
         <f>J4+1</f>
-        <v/>
-      </c>
-      <c r="L4" s="18">
+        <v>46116.0</v>
+      </c>
+      <c r="L4" s="9">
         <f>K4+1</f>
-        <v/>
-      </c>
-      <c r="M4" s="18">
+        <v>46117.0</v>
+      </c>
+      <c r="M4" s="9">
         <f>L4+1</f>
-        <v/>
-      </c>
-      <c r="N4" s="18">
+        <v>46118.0</v>
+      </c>
+      <c r="N4" s="9">
         <f>M4+1</f>
-        <v/>
-      </c>
-      <c r="O4" s="18">
+        <v>46119.0</v>
+      </c>
+      <c r="O4" s="9">
         <f>N4+1</f>
-        <v/>
-      </c>
-      <c r="P4" s="18">
+        <v>46120.0</v>
+      </c>
+      <c r="P4" s="9">
         <f>O4+1</f>
-        <v/>
-      </c>
-      <c r="Q4" s="18">
+        <v>46121.0</v>
+      </c>
+      <c r="Q4" s="9">
         <f>P4+1</f>
-        <v/>
-      </c>
-      <c r="R4" s="18">
+        <v>46122.0</v>
+      </c>
+      <c r="R4" s="9">
         <f>Q4+1</f>
-        <v/>
-      </c>
-      <c r="S4" s="18">
+        <v>46123.0</v>
+      </c>
+      <c r="S4" s="9">
         <f>R4+1</f>
-        <v/>
-      </c>
-      <c r="T4" s="18">
+        <v>46124.0</v>
+      </c>
+      <c r="T4" s="9">
         <f>S4+1</f>
-        <v/>
-      </c>
-      <c r="U4" s="18">
+        <v>46125.0</v>
+      </c>
+      <c r="U4" s="9">
         <f>T4+1</f>
-        <v/>
-      </c>
-      <c r="V4" s="18">
+        <v>46126.0</v>
+      </c>
+      <c r="V4" s="9">
         <f>U4+1</f>
-        <v/>
-      </c>
-      <c r="W4" s="18">
+        <v>46127.0</v>
+      </c>
+      <c r="W4" s="9">
         <f>V4+1</f>
-        <v/>
-      </c>
-      <c r="X4" s="18">
+        <v>46128.0</v>
+      </c>
+      <c r="X4" s="9">
         <f>W4+1</f>
-        <v/>
-      </c>
-      <c r="Y4" s="18">
+        <v>46129.0</v>
+      </c>
+      <c r="Y4" s="9">
         <f>X4+1</f>
-        <v/>
-      </c>
-      <c r="Z4" s="18">
+        <v>46130.0</v>
+      </c>
+      <c r="Z4" s="9">
         <f>Y4+1</f>
-        <v/>
-      </c>
-      <c r="AA4" s="18">
+        <v>46131.0</v>
+      </c>
+      <c r="AA4" s="9">
         <f>Z4+1</f>
-        <v/>
-      </c>
-      <c r="AB4" s="18">
+        <v>46132.0</v>
+      </c>
+      <c r="AB4" s="9">
         <f>AA4+1</f>
-        <v/>
-      </c>
-      <c r="AC4" s="18">
+        <v>46133.0</v>
+      </c>
+      <c r="AC4" s="9">
         <f>AB4+1</f>
-        <v/>
-      </c>
-      <c r="AD4" s="18">
+        <v>46134.0</v>
+      </c>
+      <c r="AD4" s="9">
         <f>AC4+1</f>
-        <v/>
-      </c>
-      <c r="AE4" s="18">
+        <v>46135.0</v>
+      </c>
+      <c r="AE4" s="9">
         <f>AD4+1</f>
-        <v/>
-      </c>
-      <c r="AF4" s="18">
+        <v>46136.0</v>
+      </c>
+      <c r="AF4" s="9">
         <f>AE4+1</f>
-        <v/>
-      </c>
-      <c r="AG4" s="18">
+        <v>46137.0</v>
+      </c>
+      <c r="AG4" s="9">
         <f>AF4+1</f>
-        <v/>
-      </c>
-      <c r="AH4" s="18">
+        <v>46138.0</v>
+      </c>
+      <c r="AH4" s="9">
         <f>AG4+1</f>
-        <v/>
-      </c>
-      <c r="AI4" s="18">
+        <v>46139.0</v>
+      </c>
+      <c r="AI4" s="9">
         <f>AH4+1</f>
-        <v/>
-      </c>
-      <c r="AJ4" s="18">
+        <v>46140.0</v>
+      </c>
+      <c r="AJ4" s="9">
         <f>AI4+1</f>
-        <v/>
-      </c>
-      <c r="AK4" s="18">
+        <v>46141.0</v>
+      </c>
+      <c r="AK4" s="9">
         <f>AJ4+1</f>
-        <v/>
-      </c>
-      <c r="AL4" s="18">
+        <v>46142.0</v>
+      </c>
+      <c r="AL4" s="9">
         <f>AK4+1</f>
-        <v/>
-      </c>
-      <c r="AM4" s="18">
+        <v>46143.0</v>
+      </c>
+      <c r="AM4" s="9">
         <f>AL4+1</f>
-        <v/>
-      </c>
-      <c r="AN4" s="18">
+        <v>46144.0</v>
+      </c>
+      <c r="AN4" s="9">
         <f>AM4+1</f>
-        <v/>
-      </c>
-      <c r="AO4" s="18">
+        <v>46145.0</v>
+      </c>
+      <c r="AO4" s="9">
         <f>AN4+1</f>
-        <v/>
-      </c>
-      <c r="AP4" s="18">
+        <v>46146.0</v>
+      </c>
+      <c r="AP4" s="9">
         <f>AO4+1</f>
-        <v/>
-      </c>
-      <c r="AQ4" s="18">
+        <v>46147.0</v>
+      </c>
+      <c r="AQ4" s="9">
         <f>AP4+1</f>
-        <v/>
-      </c>
-      <c r="AR4" s="18">
+        <v>46148.0</v>
+      </c>
+      <c r="AR4" s="9">
         <f>AQ4+1</f>
-        <v/>
-      </c>
-      <c r="AS4" s="18">
+        <v>46149.0</v>
+      </c>
+      <c r="AS4" s="9">
         <f>AR4+1</f>
-        <v/>
-      </c>
-      <c r="AT4" s="18">
+        <v>46150.0</v>
+      </c>
+      <c r="AT4" s="9">
         <f>AS4+1</f>
-        <v/>
-      </c>
-      <c r="AU4" s="18">
+        <v>46151.0</v>
+      </c>
+      <c r="AU4" s="9">
         <f>AT4+1</f>
-        <v/>
-      </c>
-      <c r="AV4" s="18">
+        <v>46152.0</v>
+      </c>
+      <c r="AV4" s="9">
         <f>AU4+1</f>
-        <v/>
-      </c>
-      <c r="AW4" s="18">
+        <v>46153.0</v>
+      </c>
+      <c r="AW4" s="9">
         <f>AV4+1</f>
-        <v/>
-      </c>
-      <c r="AX4" s="18">
+        <v>46154.0</v>
+      </c>
+      <c r="AX4" s="9">
         <f>AW4+1</f>
-        <v/>
-      </c>
-      <c r="AY4" s="18">
+        <v>46155.0</v>
+      </c>
+      <c r="AY4" s="9">
         <f>AX4+1</f>
-        <v/>
-      </c>
-      <c r="AZ4" s="18">
+        <v>46156.0</v>
+      </c>
+      <c r="AZ4" s="9">
         <f>AY4+1</f>
-        <v/>
-      </c>
-      <c r="BA4" s="18">
+        <v>46157.0</v>
+      </c>
+      <c r="BA4" s="9">
         <f>AZ4+1</f>
-        <v/>
-      </c>
-      <c r="BB4" s="18">
+        <v>46158.0</v>
+      </c>
+      <c r="BB4" s="9">
         <f>BA4+1</f>
-        <v/>
-      </c>
-      <c r="BC4" s="18">
+        <v>46159.0</v>
+      </c>
+      <c r="BC4" s="9">
         <f>BB4+1</f>
-        <v/>
-      </c>
-      <c r="BD4" s="18">
+        <v>46160.0</v>
+      </c>
+      <c r="BD4" s="9">
         <f>BC4+1</f>
-        <v/>
-      </c>
-      <c r="BE4" s="18">
+        <v>46161.0</v>
+      </c>
+      <c r="BE4" s="9">
         <f>BD4+1</f>
-        <v/>
-      </c>
-      <c r="BF4" s="18">
+        <v>46162.0</v>
+      </c>
+      <c r="BF4" s="9">
         <f>BE4+1</f>
-        <v/>
-      </c>
-      <c r="BG4" s="18">
+        <v>46163.0</v>
+      </c>
+      <c r="BG4" s="9">
         <f>BF4+1</f>
-        <v/>
-      </c>
-      <c r="BH4" s="18">
+        <v>46164.0</v>
+      </c>
+      <c r="BH4" s="9">
         <f>BG4+1</f>
-        <v/>
-      </c>
-      <c r="BI4" s="18">
+        <v>46165.0</v>
+      </c>
+      <c r="BI4" s="9">
         <f>BH4+1</f>
-        <v/>
-      </c>
-      <c r="BJ4" s="18">
+        <v>46166.0</v>
+      </c>
+      <c r="BJ4" s="9">
         <f>BI4+1</f>
-        <v/>
-      </c>
-      <c r="BK4" s="18">
+        <v>46167.0</v>
+      </c>
+      <c r="BK4" s="9">
         <f>BJ4+1</f>
-        <v/>
-      </c>
-      <c r="BL4" s="18">
+        <v>46168.0</v>
+      </c>
+      <c r="BL4" s="9">
         <f>BK4+1</f>
-        <v/>
-      </c>
-      <c r="BM4" s="18">
+        <v>46169.0</v>
+      </c>
+      <c r="BM4" s="9">
         <f>BL4+1</f>
-        <v/>
-      </c>
-      <c r="BN4" s="18">
+        <v>46170.0</v>
+      </c>
+      <c r="BN4" s="9">
         <f>BM4+1</f>
-        <v/>
-      </c>
-      <c r="BO4" s="18">
+        <v>46171.0</v>
+      </c>
+      <c r="BO4" s="9">
         <f>BN4+1</f>
-        <v/>
-      </c>
-      <c r="BP4" s="18">
+        <v>46172.0</v>
+      </c>
+      <c r="BP4" s="9">
         <f>BO4+1</f>
-        <v/>
-      </c>
-      <c r="BQ4" s="18">
+        <v>46173.0</v>
+      </c>
+      <c r="BQ4" s="9">
         <f>BP4+1</f>
-        <v/>
-      </c>
-      <c r="BR4" s="18">
+        <v>46174.0</v>
+      </c>
+      <c r="BR4" s="9">
         <f>BQ4+1</f>
-        <v/>
-      </c>
-      <c r="BS4" s="18">
+        <v>46175.0</v>
+      </c>
+      <c r="BS4" s="9">
         <f>BR4+1</f>
-        <v/>
-      </c>
-      <c r="BT4" s="18">
+        <v>46176.0</v>
+      </c>
+      <c r="BT4" s="9">
         <f>BS4+1</f>
-        <v/>
-      </c>
-      <c r="BU4" s="18">
+        <v>46177.0</v>
+      </c>
+      <c r="BU4" s="9">
         <f>BT4+1</f>
-        <v/>
-      </c>
-      <c r="BV4" s="18">
+        <v>46178.0</v>
+      </c>
+      <c r="BV4" s="9">
         <f>BU4+1</f>
-        <v/>
-      </c>
-      <c r="BW4" s="18">
+        <v>46179.0</v>
+      </c>
+      <c r="BW4" s="9">
         <f>BV4+1</f>
-        <v/>
-      </c>
-      <c r="BX4" s="18">
+        <v>46180.0</v>
+      </c>
+      <c r="BX4" s="9">
         <f>BW4+1</f>
-        <v/>
-      </c>
-      <c r="BY4" s="18">
+        <v>46181.0</v>
+      </c>
+      <c r="BY4" s="9">
         <f>BX4+1</f>
-        <v/>
-      </c>
-      <c r="BZ4" s="18">
+        <v>46182.0</v>
+      </c>
+      <c r="BZ4" s="9">
         <f>BY4+1</f>
-        <v/>
-      </c>
-      <c r="CA4" s="18">
+        <v>46183.0</v>
+      </c>
+      <c r="CA4" s="9">
         <f>BZ4+1</f>
-        <v/>
-      </c>
-      <c r="CB4" s="18">
+        <v>46184.0</v>
+      </c>
+      <c r="CB4" s="9">
         <f>CA4+1</f>
-        <v/>
-      </c>
-      <c r="CC4" s="18">
+        <v>46185.0</v>
+      </c>
+      <c r="CC4" s="9">
         <f>CB4+1</f>
-        <v/>
-      </c>
-      <c r="CD4" s="18">
+        <v>46186.0</v>
+      </c>
+      <c r="CD4" s="9">
         <f>CC4+1</f>
-        <v/>
-      </c>
-      <c r="CE4" s="18">
+        <v>46187.0</v>
+      </c>
+      <c r="CE4" s="9">
         <f>CD4+1</f>
-        <v/>
-      </c>
-      <c r="CF4" s="18">
+        <v>46188.0</v>
+      </c>
+      <c r="CF4" s="9">
         <f>CE4+1</f>
-        <v/>
-      </c>
-      <c r="CG4" s="18">
+        <v>46189.0</v>
+      </c>
+      <c r="CG4" s="9">
         <f>CF4+1</f>
-        <v/>
-      </c>
-      <c r="CH4" s="18">
+        <v>46190.0</v>
+      </c>
+      <c r="CH4" s="9">
         <f>CG4+1</f>
-        <v/>
-      </c>
-      <c r="CI4" s="18">
+        <v>46191.0</v>
+      </c>
+      <c r="CI4" s="9">
         <f>CH4+1</f>
-        <v/>
-      </c>
-      <c r="CJ4" s="18">
+        <v>46192.0</v>
+      </c>
+      <c r="CJ4" s="9">
         <f>CI4+1</f>
-        <v/>
-      </c>
-      <c r="CK4" s="18">
+        <v>46193.0</v>
+      </c>
+      <c r="CK4" s="9">
         <f>CJ4+1</f>
-        <v/>
-      </c>
-      <c r="CL4" s="18">
+        <v>46194.0</v>
+      </c>
+      <c r="CL4" s="9">
         <f>CK4+1</f>
-        <v/>
-      </c>
-      <c r="CM4" s="18">
+        <v>46195.0</v>
+      </c>
+      <c r="CM4" s="9">
         <f>CL4+1</f>
-        <v/>
-      </c>
-      <c r="CN4" s="18">
+        <v>46196.0</v>
+      </c>
+      <c r="CN4" s="9">
         <f>CM4+1</f>
-        <v/>
-      </c>
-      <c r="CO4" s="18">
+        <v>46197.0</v>
+      </c>
+      <c r="CO4" s="9">
         <f>CN4+1</f>
-        <v/>
-      </c>
-      <c r="CP4" s="18">
+        <v>46198.0</v>
+      </c>
+      <c r="CP4" s="9">
         <f>CO4+1</f>
-        <v/>
-      </c>
-      <c r="CQ4" s="18">
+        <v>46199.0</v>
+      </c>
+      <c r="CQ4" s="9">
         <f>CP4+1</f>
-        <v/>
-      </c>
-      <c r="CR4" s="18">
+        <v>46200.0</v>
+      </c>
+      <c r="CR4" s="9">
         <f>CQ4+1</f>
-        <v/>
-      </c>
-      <c r="CS4" s="18">
+        <v>46201.0</v>
+      </c>
+      <c r="CS4" s="9">
         <f>CR4+1</f>
-        <v/>
-      </c>
-      <c r="CT4" s="18">
+        <v>46202.0</v>
+      </c>
+      <c r="CT4" s="9">
         <f>CS4+1</f>
-        <v/>
-      </c>
-      <c r="CU4" s="18">
+        <v>46203.0</v>
+      </c>
+      <c r="CU4" s="9">
         <f>CT4+1</f>
-        <v/>
-      </c>
-      <c r="CV4" s="18">
+        <v>46204.0</v>
+      </c>
+      <c r="CV4" s="9">
         <f>CU4+1</f>
-        <v/>
-      </c>
-      <c r="CW4" s="18">
+        <v>46205.0</v>
+      </c>
+      <c r="CW4" s="9">
         <f>CV4+1</f>
-        <v/>
-      </c>
-      <c r="CX4" s="18">
+        <v>46206.0</v>
+      </c>
+      <c r="CX4" s="9">
         <f>CW4+1</f>
-        <v/>
-      </c>
-      <c r="CY4" s="18">
+        <v>46207.0</v>
+      </c>
+      <c r="CY4" s="9">
         <f>CX4+1</f>
-        <v/>
-      </c>
-      <c r="CZ4" s="18">
+        <v>46208.0</v>
+      </c>
+      <c r="CZ4" s="9">
         <f>CY4+1</f>
-        <v/>
-      </c>
-      <c r="DA4" s="18">
+        <v>46209.0</v>
+      </c>
+      <c r="DA4" s="9">
         <f>CZ4+1</f>
-        <v/>
-      </c>
-      <c r="DB4" s="18">
+        <v>46210.0</v>
+      </c>
+      <c r="DB4" s="9">
         <f>DA4+1</f>
-        <v/>
-      </c>
-      <c r="DC4" s="18">
+        <v>46211.0</v>
+      </c>
+      <c r="DC4" s="9">
         <f>DB4+1</f>
-        <v/>
-      </c>
-      <c r="DD4" s="18">
+        <v>46212.0</v>
+      </c>
+      <c r="DD4" s="9">
         <f>DC4+1</f>
-        <v/>
-      </c>
-      <c r="DE4" s="18">
+        <v>46213.0</v>
+      </c>
+      <c r="DE4" s="9">
         <f>DD4+1</f>
-        <v/>
-      </c>
-      <c r="DF4" s="18">
+        <v>46214.0</v>
+      </c>
+      <c r="DF4" s="9">
         <f>DE4+1</f>
-        <v/>
-      </c>
-      <c r="DG4" s="18">
+        <v>46215.0</v>
+      </c>
+      <c r="DG4" s="9">
         <f>DF4+1</f>
-        <v/>
-      </c>
-      <c r="DH4" s="18">
+        <v>46216.0</v>
+      </c>
+      <c r="DH4" s="9">
         <f>DG4+1</f>
-        <v/>
-      </c>
-      <c r="DI4" s="18">
+        <v>46217.0</v>
+      </c>
+      <c r="DI4" s="9">
         <f>DH4+1</f>
-        <v/>
-      </c>
-      <c r="DJ4" s="18">
+        <v>46218.0</v>
+      </c>
+      <c r="DJ4" s="9">
         <f>DI4+1</f>
-        <v/>
-      </c>
-      <c r="DK4" s="18">
+        <v>46219.0</v>
+      </c>
+      <c r="DK4" s="9">
         <f>DJ4+1</f>
-        <v/>
-      </c>
-      <c r="DL4" s="18">
+        <v>46220.0</v>
+      </c>
+      <c r="DL4" s="9">
         <f>DK4+1</f>
-        <v/>
-      </c>
-      <c r="DM4" s="18">
+        <v>46221.0</v>
+      </c>
+      <c r="DM4" s="9">
         <f>DL4+1</f>
-        <v/>
-      </c>
-      <c r="DN4" s="18">
+        <v>46222.0</v>
+      </c>
+      <c r="DN4" s="9">
         <f>DM4+1</f>
-        <v/>
-      </c>
-      <c r="DO4" s="18">
+        <v>46223.0</v>
+      </c>
+      <c r="DO4" s="9">
         <f>DN4+1</f>
-        <v/>
-      </c>
-      <c r="DP4" s="18">
+        <v>46224.0</v>
+      </c>
+      <c r="DP4" s="9">
         <f>DO4+1</f>
-        <v/>
-      </c>
-      <c r="DQ4" s="18">
+        <v>46225.0</v>
+      </c>
+      <c r="DQ4" s="9">
         <f>DP4+1</f>
-        <v/>
-      </c>
-      <c r="DR4" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="DR4" s="9">
         <f>DQ4+1</f>
-        <v/>
-      </c>
-      <c r="DS4" s="18">
+        <v>46227.0</v>
+      </c>
+      <c r="DS4" s="9">
         <f>DR4+1</f>
-        <v/>
-      </c>
-      <c r="DT4" s="18">
+        <v>46228.0</v>
+      </c>
+      <c r="DT4" s="9">
         <f>DS4+1</f>
-        <v/>
-      </c>
-      <c r="DU4" s="18">
+        <v>46229.0</v>
+      </c>
+      <c r="DU4" s="9">
         <f>DT4+1</f>
-        <v/>
-      </c>
-      <c r="DV4" s="18">
+        <v>46230.0</v>
+      </c>
+      <c r="DV4" s="9">
         <f>DU4+1</f>
-        <v/>
-      </c>
-      <c r="DW4" s="18">
+        <v>46231.0</v>
+      </c>
+      <c r="DW4" s="9">
         <f>DV4+1</f>
-        <v/>
-      </c>
-      <c r="DX4" s="18">
+        <v>46232.0</v>
+      </c>
+      <c r="DX4" s="9">
         <f>DW4+1</f>
-        <v/>
-      </c>
-      <c r="DY4" s="18">
+        <v>46233.0</v>
+      </c>
+      <c r="DY4" s="9">
         <f>DX4+1</f>
-        <v/>
-      </c>
-      <c r="DZ4" s="18">
+        <v>46234.0</v>
+      </c>
+      <c r="DZ4" s="9">
         <f>DY4+1</f>
-        <v/>
-      </c>
-      <c r="EA4" s="18">
+        <v>46235.0</v>
+      </c>
+      <c r="EA4" s="9">
         <f>DZ4+1</f>
-        <v/>
-      </c>
-      <c r="EB4" s="18">
+        <v>46236.0</v>
+      </c>
+      <c r="EB4" s="9">
         <f>EA4+1</f>
-        <v/>
-      </c>
-      <c r="EC4" s="18">
+        <v>46237.0</v>
+      </c>
+      <c r="EC4" s="9">
         <f>EB4+1</f>
-        <v/>
-      </c>
-      <c r="ED4" s="18">
+        <v>46238.0</v>
+      </c>
+      <c r="ED4" s="9">
         <f>EC4+1</f>
-        <v/>
-      </c>
-      <c r="EE4" s="18">
+        <v>46239.0</v>
+      </c>
+      <c r="EE4" s="9">
         <f>ED4+1</f>
-        <v/>
-      </c>
-      <c r="EF4" s="18">
+        <v>46240.0</v>
+      </c>
+      <c r="EF4" s="9">
         <f>EE4+1</f>
-        <v/>
-      </c>
-      <c r="EG4" s="18">
+        <v>46241.0</v>
+      </c>
+      <c r="EG4" s="9">
         <f>EF4+1</f>
-        <v/>
-      </c>
-      <c r="EH4" s="18">
+        <v>46242.0</v>
+      </c>
+      <c r="EH4" s="9">
         <f>EG4+1</f>
-        <v/>
-      </c>
-      <c r="EI4" s="18">
+        <v>46243.0</v>
+      </c>
+      <c r="EI4" s="9">
         <f>EH4+1</f>
-        <v/>
-      </c>
-      <c r="EJ4" s="18">
+        <v>46244.0</v>
+      </c>
+      <c r="EJ4" s="9">
         <f>EI4+1</f>
-        <v/>
-      </c>
-      <c r="EK4" s="18">
+        <v>46245.0</v>
+      </c>
+      <c r="EK4" s="9">
         <f>EJ4+1</f>
-        <v/>
-      </c>
-      <c r="EL4" s="18">
+        <v>46246.0</v>
+      </c>
+      <c r="EL4" s="9">
         <f>EK4+1</f>
-        <v/>
-      </c>
-      <c r="EM4" s="18">
+        <v>46247.0</v>
+      </c>
+      <c r="EM4" s="9">
         <f>EL4+1</f>
-        <v/>
-      </c>
-      <c r="EN4" s="18">
+        <v>46248.0</v>
+      </c>
+      <c r="EN4" s="9">
         <f>EM4+1</f>
-        <v/>
-      </c>
-      <c r="EO4" s="18">
+        <v>46249.0</v>
+      </c>
+      <c r="EO4" s="9">
         <f>EN4+1</f>
-        <v/>
-      </c>
-      <c r="EP4" s="18">
+        <v>46250.0</v>
+      </c>
+      <c r="EP4" s="9">
         <f>EO4+1</f>
-        <v/>
-      </c>
-      <c r="EQ4" s="18">
+        <v>46251.0</v>
+      </c>
+      <c r="EQ4" s="9">
         <f>EP4+1</f>
-        <v/>
-      </c>
-      <c r="ER4" s="18">
+        <v>46252.0</v>
+      </c>
+      <c r="ER4" s="9">
         <f>EQ4+1</f>
-        <v/>
-      </c>
-      <c r="ES4" s="18">
+        <v>46253.0</v>
+      </c>
+      <c r="ES4" s="9">
         <f>ER4+1</f>
-        <v/>
-      </c>
-      <c r="ET4" s="18">
+        <v>46254.0</v>
+      </c>
+      <c r="ET4" s="9">
         <f>ES4+1</f>
-        <v/>
-      </c>
-      <c r="EU4" s="18">
+        <v>46255.0</v>
+      </c>
+      <c r="EU4" s="9">
         <f>ET4+1</f>
-        <v/>
-      </c>
-      <c r="EV4" s="18">
+        <v>46256.0</v>
+      </c>
+      <c r="EV4" s="9">
         <f>EU4+1</f>
-        <v/>
-      </c>
-      <c r="EW4" s="18">
+        <v>46257.0</v>
+      </c>
+      <c r="EW4" s="9">
         <f>EV4+1</f>
-        <v/>
-      </c>
-      <c r="EX4" s="18">
+        <v>46258.0</v>
+      </c>
+      <c r="EX4" s="9">
         <f>EW4+1</f>
-        <v/>
-      </c>
-      <c r="EY4" s="18">
+        <v>46259.0</v>
+      </c>
+      <c r="EY4" s="9">
         <f>EX4+1</f>
-        <v/>
-      </c>
-      <c r="EZ4" s="18">
+        <v>46260.0</v>
+      </c>
+      <c r="EZ4" s="9">
         <f>EY4+1</f>
-        <v/>
-      </c>
-      <c r="FA4" s="18">
+        <v>46261.0</v>
+      </c>
+      <c r="FA4" s="9">
         <f>EZ4+1</f>
-        <v/>
-      </c>
-      <c r="FB4" s="18">
+        <v>46262.0</v>
+      </c>
+      <c r="FB4" s="9">
         <f>FA4+1</f>
-        <v/>
-      </c>
-      <c r="FC4" s="18">
+        <v>46263.0</v>
+      </c>
+      <c r="FC4" s="9">
         <f>FB4+1</f>
-        <v/>
-      </c>
-      <c r="FD4" s="18">
+        <v>46264.0</v>
+      </c>
+      <c r="FD4" s="9">
         <f>FC4+1</f>
-        <v/>
-      </c>
-      <c r="FE4" s="18">
+        <v>46265.0</v>
+      </c>
+      <c r="FE4" s="9">
         <f>FD4+1</f>
-        <v/>
-      </c>
-      <c r="FF4" s="18">
+        <v>46266.0</v>
+      </c>
+      <c r="FF4" s="9">
         <f>FE4+1</f>
-        <v/>
-      </c>
-      <c r="FG4" s="18">
+        <v>46267.0</v>
+      </c>
+      <c r="FG4" s="9">
         <f>FF4+1</f>
-        <v/>
-      </c>
-      <c r="FH4" s="18">
+        <v>46268.0</v>
+      </c>
+      <c r="FH4" s="9">
         <f>FG4+1</f>
-        <v/>
-      </c>
-      <c r="FI4" s="18">
+        <v>46269.0</v>
+      </c>
+      <c r="FI4" s="9">
         <f>FH4+1</f>
-        <v/>
-      </c>
-      <c r="FJ4" s="18">
+        <v>46270.0</v>
+      </c>
+      <c r="FJ4" s="9">
         <f>FI4+1</f>
-        <v/>
-      </c>
-      <c r="FK4" s="18">
+        <v>46271.0</v>
+      </c>
+      <c r="FK4" s="9">
         <f>FJ4+1</f>
-        <v/>
-      </c>
-      <c r="FL4" s="18">
+        <v>46272.0</v>
+      </c>
+      <c r="FL4" s="9">
         <f>FK4+1</f>
-        <v/>
-      </c>
-      <c r="FM4" s="18">
+        <v>46273.0</v>
+      </c>
+      <c r="FM4" s="9">
         <f>FL4+1</f>
-        <v/>
-      </c>
-      <c r="FN4" s="18">
+        <v>46274.0</v>
+      </c>
+      <c r="FN4" s="9">
         <f>FM4+1</f>
-        <v/>
-      </c>
-      <c r="FO4" s="18">
+        <v>46275.0</v>
+      </c>
+      <c r="FO4" s="9">
         <f>FN4+1</f>
-        <v/>
-      </c>
-      <c r="FP4" s="18">
+        <v>46276.0</v>
+      </c>
+      <c r="FP4" s="9">
         <f>FO4+1</f>
-        <v/>
-      </c>
-      <c r="FQ4" s="18">
+        <v>46277.0</v>
+      </c>
+      <c r="FQ4" s="9">
         <f>FP4+1</f>
-        <v/>
-      </c>
-      <c r="FR4" s="18">
+        <v>46278.0</v>
+      </c>
+      <c r="FR4" s="9">
         <f>FQ4+1</f>
-        <v/>
-      </c>
-      <c r="FS4" s="18">
+        <v>46279.0</v>
+      </c>
+      <c r="FS4" s="9">
         <f>FR4+1</f>
-        <v/>
-      </c>
-      <c r="FT4" s="18">
+        <v>46280.0</v>
+      </c>
+      <c r="FT4" s="9">
         <f>FS4+1</f>
-        <v/>
-      </c>
-      <c r="FU4" s="18">
+        <v>46281.0</v>
+      </c>
+      <c r="FU4" s="9">
         <f>FT4+1</f>
-        <v/>
-      </c>
-      <c r="FV4" s="18">
+        <v>46282.0</v>
+      </c>
+      <c r="FV4" s="9">
         <f>FU4+1</f>
-        <v/>
-      </c>
-      <c r="FW4" s="18">
+        <v>46283.0</v>
+      </c>
+      <c r="FW4" s="9">
         <f>FV4+1</f>
-        <v/>
-      </c>
-      <c r="FX4" s="18">
+        <v>46284.0</v>
+      </c>
+      <c r="FX4" s="9">
         <f>FW4+1</f>
-        <v/>
-      </c>
-      <c r="FY4" s="18">
+        <v>46285.0</v>
+      </c>
+      <c r="FY4" s="9">
         <f>FX4+1</f>
-        <v/>
-      </c>
-      <c r="FZ4" s="18">
+        <v>46286.0</v>
+      </c>
+      <c r="FZ4" s="9">
         <f>FY4+1</f>
-        <v/>
-      </c>
-      <c r="GA4" s="18">
+        <v>46287.0</v>
+      </c>
+      <c r="GA4" s="9">
         <f>FZ4+1</f>
-        <v/>
-      </c>
-      <c r="GB4" s="18">
+        <v>46288.0</v>
+      </c>
+      <c r="GB4" s="9">
         <f>GA4+1</f>
-        <v/>
-      </c>
-      <c r="GC4" s="18">
+        <v>46289.0</v>
+      </c>
+      <c r="GC4" s="9">
         <f>GB4+1</f>
-        <v/>
-      </c>
-      <c r="GD4" s="18">
+        <v>46290.0</v>
+      </c>
+      <c r="GD4" s="9">
         <f>GC4+1</f>
-        <v/>
-      </c>
-      <c r="GE4" s="18">
+        <v>46291.0</v>
+      </c>
+      <c r="GE4" s="9">
         <f>GD4+1</f>
-        <v/>
-      </c>
-      <c r="GF4" s="18">
+        <v>46292.0</v>
+      </c>
+      <c r="GF4" s="9">
         <f>GE4+1</f>
-        <v/>
-      </c>
-      <c r="GG4" s="18">
+        <v>46293.0</v>
+      </c>
+      <c r="GG4" s="9">
         <f>GF4+1</f>
-        <v/>
-      </c>
-      <c r="GH4" s="18">
+        <v>46294.0</v>
+      </c>
+      <c r="GH4" s="9">
         <f>GG4+1</f>
-        <v/>
-      </c>
-      <c r="GI4" s="18">
+        <v>46295.0</v>
+      </c>
+      <c r="GI4" s="9">
         <f>GH4+1</f>
-        <v/>
-      </c>
-      <c r="GJ4" s="18">
+        <v>46296.0</v>
+      </c>
+      <c r="GJ4" s="9">
         <f>GI4+1</f>
-        <v/>
-      </c>
-      <c r="GK4" s="18">
+        <v>46297.0</v>
+      </c>
+      <c r="GK4" s="9">
         <f>GJ4+1</f>
-        <v/>
-      </c>
-      <c r="GL4" s="18">
+        <v>46298.0</v>
+      </c>
+      <c r="GL4" s="9">
         <f>GK4+1</f>
-        <v/>
-      </c>
-      <c r="GM4" s="18">
+        <v>46299.0</v>
+      </c>
+      <c r="GM4" s="9">
         <f>GL4+1</f>
-        <v/>
-      </c>
-      <c r="GN4" s="18">
+        <v>46300.0</v>
+      </c>
+      <c r="GN4" s="9">
         <f>GM4+1</f>
-        <v/>
-      </c>
-      <c r="GO4" s="18">
+        <v>46301.0</v>
+      </c>
+      <c r="GO4" s="9">
         <f>GN4+1</f>
-        <v/>
-      </c>
-      <c r="GP4" s="18">
+        <v>46302.0</v>
+      </c>
+      <c r="GP4" s="9">
         <f>GO4+1</f>
-        <v/>
-      </c>
-      <c r="GQ4" s="18">
+        <v>46303.0</v>
+      </c>
+      <c r="GQ4" s="9">
         <f>GP4+1</f>
-        <v/>
-      </c>
-      <c r="GR4" s="18">
+        <v>46304.0</v>
+      </c>
+      <c r="GR4" s="9">
         <f>GQ4+1</f>
-        <v/>
-      </c>
-      <c r="GS4" s="18">
+        <v>46305.0</v>
+      </c>
+      <c r="GS4" s="9">
         <f>GR4+1</f>
-        <v/>
-      </c>
-      <c r="GT4" s="18">
+        <v>46306.0</v>
+      </c>
+      <c r="GT4" s="9">
         <f>GS4+1</f>
-        <v/>
-      </c>
-      <c r="GU4" s="18">
+        <v>46307.0</v>
+      </c>
+      <c r="GU4" s="9">
         <f>GT4+1</f>
-        <v/>
-      </c>
-      <c r="GV4" s="18">
+        <v>46308.0</v>
+      </c>
+      <c r="GV4" s="9">
         <f>GU4+1</f>
-        <v/>
-      </c>
-      <c r="GW4" s="18">
+        <v>46309.0</v>
+      </c>
+      <c r="GW4" s="9">
         <f>GV4+1</f>
-        <v/>
-      </c>
-      <c r="GX4" s="18">
+        <v>46310.0</v>
+      </c>
+      <c r="GX4" s="9">
         <f>GW4+1</f>
-        <v/>
-      </c>
-      <c r="GY4" s="18">
+        <v>46311.0</v>
+      </c>
+      <c r="GY4" s="9">
         <f>GX4+1</f>
-        <v/>
-      </c>
-      <c r="GZ4" s="18">
+        <v>46312.0</v>
+      </c>
+      <c r="GZ4" s="9">
         <f>GY4+1</f>
-        <v/>
-      </c>
-      <c r="HA4" s="18">
+        <v>46313.0</v>
+      </c>
+      <c r="HA4" s="9">
         <f>GZ4+1</f>
-        <v/>
-      </c>
-      <c r="HB4" s="18">
+        <v>46314.0</v>
+      </c>
+      <c r="HB4" s="9">
         <f>HA4+1</f>
-        <v/>
-      </c>
-      <c r="HC4" s="18">
+        <v>46315.0</v>
+      </c>
+      <c r="HC4" s="9">
         <f>HB4+1</f>
-        <v/>
-      </c>
-      <c r="HD4" s="18">
+        <v>46316.0</v>
+      </c>
+      <c r="HD4" s="9">
         <f>HC4+1</f>
-        <v/>
-      </c>
-      <c r="HE4" s="18">
+        <v>46317.0</v>
+      </c>
+      <c r="HE4" s="9">
         <f>HD4+1</f>
-        <v/>
-      </c>
-      <c r="HF4" s="18">
+        <v>46318.0</v>
+      </c>
+      <c r="HF4" s="9">
         <f>HE4+1</f>
-        <v/>
-      </c>
-      <c r="HG4" s="18">
+        <v>46319.0</v>
+      </c>
+      <c r="HG4" s="9">
         <f>HF4+1</f>
-        <v/>
-      </c>
-      <c r="HH4" s="18">
+        <v>46320.0</v>
+      </c>
+      <c r="HH4" s="9">
         <f>HG4+1</f>
-        <v/>
-      </c>
-      <c r="HI4" s="18">
+        <v>46321.0</v>
+      </c>
+      <c r="HI4" s="9">
         <f>HH4+1</f>
-        <v/>
-      </c>
-      <c r="HJ4" s="18">
+        <v>46322.0</v>
+      </c>
+      <c r="HJ4" s="9">
         <f>HI4+1</f>
-        <v/>
-      </c>
-      <c r="HK4" s="18">
+        <v>46323.0</v>
+      </c>
+      <c r="HK4" s="9">
         <f>HJ4+1</f>
-        <v/>
-      </c>
-      <c r="HL4" s="18">
+        <v>46324.0</v>
+      </c>
+      <c r="HL4" s="9">
         <f>HK4+1</f>
-        <v/>
-      </c>
-      <c r="HM4" s="18">
+        <v>46325.0</v>
+      </c>
+      <c r="HM4" s="9">
         <f>HL4+1</f>
-        <v/>
-      </c>
-      <c r="HN4" s="18">
+        <v>46326.0</v>
+      </c>
+      <c r="HN4" s="9">
         <f>HM4+1</f>
-        <v/>
-      </c>
-      <c r="HO4" s="18">
+        <v>46327.0</v>
+      </c>
+      <c r="HO4" s="9">
         <f>HN4+1</f>
-        <v/>
-      </c>
-      <c r="HP4" s="18">
+        <v>46328.0</v>
+      </c>
+      <c r="HP4" s="9">
         <f>HO4+1</f>
-        <v/>
-      </c>
-      <c r="HQ4" s="18">
+        <v>46329.0</v>
+      </c>
+      <c r="HQ4" s="9">
         <f>HP4+1</f>
-        <v/>
-      </c>
-      <c r="HR4" s="18">
+        <v>46330.0</v>
+      </c>
+      <c r="HR4" s="9">
         <f>HQ4+1</f>
-        <v/>
-      </c>
-      <c r="HS4" s="18">
+        <v>46331.0</v>
+      </c>
+      <c r="HS4" s="9">
         <f>HR4+1</f>
-        <v/>
-      </c>
-      <c r="HT4" s="18">
+        <v>46332.0</v>
+      </c>
+      <c r="HT4" s="9">
         <f>HS4+1</f>
-        <v/>
-      </c>
-      <c r="HU4" s="18">
+        <v>46333.0</v>
+      </c>
+      <c r="HU4" s="9">
         <f>HT4+1</f>
-        <v/>
-      </c>
-      <c r="HV4" s="18">
+        <v>46334.0</v>
+      </c>
+      <c r="HV4" s="9">
         <f>HU4+1</f>
-        <v/>
-      </c>
-      <c r="HW4" s="18">
+        <v>46335.0</v>
+      </c>
+      <c r="HW4" s="9">
         <f>HV4+1</f>
-        <v/>
-      </c>
-      <c r="HX4" s="18">
+        <v>46336.0</v>
+      </c>
+      <c r="HX4" s="9">
         <f>HW4+1</f>
-        <v/>
-      </c>
-      <c r="HY4" s="18">
+        <v>46337.0</v>
+      </c>
+      <c r="HY4" s="9">
         <f>HX4+1</f>
-        <v/>
-      </c>
-      <c r="HZ4" s="18">
+        <v>46338.0</v>
+      </c>
+      <c r="HZ4" s="9">
         <f>HY4+1</f>
-        <v/>
-      </c>
-      <c r="IA4" s="18">
+        <v>46339.0</v>
+      </c>
+      <c r="IA4" s="9">
         <f>HZ4+1</f>
-        <v/>
-      </c>
-      <c r="IB4" s="18">
+        <v>46340.0</v>
+      </c>
+      <c r="IB4" s="9">
         <f>IA4+1</f>
-        <v/>
-      </c>
-      <c r="IC4" s="18">
+        <v>46341.0</v>
+      </c>
+      <c r="IC4" s="9">
         <f>IB4+1</f>
-        <v/>
-      </c>
-      <c r="ID4" s="18">
+        <v>46342.0</v>
+      </c>
+      <c r="ID4" s="9">
         <f>IC4+1</f>
-        <v/>
-      </c>
-      <c r="IE4" s="18">
+        <v>46343.0</v>
+      </c>
+      <c r="IE4" s="9">
         <f>ID4+1</f>
-        <v/>
-      </c>
-      <c r="IF4" s="18">
+        <v>46344.0</v>
+      </c>
+      <c r="IF4" s="9">
         <f>IE4+1</f>
-        <v/>
-      </c>
-      <c r="IG4" s="18">
+        <v>46345.0</v>
+      </c>
+      <c r="IG4" s="9">
         <f>IF4+1</f>
-        <v/>
-      </c>
-      <c r="IH4" s="18">
+        <v>46346.0</v>
+      </c>
+      <c r="IH4" s="9">
         <f>IG4+1</f>
-        <v/>
-      </c>
-      <c r="II4" s="18">
+        <v>46347.0</v>
+      </c>
+      <c r="II4" s="9">
         <f>IH4+1</f>
-        <v/>
-      </c>
-      <c r="IJ4" s="18">
+        <v>46348.0</v>
+      </c>
+      <c r="IJ4" s="9">
         <f>II4+1</f>
-        <v/>
-      </c>
-      <c r="IK4" s="18">
+        <v>46349.0</v>
+      </c>
+      <c r="IK4" s="9">
         <f>IJ4+1</f>
-        <v/>
-      </c>
-      <c r="IL4" s="18">
+        <v>46350.0</v>
+      </c>
+      <c r="IL4" s="9">
         <f>IK4+1</f>
-        <v/>
-      </c>
-      <c r="IM4" s="18">
+        <v>46351.0</v>
+      </c>
+      <c r="IM4" s="9">
         <f>IL4+1</f>
-        <v/>
-      </c>
-      <c r="IN4" s="18">
+        <v>46352.0</v>
+      </c>
+      <c r="IN4" s="9">
         <f>IM4+1</f>
-        <v/>
-      </c>
-      <c r="IO4" s="18">
+        <v>46353.0</v>
+      </c>
+      <c r="IO4" s="9">
         <f>IN4+1</f>
-        <v/>
-      </c>
-      <c r="IP4" s="18">
+        <v>46354.0</v>
+      </c>
+      <c r="IP4" s="9">
         <f>IO4+1</f>
-        <v/>
-      </c>
-      <c r="IQ4" s="18">
+        <v>46355.0</v>
+      </c>
+      <c r="IQ4" s="9">
         <f>IP4+1</f>
-        <v/>
-      </c>
-      <c r="IR4" s="18">
+        <v>46356.0</v>
+      </c>
+      <c r="IR4" s="9">
         <f>IQ4+1</f>
-        <v/>
-      </c>
-      <c r="IS4" s="18">
+        <v>46357.0</v>
+      </c>
+      <c r="IS4" s="9">
         <f>IR4+1</f>
-        <v/>
-      </c>
-      <c r="IT4" s="18">
+        <v>46358.0</v>
+      </c>
+      <c r="IT4" s="9">
         <f>IS4+1</f>
-        <v/>
-      </c>
-      <c r="IU4" s="18">
+        <v>46359.0</v>
+      </c>
+      <c r="IU4" s="9">
         <f>IT4+1</f>
-        <v/>
-      </c>
-      <c r="IV4" s="18">
+        <v>46360.0</v>
+      </c>
+      <c r="IV4" s="9">
         <f>IU4+1</f>
-        <v/>
-      </c>
-      <c r="IW4" s="18">
+        <v>46361.0</v>
+      </c>
+      <c r="IW4" s="9">
         <f>IV4+1</f>
-        <v/>
-      </c>
-      <c r="IX4" s="18">
+        <v>46362.0</v>
+      </c>
+      <c r="IX4" s="9">
         <f>IW4+1</f>
-        <v/>
-      </c>
-      <c r="IY4" s="18">
+        <v>46363.0</v>
+      </c>
+      <c r="IY4" s="9">
         <f>IX4+1</f>
-        <v/>
-      </c>
-      <c r="IZ4" s="18">
+        <v>46364.0</v>
+      </c>
+      <c r="IZ4" s="9">
         <f>IY4+1</f>
-        <v/>
-      </c>
-      <c r="JA4" s="18">
+        <v>46365.0</v>
+      </c>
+      <c r="JA4" s="9">
         <f>IZ4+1</f>
-        <v/>
-      </c>
-      <c r="JB4" s="18">
+        <v>46366.0</v>
+      </c>
+      <c r="JB4" s="9">
         <f>JA4+1</f>
-        <v/>
-      </c>
-      <c r="JC4" s="18">
+        <v>46367.0</v>
+      </c>
+      <c r="JC4" s="9">
         <f>JB4+1</f>
-        <v/>
-      </c>
-      <c r="JD4" s="18">
+        <v>46368.0</v>
+      </c>
+      <c r="JD4" s="9">
         <f>JC4+1</f>
-        <v/>
-      </c>
-      <c r="JE4" s="18">
+        <v>46369.0</v>
+      </c>
+      <c r="JE4" s="9">
         <f>JD4+1</f>
-        <v/>
-      </c>
-      <c r="JF4" s="18">
+        <v>46370.0</v>
+      </c>
+      <c r="JF4" s="9">
         <f>JE4+1</f>
-        <v/>
-      </c>
-      <c r="JG4" s="18">
+        <v>46371.0</v>
+      </c>
+      <c r="JG4" s="9">
         <f>JF4+1</f>
-        <v/>
-      </c>
-      <c r="JH4" s="18">
+        <v>46372.0</v>
+      </c>
+      <c r="JH4" s="9">
         <f>JG4+1</f>
-        <v/>
-      </c>
-      <c r="JI4" s="18">
+        <v>46373.0</v>
+      </c>
+      <c r="JI4" s="9">
         <f>JH4+1</f>
-        <v/>
-      </c>
-      <c r="JJ4" s="18">
+        <v>46374.0</v>
+      </c>
+      <c r="JJ4" s="9">
         <f>JI4+1</f>
-        <v/>
-      </c>
-      <c r="JK4" s="18">
+        <v>46375.0</v>
+      </c>
+      <c r="JK4" s="9">
         <f>JJ4+1</f>
-        <v/>
-      </c>
-      <c r="JL4" s="18">
+        <v>46376.0</v>
+      </c>
+      <c r="JL4" s="9">
         <f>JK4+1</f>
-        <v/>
-      </c>
-      <c r="JM4" s="18">
+        <v>46377.0</v>
+      </c>
+      <c r="JM4" s="9">
         <f>JL4+1</f>
-        <v/>
-      </c>
-      <c r="JN4" s="18">
+        <v>46378.0</v>
+      </c>
+      <c r="JN4" s="9">
         <f>JM4+1</f>
-        <v/>
-      </c>
-      <c r="JO4" s="18">
+        <v>46379.0</v>
+      </c>
+      <c r="JO4" s="9">
         <f>JN4+1</f>
-        <v/>
-      </c>
-      <c r="JP4" s="18">
+        <v>46380.0</v>
+      </c>
+      <c r="JP4" s="9">
         <f>JO4+1</f>
-        <v/>
-      </c>
-      <c r="JQ4" s="18">
+        <v>46381.0</v>
+      </c>
+      <c r="JQ4" s="9">
         <f>JP4+1</f>
-        <v/>
-      </c>
-      <c r="JR4" s="18">
+        <v>46382.0</v>
+      </c>
+      <c r="JR4" s="9">
         <f>JQ4+1</f>
-        <v/>
-      </c>
-      <c r="JS4" s="18">
+        <v>46383.0</v>
+      </c>
+      <c r="JS4" s="9">
         <f>JR4+1</f>
-        <v/>
-      </c>
-      <c r="JT4" s="18">
+        <v>46384.0</v>
+      </c>
+      <c r="JT4" s="9">
         <f>JS4+1</f>
-        <v/>
-      </c>
-      <c r="JU4" s="18">
+        <v>46385.0</v>
+      </c>
+      <c r="JU4" s="9">
         <f>JT4+1</f>
-        <v/>
-      </c>
-      <c r="JV4" s="18">
+        <v>46386.0</v>
+      </c>
+      <c r="JV4" s="9">
         <f>JU4+1</f>
-        <v/>
-      </c>
-      <c r="JW4" s="18">
+        <v>46387.0</v>
+      </c>
+      <c r="JW4" s="9">
         <f>JV4+1</f>
-        <v/>
-      </c>
-      <c r="JX4" s="18">
+        <v>46388.0</v>
+      </c>
+      <c r="JX4" s="9">
         <f>JW4+1</f>
-        <v/>
-      </c>
-      <c r="JY4" s="18">
+        <v>46389.0</v>
+      </c>
+      <c r="JY4" s="9">
         <f>JX4+1</f>
-        <v/>
-      </c>
-      <c r="JZ4" s="18">
+        <v>46390.0</v>
+      </c>
+      <c r="JZ4" s="9">
         <f>JY4+1</f>
-        <v/>
-      </c>
-      <c r="KA4" s="18">
+        <v>46391.0</v>
+      </c>
+      <c r="KA4" s="9">
         <f>JZ4+1</f>
-        <v/>
-      </c>
-      <c r="KB4" s="18">
+        <v>46392.0</v>
+      </c>
+      <c r="KB4" s="9">
         <f>KA4+1</f>
-        <v/>
-      </c>
-      <c r="KC4" s="18">
+        <v>46393.0</v>
+      </c>
+      <c r="KC4" s="9">
         <f>KB4+1</f>
-        <v/>
-      </c>
-      <c r="KD4" s="18">
+        <v>46394.0</v>
+      </c>
+      <c r="KD4" s="9">
         <f>KC4+1</f>
-        <v/>
-      </c>
-      <c r="KE4" s="18">
+        <v>46395.0</v>
+      </c>
+      <c r="KE4" s="9">
         <f>KD4+1</f>
-        <v/>
-      </c>
-      <c r="KF4" s="18">
+        <v>46396.0</v>
+      </c>
+      <c r="KF4" s="9">
         <f>KE4+1</f>
-        <v/>
-      </c>
-      <c r="KG4" s="18">
+        <v>46397.0</v>
+      </c>
+      <c r="KG4" s="9">
         <f>KF4+1</f>
-        <v/>
-      </c>
-      <c r="KH4" s="18">
+        <v>46398.0</v>
+      </c>
+      <c r="KH4" s="9">
         <f>KG4+1</f>
-        <v/>
-      </c>
-      <c r="KI4" s="18">
+        <v>46399.0</v>
+      </c>
+      <c r="KI4" s="9">
         <f>KH4+1</f>
-        <v/>
-      </c>
-      <c r="KJ4" s="18">
+        <v>46400.0</v>
+      </c>
+      <c r="KJ4" s="9">
         <f>KI4+1</f>
-        <v/>
-      </c>
-      <c r="KK4" s="18">
+        <v>46401.0</v>
+      </c>
+      <c r="KK4" s="9">
         <f>KJ4+1</f>
-        <v/>
-      </c>
-      <c r="KL4" s="18">
+        <v>46402.0</v>
+      </c>
+      <c r="KL4" s="9">
         <f>KK4+1</f>
-        <v/>
-      </c>
-      <c r="KM4" s="18">
+        <v>46403.0</v>
+      </c>
+      <c r="KM4" s="9">
         <f>KL4+1</f>
-        <v/>
-      </c>
-      <c r="KN4" s="18">
+        <v>46404.0</v>
+      </c>
+      <c r="KN4" s="9">
         <f>KM4+1</f>
-        <v/>
-      </c>
-      <c r="KO4" s="18">
+        <v>46405.0</v>
+      </c>
+      <c r="KO4" s="9">
         <f>KN4+1</f>
-        <v/>
-      </c>
-      <c r="KP4" s="18">
+        <v>46406.0</v>
+      </c>
+      <c r="KP4" s="9">
         <f>KO4+1</f>
-        <v/>
-      </c>
-      <c r="KQ4" s="18">
+        <v>46407.0</v>
+      </c>
+      <c r="KQ4" s="9">
         <f>KP4+1</f>
-        <v/>
-      </c>
-      <c r="KR4" s="18">
+        <v>46408.0</v>
+      </c>
+      <c r="KR4" s="9">
         <f>KQ4+1</f>
-        <v/>
-      </c>
-      <c r="KS4" s="18">
+        <v>46409.0</v>
+      </c>
+      <c r="KS4" s="9">
         <f>KR4+1</f>
-        <v/>
-      </c>
-      <c r="KT4" s="18">
+        <v>46410.0</v>
+      </c>
+      <c r="KT4" s="9">
         <f>KS4+1</f>
-        <v/>
-      </c>
-      <c r="KU4" s="18">
+        <v>46411.0</v>
+      </c>
+      <c r="KU4" s="9">
         <f>KT4+1</f>
-        <v/>
-      </c>
-      <c r="KV4" s="18">
+        <v>46412.0</v>
+      </c>
+      <c r="KV4" s="9">
         <f>KU4+1</f>
-        <v/>
-      </c>
-      <c r="KW4" s="18">
+        <v>46413.0</v>
+      </c>
+      <c r="KW4" s="9">
         <f>KV4+1</f>
-        <v/>
-      </c>
-      <c r="KX4" s="18">
+        <v>46414.0</v>
+      </c>
+      <c r="KX4" s="9">
         <f>KW4+1</f>
-        <v/>
-      </c>
-      <c r="KY4" s="18">
+        <v>46415.0</v>
+      </c>
+      <c r="KY4" s="9">
         <f>KX4+1</f>
-        <v/>
-      </c>
-      <c r="KZ4" s="18">
+        <v>46416.0</v>
+      </c>
+      <c r="KZ4" s="9">
         <f>KY4+1</f>
-        <v/>
-      </c>
-      <c r="LA4" s="18">
+        <v>46417.0</v>
+      </c>
+      <c r="LA4" s="9">
         <f>KZ4+1</f>
-        <v/>
-      </c>
-      <c r="LB4" s="18">
+        <v>46418.0</v>
+      </c>
+      <c r="LB4" s="9">
         <f>LA4+1</f>
-        <v/>
-      </c>
-      <c r="LC4" s="18">
+        <v>46419.0</v>
+      </c>
+      <c r="LC4" s="9">
         <f>LB4+1</f>
-        <v/>
-      </c>
-      <c r="LD4" s="18">
+        <v>46420.0</v>
+      </c>
+      <c r="LD4" s="9">
         <f>LC4+1</f>
-        <v/>
-      </c>
-      <c r="LE4" s="18">
+        <v>46421.0</v>
+      </c>
+      <c r="LE4" s="9">
         <f>LD4+1</f>
-        <v/>
-      </c>
-      <c r="LF4" s="18">
+        <v>46422.0</v>
+      </c>
+      <c r="LF4" s="9">
         <f>LE4+1</f>
-        <v/>
-      </c>
-      <c r="LG4" s="18">
+        <v>46423.0</v>
+      </c>
+      <c r="LG4" s="9">
         <f>LF4+1</f>
-        <v/>
-      </c>
-      <c r="LH4" s="18">
+        <v>46424.0</v>
+      </c>
+      <c r="LH4" s="9">
         <f>LG4+1</f>
-        <v/>
-      </c>
-      <c r="LI4" s="18">
+        <v>46425.0</v>
+      </c>
+      <c r="LI4" s="9">
         <f>LH4+1</f>
-        <v/>
-      </c>
-      <c r="LJ4" s="18">
+        <v>46426.0</v>
+      </c>
+      <c r="LJ4" s="9">
         <f>LI4+1</f>
-        <v/>
-      </c>
-      <c r="LK4" s="18">
+        <v>46427.0</v>
+      </c>
+      <c r="LK4" s="9">
         <f>LJ4+1</f>
-        <v/>
-      </c>
-      <c r="LL4" s="18">
+        <v>46428.0</v>
+      </c>
+      <c r="LL4" s="9">
         <f>LK4+1</f>
-        <v/>
-      </c>
-      <c r="LM4" s="18">
+        <v>46429.0</v>
+      </c>
+      <c r="LM4" s="9">
         <f>LL4+1</f>
-        <v/>
-      </c>
-      <c r="LN4" s="18">
+        <v>46430.0</v>
+      </c>
+      <c r="LN4" s="9">
         <f>LM4+1</f>
-        <v/>
-      </c>
-      <c r="LO4" s="18">
+        <v>46431.0</v>
+      </c>
+      <c r="LO4" s="9">
         <f>LN4+1</f>
-        <v/>
-      </c>
-      <c r="LP4" s="18">
+        <v>46432.0</v>
+      </c>
+      <c r="LP4" s="9">
         <f>LO4+1</f>
-        <v/>
-      </c>
-      <c r="LQ4" s="18">
+        <v>46433.0</v>
+      </c>
+      <c r="LQ4" s="9">
         <f>LP4+1</f>
-        <v/>
-      </c>
-      <c r="LR4" s="18">
+        <v>46434.0</v>
+      </c>
+      <c r="LR4" s="9">
         <f>LQ4+1</f>
-        <v/>
-      </c>
-      <c r="LS4" s="18">
+        <v>46435.0</v>
+      </c>
+      <c r="LS4" s="9">
         <f>LR4+1</f>
-        <v/>
-      </c>
-      <c r="LT4" s="18">
+        <v>46436.0</v>
+      </c>
+      <c r="LT4" s="9">
         <f>LS4+1</f>
-        <v/>
-      </c>
-      <c r="LU4" s="18">
+        <v>46437.0</v>
+      </c>
+      <c r="LU4" s="9">
         <f>LT4+1</f>
-        <v/>
-      </c>
-      <c r="LV4" s="18">
+        <v>46438.0</v>
+      </c>
+      <c r="LV4" s="9">
         <f>LU4+1</f>
-        <v/>
-      </c>
-      <c r="LW4" s="18">
+        <v>46439.0</v>
+      </c>
+      <c r="LW4" s="9">
         <f>LV4+1</f>
-        <v/>
-      </c>
-      <c r="LX4" s="18">
+        <v>46440.0</v>
+      </c>
+      <c r="LX4" s="9">
         <f>LW4+1</f>
-        <v/>
-      </c>
-      <c r="LY4" s="18">
+        <v>46441.0</v>
+      </c>
+      <c r="LY4" s="9">
         <f>LX4+1</f>
-        <v/>
-      </c>
-      <c r="LZ4" s="18">
+        <v>46442.0</v>
+      </c>
+      <c r="LZ4" s="9">
         <f>LY4+1</f>
-        <v/>
-      </c>
-      <c r="MA4" s="18">
+        <v>46443.0</v>
+      </c>
+      <c r="MA4" s="9">
         <f>LZ4+1</f>
-        <v/>
-      </c>
-      <c r="MB4" s="18">
+        <v>46444.0</v>
+      </c>
+      <c r="MB4" s="9">
         <f>MA4+1</f>
-        <v/>
-      </c>
-      <c r="MC4" s="18">
+        <v>46445.0</v>
+      </c>
+      <c r="MC4" s="9">
         <f>MB4+1</f>
-        <v/>
-      </c>
-      <c r="MD4" s="18">
+        <v>46446.0</v>
+      </c>
+      <c r="MD4" s="9">
         <f>MC4+1</f>
-        <v/>
-      </c>
-      <c r="ME4" s="18">
+        <v>46447.0</v>
+      </c>
+      <c r="ME4" s="9">
         <f>MD4+1</f>
-        <v/>
-      </c>
-      <c r="MF4" s="18">
+        <v>46448.0</v>
+      </c>
+      <c r="MF4" s="9">
         <f>ME4+1</f>
-        <v/>
-      </c>
-      <c r="MG4" s="18">
+        <v>46449.0</v>
+      </c>
+      <c r="MG4" s="9">
         <f>MF4+1</f>
-        <v/>
-      </c>
-      <c r="MH4" s="18">
+        <v>46450.0</v>
+      </c>
+      <c r="MH4" s="9">
         <f>MG4+1</f>
-        <v/>
-      </c>
-      <c r="MI4" s="18">
+        <v>46451.0</v>
+      </c>
+      <c r="MI4" s="9">
         <f>MH4+1</f>
-        <v/>
-      </c>
-      <c r="MJ4" s="18">
+        <v>46452.0</v>
+      </c>
+      <c r="MJ4" s="9">
         <f>MI4+1</f>
-        <v/>
-      </c>
-      <c r="MK4" s="18">
+        <v>46453.0</v>
+      </c>
+      <c r="MK4" s="9">
         <f>MJ4+1</f>
-        <v/>
-      </c>
-      <c r="ML4" s="18">
+        <v>46454.0</v>
+      </c>
+      <c r="ML4" s="9">
         <f>MK4+1</f>
-        <v/>
-      </c>
-      <c r="MM4" s="18">
+        <v>46455.0</v>
+      </c>
+      <c r="MM4" s="9">
         <f>ML4+1</f>
-        <v/>
-      </c>
-      <c r="MN4" s="18">
+        <v>46456.0</v>
+      </c>
+      <c r="MN4" s="9">
         <f>MM4+1</f>
-        <v/>
-      </c>
-      <c r="MO4" s="18">
+        <v>46457.0</v>
+      </c>
+      <c r="MO4" s="9">
         <f>MN4+1</f>
-        <v/>
-      </c>
-      <c r="MP4" s="18">
+        <v>46458.0</v>
+      </c>
+      <c r="MP4" s="9">
         <f>MO4+1</f>
-        <v/>
-      </c>
-      <c r="MQ4" s="18">
+        <v>46459.0</v>
+      </c>
+      <c r="MQ4" s="9">
         <f>MP4+1</f>
-        <v/>
-      </c>
-      <c r="MR4" s="18">
+        <v>46460.0</v>
+      </c>
+      <c r="MR4" s="9">
         <f>MQ4+1</f>
-        <v/>
-      </c>
-      <c r="MS4" s="18">
+        <v>46461.0</v>
+      </c>
+      <c r="MS4" s="9">
         <f>MR4+1</f>
-        <v/>
-      </c>
-      <c r="MT4" s="18">
+        <v>46462.0</v>
+      </c>
+      <c r="MT4" s="9">
         <f>MS4+1</f>
-        <v/>
-      </c>
-      <c r="MU4" s="18">
+        <v>46463.0</v>
+      </c>
+      <c r="MU4" s="9">
         <f>MT4+1</f>
-        <v/>
-      </c>
-      <c r="MV4" s="18">
+        <v>46464.0</v>
+      </c>
+      <c r="MV4" s="9">
         <f>MU4+1</f>
-        <v/>
-      </c>
-      <c r="MW4" s="18">
+        <v>46465.0</v>
+      </c>
+      <c r="MW4" s="9">
         <f>MV4+1</f>
-        <v/>
-      </c>
-      <c r="MX4" s="18">
+        <v>46466.0</v>
+      </c>
+      <c r="MX4" s="9">
         <f>MW4+1</f>
-        <v/>
-      </c>
-      <c r="MY4" s="18">
+        <v>46467.0</v>
+      </c>
+      <c r="MY4" s="9">
         <f>MX4+1</f>
-        <v/>
-      </c>
-      <c r="MZ4" s="18">
+        <v>46468.0</v>
+      </c>
+      <c r="MZ4" s="9">
         <f>MY4+1</f>
-        <v/>
-      </c>
-      <c r="NA4" s="18">
+        <v>46469.0</v>
+      </c>
+      <c r="NA4" s="9">
         <f>MZ4+1</f>
-        <v/>
-      </c>
-      <c r="NB4" s="18">
+        <v>46470.0</v>
+      </c>
+      <c r="NB4" s="9">
         <f>NA4+1</f>
-        <v/>
-      </c>
-      <c r="NC4" s="18">
+        <v>46471.0</v>
+      </c>
+      <c r="NC4" s="9">
         <f>NB4+1</f>
-        <v/>
-      </c>
-      <c r="ND4" s="18">
+        <v>46472.0</v>
+      </c>
+      <c r="ND4" s="9">
         <f>NC4+1</f>
-        <v/>
-      </c>
-      <c r="NE4" s="18">
+        <v>46473.0</v>
+      </c>
+      <c r="NE4" s="9">
         <f>ND4+1</f>
-        <v/>
-      </c>
-      <c r="NF4" s="18">
+        <v>46474.0</v>
+      </c>
+      <c r="NF4" s="9">
         <f>NE4+1</f>
-        <v/>
-      </c>
-      <c r="NG4" s="18">
+        <v>46475.0</v>
+      </c>
+      <c r="NG4" s="9">
         <f>NF4+1</f>
-        <v/>
-      </c>
-      <c r="NH4" s="18">
+        <v>46476.0</v>
+      </c>
+      <c r="NH4" s="9">
         <f>NG4+1</f>
-        <v/>
+        <v>46477.0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="19" t="n"/>
-      <c r="B5" s="19" t="n"/>
-      <c r="C5" s="19" t="n"/>
-      <c r="D5" s="19" t="n"/>
-      <c r="E5" s="19" t="n"/>
-      <c r="F5" s="19" t="n"/>
-      <c r="G5" s="19" t="n"/>
-      <c r="H5" s="10">
+    <row r="5" ht="15" customHeight="1">
+      <c r="H5" s="10" t="str">
         <f>TEXT(H4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="I5" s="10">
+        <v>水</v>
+      </c>
+      <c r="I5" s="10" t="str">
         <f>TEXT(I4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="J5" s="10">
+        <v>木</v>
+      </c>
+      <c r="J5" s="10" t="str">
         <f>TEXT(J4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="K5" s="10">
+        <v>金</v>
+      </c>
+      <c r="K5" s="10" t="str">
         <f>TEXT(K4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="L5" s="10">
+        <v>土</v>
+      </c>
+      <c r="L5" s="10" t="str">
         <f>TEXT(L4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="M5" s="10">
+        <v>日</v>
+      </c>
+      <c r="M5" s="10" t="str">
         <f>TEXT(M4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="N5" s="10">
+        <v>月</v>
+      </c>
+      <c r="N5" s="10" t="str">
         <f>TEXT(N4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="O5" s="10">
+        <v>火</v>
+      </c>
+      <c r="O5" s="10" t="str">
         <f>TEXT(O4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="P5" s="10">
+        <v>水</v>
+      </c>
+      <c r="P5" s="10" t="str">
         <f>TEXT(P4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="Q5" s="10">
+        <v>木</v>
+      </c>
+      <c r="Q5" s="10" t="str">
         <f>TEXT(Q4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="R5" s="10">
+        <v>金</v>
+      </c>
+      <c r="R5" s="10" t="str">
         <f>TEXT(R4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="S5" s="10">
+        <v>土</v>
+      </c>
+      <c r="S5" s="10" t="str">
         <f>TEXT(S4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="T5" s="10">
+        <v>日</v>
+      </c>
+      <c r="T5" s="10" t="str">
         <f>TEXT(T4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="U5" s="10">
+        <v>月</v>
+      </c>
+      <c r="U5" s="10" t="str">
         <f>TEXT(U4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="V5" s="10">
+        <v>火</v>
+      </c>
+      <c r="V5" s="10" t="str">
         <f>TEXT(V4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="W5" s="10">
+        <v>水</v>
+      </c>
+      <c r="W5" s="10" t="str">
         <f>TEXT(W4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="X5" s="10">
+        <v>木</v>
+      </c>
+      <c r="X5" s="10" t="str">
         <f>TEXT(X4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="Y5" s="10">
+        <v>金</v>
+      </c>
+      <c r="Y5" s="10" t="str">
         <f>TEXT(Y4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="Z5" s="10">
+        <v>土</v>
+      </c>
+      <c r="Z5" s="10" t="str">
         <f>TEXT(Z4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="AA5" s="10">
+        <v>日</v>
+      </c>
+      <c r="AA5" s="10" t="str">
         <f>TEXT(AA4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="AB5" s="10">
+        <v>月</v>
+      </c>
+      <c r="AB5" s="10" t="str">
         <f>TEXT(AB4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="AC5" s="10">
+        <v>火</v>
+      </c>
+      <c r="AC5" s="10" t="str">
         <f>TEXT(AC4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="AD5" s="10">
+        <v>水</v>
+      </c>
+      <c r="AD5" s="10" t="str">
         <f>TEXT(AD4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="AE5" s="10">
+        <v>木</v>
+      </c>
+      <c r="AE5" s="10" t="str">
         <f>TEXT(AE4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="AF5" s="10">
+        <v>金</v>
+      </c>
+      <c r="AF5" s="10" t="str">
         <f>TEXT(AF4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="AG5" s="10">
+        <v>土</v>
+      </c>
+      <c r="AG5" s="10" t="str">
         <f>TEXT(AG4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="AH5" s="10">
+        <v>日</v>
+      </c>
+      <c r="AH5" s="10" t="str">
         <f>TEXT(AH4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="AI5" s="10">
+        <v>月</v>
+      </c>
+      <c r="AI5" s="10" t="str">
         <f>TEXT(AI4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="AJ5" s="10">
+        <v>火</v>
+      </c>
+      <c r="AJ5" s="10" t="str">
         <f>TEXT(AJ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="AK5" s="10">
+        <v>水</v>
+      </c>
+      <c r="AK5" s="10" t="str">
         <f>TEXT(AK4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="AL5" s="10">
+        <v>木</v>
+      </c>
+      <c r="AL5" s="10" t="str">
         <f>TEXT(AL4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="AM5" s="10">
+        <v>金</v>
+      </c>
+      <c r="AM5" s="10" t="str">
         <f>TEXT(AM4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="AN5" s="10">
+        <v>土</v>
+      </c>
+      <c r="AN5" s="10" t="str">
         <f>TEXT(AN4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="AO5" s="10">
+        <v>日</v>
+      </c>
+      <c r="AO5" s="10" t="str">
         <f>TEXT(AO4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="AP5" s="10">
+        <v>月</v>
+      </c>
+      <c r="AP5" s="10" t="str">
         <f>TEXT(AP4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="AQ5" s="10">
+        <v>火</v>
+      </c>
+      <c r="AQ5" s="10" t="str">
         <f>TEXT(AQ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="AR5" s="10">
+        <v>水</v>
+      </c>
+      <c r="AR5" s="10" t="str">
         <f>TEXT(AR4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="AS5" s="10">
+        <v>木</v>
+      </c>
+      <c r="AS5" s="10" t="str">
         <f>TEXT(AS4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="AT5" s="10">
+        <v>金</v>
+      </c>
+      <c r="AT5" s="10" t="str">
         <f>TEXT(AT4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="AU5" s="10">
+        <v>土</v>
+      </c>
+      <c r="AU5" s="10" t="str">
         <f>TEXT(AU4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="AV5" s="10">
+        <v>日</v>
+      </c>
+      <c r="AV5" s="10" t="str">
         <f>TEXT(AV4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="AW5" s="10">
+        <v>月</v>
+      </c>
+      <c r="AW5" s="10" t="str">
         <f>TEXT(AW4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="AX5" s="10">
+        <v>火</v>
+      </c>
+      <c r="AX5" s="10" t="str">
         <f>TEXT(AX4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="AY5" s="10">
+        <v>水</v>
+      </c>
+      <c r="AY5" s="10" t="str">
         <f>TEXT(AY4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="AZ5" s="10">
+        <v>木</v>
+      </c>
+      <c r="AZ5" s="10" t="str">
         <f>TEXT(AZ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="BA5" s="10">
+        <v>金</v>
+      </c>
+      <c r="BA5" s="10" t="str">
         <f>TEXT(BA4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="BB5" s="10">
+        <v>土</v>
+      </c>
+      <c r="BB5" s="10" t="str">
         <f>TEXT(BB4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="BC5" s="10">
+        <v>日</v>
+      </c>
+      <c r="BC5" s="10" t="str">
         <f>TEXT(BC4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="BD5" s="10">
+        <v>月</v>
+      </c>
+      <c r="BD5" s="10" t="str">
         <f>TEXT(BD4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="BE5" s="10">
+        <v>火</v>
+      </c>
+      <c r="BE5" s="10" t="str">
         <f>TEXT(BE4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="BF5" s="10">
+        <v>水</v>
+      </c>
+      <c r="BF5" s="10" t="str">
         <f>TEXT(BF4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="BG5" s="10">
+        <v>木</v>
+      </c>
+      <c r="BG5" s="10" t="str">
         <f>TEXT(BG4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="BH5" s="10">
+        <v>金</v>
+      </c>
+      <c r="BH5" s="10" t="str">
         <f>TEXT(BH4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="BI5" s="10">
+        <v>土</v>
+      </c>
+      <c r="BI5" s="10" t="str">
         <f>TEXT(BI4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="BJ5" s="10">
+        <v>日</v>
+      </c>
+      <c r="BJ5" s="10" t="str">
         <f>TEXT(BJ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="BK5" s="10">
+        <v>月</v>
+      </c>
+      <c r="BK5" s="10" t="str">
         <f>TEXT(BK4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="BL5" s="10">
+        <v>火</v>
+      </c>
+      <c r="BL5" s="10" t="str">
         <f>TEXT(BL4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="BM5" s="10">
+        <v>水</v>
+      </c>
+      <c r="BM5" s="10" t="str">
         <f>TEXT(BM4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="BN5" s="10">
+        <v>木</v>
+      </c>
+      <c r="BN5" s="10" t="str">
         <f>TEXT(BN4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="BO5" s="10">
+        <v>金</v>
+      </c>
+      <c r="BO5" s="10" t="str">
         <f>TEXT(BO4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="BP5" s="10">
+        <v>土</v>
+      </c>
+      <c r="BP5" s="10" t="str">
         <f>TEXT(BP4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="BQ5" s="10">
+        <v>日</v>
+      </c>
+      <c r="BQ5" s="10" t="str">
         <f>TEXT(BQ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="BR5" s="10">
+        <v>月</v>
+      </c>
+      <c r="BR5" s="10" t="str">
         <f>TEXT(BR4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="BS5" s="10">
+        <v>火</v>
+      </c>
+      <c r="BS5" s="10" t="str">
         <f>TEXT(BS4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="BT5" s="10">
+        <v>水</v>
+      </c>
+      <c r="BT5" s="10" t="str">
         <f>TEXT(BT4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="BU5" s="10">
+        <v>木</v>
+      </c>
+      <c r="BU5" s="10" t="str">
         <f>TEXT(BU4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="BV5" s="10">
+        <v>金</v>
+      </c>
+      <c r="BV5" s="10" t="str">
         <f>TEXT(BV4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="BW5" s="10">
+        <v>土</v>
+      </c>
+      <c r="BW5" s="10" t="str">
         <f>TEXT(BW4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="BX5" s="10">
+        <v>日</v>
+      </c>
+      <c r="BX5" s="10" t="str">
         <f>TEXT(BX4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="BY5" s="10">
+        <v>月</v>
+      </c>
+      <c r="BY5" s="10" t="str">
         <f>TEXT(BY4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="BZ5" s="10">
+        <v>火</v>
+      </c>
+      <c r="BZ5" s="10" t="str">
         <f>TEXT(BZ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="CA5" s="10">
+        <v>水</v>
+      </c>
+      <c r="CA5" s="10" t="str">
         <f>TEXT(CA4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="CB5" s="10">
+        <v>木</v>
+      </c>
+      <c r="CB5" s="10" t="str">
         <f>TEXT(CB4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="CC5" s="10">
+        <v>金</v>
+      </c>
+      <c r="CC5" s="10" t="str">
         <f>TEXT(CC4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="CD5" s="10">
+        <v>土</v>
+      </c>
+      <c r="CD5" s="10" t="str">
         <f>TEXT(CD4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="CE5" s="10">
+        <v>日</v>
+      </c>
+      <c r="CE5" s="10" t="str">
         <f>TEXT(CE4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="CF5" s="10">
+        <v>月</v>
+      </c>
+      <c r="CF5" s="10" t="str">
         <f>TEXT(CF4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="CG5" s="10">
+        <v>火</v>
+      </c>
+      <c r="CG5" s="10" t="str">
         <f>TEXT(CG4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="CH5" s="10">
+        <v>水</v>
+      </c>
+      <c r="CH5" s="10" t="str">
         <f>TEXT(CH4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="CI5" s="10">
+        <v>木</v>
+      </c>
+      <c r="CI5" s="10" t="str">
         <f>TEXT(CI4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="CJ5" s="10">
+        <v>金</v>
+      </c>
+      <c r="CJ5" s="10" t="str">
         <f>TEXT(CJ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="CK5" s="10">
+        <v>土</v>
+      </c>
+      <c r="CK5" s="10" t="str">
         <f>TEXT(CK4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="CL5" s="10">
+        <v>日</v>
+      </c>
+      <c r="CL5" s="10" t="str">
         <f>TEXT(CL4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="CM5" s="10">
+        <v>月</v>
+      </c>
+      <c r="CM5" s="10" t="str">
         <f>TEXT(CM4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="CN5" s="10">
+        <v>火</v>
+      </c>
+      <c r="CN5" s="10" t="str">
         <f>TEXT(CN4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="CO5" s="10">
+        <v>水</v>
+      </c>
+      <c r="CO5" s="10" t="str">
         <f>TEXT(CO4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="CP5" s="10">
+        <v>木</v>
+      </c>
+      <c r="CP5" s="10" t="str">
         <f>TEXT(CP4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="CQ5" s="10">
+        <v>金</v>
+      </c>
+      <c r="CQ5" s="10" t="str">
         <f>TEXT(CQ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="CR5" s="10">
+        <v>土</v>
+      </c>
+      <c r="CR5" s="10" t="str">
         <f>TEXT(CR4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="CS5" s="10">
+        <v>日</v>
+      </c>
+      <c r="CS5" s="10" t="str">
         <f>TEXT(CS4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="CT5" s="10">
+        <v>月</v>
+      </c>
+      <c r="CT5" s="10" t="str">
         <f>TEXT(CT4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="CU5" s="10">
+        <v>火</v>
+      </c>
+      <c r="CU5" s="10" t="str">
         <f>TEXT(CU4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="CV5" s="10">
+        <v>水</v>
+      </c>
+      <c r="CV5" s="10" t="str">
         <f>TEXT(CV4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="CW5" s="10">
+        <v>木</v>
+      </c>
+      <c r="CW5" s="10" t="str">
         <f>TEXT(CW4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="CX5" s="10">
+        <v>金</v>
+      </c>
+      <c r="CX5" s="10" t="str">
         <f>TEXT(CX4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="CY5" s="10">
+        <v>土</v>
+      </c>
+      <c r="CY5" s="10" t="str">
         <f>TEXT(CY4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="CZ5" s="10">
+        <v>日</v>
+      </c>
+      <c r="CZ5" s="10" t="str">
         <f>TEXT(CZ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="DA5" s="10">
+        <v>月</v>
+      </c>
+      <c r="DA5" s="10" t="str">
         <f>TEXT(DA4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="DB5" s="10">
+        <v>火</v>
+      </c>
+      <c r="DB5" s="10" t="str">
         <f>TEXT(DB4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="DC5" s="10">
+        <v>水</v>
+      </c>
+      <c r="DC5" s="10" t="str">
         <f>TEXT(DC4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="DD5" s="10">
+        <v>木</v>
+      </c>
+      <c r="DD5" s="10" t="str">
         <f>TEXT(DD4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="DE5" s="10">
+        <v>金</v>
+      </c>
+      <c r="DE5" s="10" t="str">
         <f>TEXT(DE4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="DF5" s="10">
+        <v>土</v>
+      </c>
+      <c r="DF5" s="10" t="str">
         <f>TEXT(DF4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="DG5" s="10">
+        <v>日</v>
+      </c>
+      <c r="DG5" s="10" t="str">
         <f>TEXT(DG4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="DH5" s="10">
+        <v>月</v>
+      </c>
+      <c r="DH5" s="10" t="str">
         <f>TEXT(DH4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="DI5" s="10">
+        <v>火</v>
+      </c>
+      <c r="DI5" s="10" t="str">
         <f>TEXT(DI4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="DJ5" s="10">
+        <v>水</v>
+      </c>
+      <c r="DJ5" s="10" t="str">
         <f>TEXT(DJ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="DK5" s="10">
+        <v>木</v>
+      </c>
+      <c r="DK5" s="10" t="str">
         <f>TEXT(DK4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="DL5" s="10">
+        <v>金</v>
+      </c>
+      <c r="DL5" s="10" t="str">
         <f>TEXT(DL4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="DM5" s="10">
+        <v>土</v>
+      </c>
+      <c r="DM5" s="10" t="str">
         <f>TEXT(DM4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="DN5" s="10">
+        <v>日</v>
+      </c>
+      <c r="DN5" s="10" t="str">
         <f>TEXT(DN4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="DO5" s="10">
+        <v>月</v>
+      </c>
+      <c r="DO5" s="10" t="str">
         <f>TEXT(DO4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="DP5" s="10">
+        <v>火</v>
+      </c>
+      <c r="DP5" s="10" t="str">
         <f>TEXT(DP4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="DQ5" s="10">
+        <v>水</v>
+      </c>
+      <c r="DQ5" s="10" t="str">
         <f>TEXT(DQ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="DR5" s="10">
+        <v>木</v>
+      </c>
+      <c r="DR5" s="10" t="str">
         <f>TEXT(DR4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="DS5" s="10">
+        <v>金</v>
+      </c>
+      <c r="DS5" s="10" t="str">
         <f>TEXT(DS4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="DT5" s="10">
+        <v>土</v>
+      </c>
+      <c r="DT5" s="10" t="str">
         <f>TEXT(DT4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="DU5" s="10">
+        <v>日</v>
+      </c>
+      <c r="DU5" s="10" t="str">
         <f>TEXT(DU4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="DV5" s="10">
+        <v>月</v>
+      </c>
+      <c r="DV5" s="10" t="str">
         <f>TEXT(DV4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="DW5" s="10">
+        <v>火</v>
+      </c>
+      <c r="DW5" s="10" t="str">
         <f>TEXT(DW4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="DX5" s="10">
+        <v>水</v>
+      </c>
+      <c r="DX5" s="10" t="str">
         <f>TEXT(DX4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="DY5" s="10">
+        <v>木</v>
+      </c>
+      <c r="DY5" s="10" t="str">
         <f>TEXT(DY4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="DZ5" s="10">
+        <v>金</v>
+      </c>
+      <c r="DZ5" s="10" t="str">
         <f>TEXT(DZ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="EA5" s="10">
+        <v>土</v>
+      </c>
+      <c r="EA5" s="10" t="str">
         <f>TEXT(EA4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="EB5" s="10">
+        <v>日</v>
+      </c>
+      <c r="EB5" s="10" t="str">
         <f>TEXT(EB4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="EC5" s="10">
+        <v>月</v>
+      </c>
+      <c r="EC5" s="10" t="str">
         <f>TEXT(EC4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="ED5" s="10">
+        <v>火</v>
+      </c>
+      <c r="ED5" s="10" t="str">
         <f>TEXT(ED4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="EE5" s="10">
+        <v>水</v>
+      </c>
+      <c r="EE5" s="10" t="str">
         <f>TEXT(EE4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="EF5" s="10">
+        <v>木</v>
+      </c>
+      <c r="EF5" s="10" t="str">
         <f>TEXT(EF4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="EG5" s="10">
+        <v>金</v>
+      </c>
+      <c r="EG5" s="10" t="str">
         <f>TEXT(EG4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="EH5" s="10">
+        <v>土</v>
+      </c>
+      <c r="EH5" s="10" t="str">
         <f>TEXT(EH4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="EI5" s="10">
+        <v>日</v>
+      </c>
+      <c r="EI5" s="10" t="str">
         <f>TEXT(EI4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="EJ5" s="10">
+        <v>月</v>
+      </c>
+      <c r="EJ5" s="10" t="str">
         <f>TEXT(EJ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="EK5" s="10">
+        <v>火</v>
+      </c>
+      <c r="EK5" s="10" t="str">
         <f>TEXT(EK4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="EL5" s="10">
+        <v>水</v>
+      </c>
+      <c r="EL5" s="10" t="str">
         <f>TEXT(EL4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="EM5" s="10">
+        <v>木</v>
+      </c>
+      <c r="EM5" s="10" t="str">
         <f>TEXT(EM4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="EN5" s="10">
+        <v>金</v>
+      </c>
+      <c r="EN5" s="10" t="str">
         <f>TEXT(EN4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="EO5" s="10">
+        <v>土</v>
+      </c>
+      <c r="EO5" s="10" t="str">
         <f>TEXT(EO4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="EP5" s="10">
+        <v>日</v>
+      </c>
+      <c r="EP5" s="10" t="str">
         <f>TEXT(EP4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="EQ5" s="10">
+        <v>月</v>
+      </c>
+      <c r="EQ5" s="10" t="str">
         <f>TEXT(EQ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="ER5" s="10">
+        <v>火</v>
+      </c>
+      <c r="ER5" s="10" t="str">
         <f>TEXT(ER4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="ES5" s="10">
+        <v>水</v>
+      </c>
+      <c r="ES5" s="10" t="str">
         <f>TEXT(ES4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="ET5" s="10">
+        <v>木</v>
+      </c>
+      <c r="ET5" s="10" t="str">
         <f>TEXT(ET4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="EU5" s="10">
+        <v>金</v>
+      </c>
+      <c r="EU5" s="10" t="str">
         <f>TEXT(EU4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="EV5" s="10">
+        <v>土</v>
+      </c>
+      <c r="EV5" s="10" t="str">
         <f>TEXT(EV4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="EW5" s="10">
+        <v>日</v>
+      </c>
+      <c r="EW5" s="10" t="str">
         <f>TEXT(EW4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="EX5" s="10">
+        <v>月</v>
+      </c>
+      <c r="EX5" s="10" t="str">
         <f>TEXT(EX4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="EY5" s="10">
+        <v>火</v>
+      </c>
+      <c r="EY5" s="10" t="str">
         <f>TEXT(EY4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="EZ5" s="10">
+        <v>水</v>
+      </c>
+      <c r="EZ5" s="10" t="str">
         <f>TEXT(EZ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="FA5" s="10">
+        <v>木</v>
+      </c>
+      <c r="FA5" s="10" t="str">
         <f>TEXT(FA4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="FB5" s="10">
+        <v>金</v>
+      </c>
+      <c r="FB5" s="10" t="str">
         <f>TEXT(FB4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="FC5" s="10">
+        <v>土</v>
+      </c>
+      <c r="FC5" s="10" t="str">
         <f>TEXT(FC4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="FD5" s="10">
+        <v>日</v>
+      </c>
+      <c r="FD5" s="10" t="str">
         <f>TEXT(FD4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="FE5" s="10">
+        <v>月</v>
+      </c>
+      <c r="FE5" s="10" t="str">
         <f>TEXT(FE4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="FF5" s="10">
+        <v>火</v>
+      </c>
+      <c r="FF5" s="10" t="str">
         <f>TEXT(FF4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="FG5" s="10">
+        <v>水</v>
+      </c>
+      <c r="FG5" s="10" t="str">
         <f>TEXT(FG4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="FH5" s="10">
+        <v>木</v>
+      </c>
+      <c r="FH5" s="10" t="str">
         <f>TEXT(FH4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="FI5" s="10">
+        <v>金</v>
+      </c>
+      <c r="FI5" s="10" t="str">
         <f>TEXT(FI4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="FJ5" s="10">
+        <v>土</v>
+      </c>
+      <c r="FJ5" s="10" t="str">
         <f>TEXT(FJ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="FK5" s="10">
+        <v>日</v>
+      </c>
+      <c r="FK5" s="10" t="str">
         <f>TEXT(FK4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="FL5" s="10">
+        <v>月</v>
+      </c>
+      <c r="FL5" s="10" t="str">
         <f>TEXT(FL4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="FM5" s="10">
+        <v>火</v>
+      </c>
+      <c r="FM5" s="10" t="str">
         <f>TEXT(FM4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="FN5" s="10">
+        <v>水</v>
+      </c>
+      <c r="FN5" s="10" t="str">
         <f>TEXT(FN4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="FO5" s="10">
+        <v>木</v>
+      </c>
+      <c r="FO5" s="10" t="str">
         <f>TEXT(FO4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="FP5" s="10">
+        <v>金</v>
+      </c>
+      <c r="FP5" s="10" t="str">
         <f>TEXT(FP4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="FQ5" s="10">
+        <v>土</v>
+      </c>
+      <c r="FQ5" s="10" t="str">
         <f>TEXT(FQ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="FR5" s="10">
+        <v>日</v>
+      </c>
+      <c r="FR5" s="10" t="str">
         <f>TEXT(FR4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="FS5" s="10">
+        <v>月</v>
+      </c>
+      <c r="FS5" s="10" t="str">
         <f>TEXT(FS4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="FT5" s="10">
+        <v>火</v>
+      </c>
+      <c r="FT5" s="10" t="str">
         <f>TEXT(FT4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="FU5" s="10">
+        <v>水</v>
+      </c>
+      <c r="FU5" s="10" t="str">
         <f>TEXT(FU4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="FV5" s="10">
+        <v>木</v>
+      </c>
+      <c r="FV5" s="10" t="str">
         <f>TEXT(FV4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="FW5" s="10">
+        <v>金</v>
+      </c>
+      <c r="FW5" s="10" t="str">
         <f>TEXT(FW4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="FX5" s="10">
+        <v>土</v>
+      </c>
+      <c r="FX5" s="10" t="str">
         <f>TEXT(FX4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="FY5" s="10">
+        <v>日</v>
+      </c>
+      <c r="FY5" s="10" t="str">
         <f>TEXT(FY4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="FZ5" s="10">
+        <v>月</v>
+      </c>
+      <c r="FZ5" s="10" t="str">
         <f>TEXT(FZ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="GA5" s="10">
+        <v>火</v>
+      </c>
+      <c r="GA5" s="10" t="str">
         <f>TEXT(GA4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="GB5" s="10">
+        <v>水</v>
+      </c>
+      <c r="GB5" s="10" t="str">
         <f>TEXT(GB4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="GC5" s="10">
+        <v>木</v>
+      </c>
+      <c r="GC5" s="10" t="str">
         <f>TEXT(GC4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="GD5" s="10">
+        <v>金</v>
+      </c>
+      <c r="GD5" s="10" t="str">
         <f>TEXT(GD4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="GE5" s="10">
+        <v>土</v>
+      </c>
+      <c r="GE5" s="10" t="str">
         <f>TEXT(GE4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="GF5" s="10">
+        <v>日</v>
+      </c>
+      <c r="GF5" s="10" t="str">
         <f>TEXT(GF4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="GG5" s="10">
+        <v>月</v>
+      </c>
+      <c r="GG5" s="10" t="str">
         <f>TEXT(GG4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="GH5" s="10">
+        <v>火</v>
+      </c>
+      <c r="GH5" s="10" t="str">
         <f>TEXT(GH4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="GI5" s="10">
+        <v>水</v>
+      </c>
+      <c r="GI5" s="10" t="str">
         <f>TEXT(GI4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="GJ5" s="10">
+        <v>木</v>
+      </c>
+      <c r="GJ5" s="10" t="str">
         <f>TEXT(GJ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="GK5" s="10">
+        <v>金</v>
+      </c>
+      <c r="GK5" s="10" t="str">
         <f>TEXT(GK4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="GL5" s="10">
+        <v>土</v>
+      </c>
+      <c r="GL5" s="10" t="str">
         <f>TEXT(GL4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="GM5" s="10">
+        <v>日</v>
+      </c>
+      <c r="GM5" s="10" t="str">
         <f>TEXT(GM4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="GN5" s="10">
+        <v>月</v>
+      </c>
+      <c r="GN5" s="10" t="str">
         <f>TEXT(GN4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="GO5" s="10">
+        <v>火</v>
+      </c>
+      <c r="GO5" s="10" t="str">
         <f>TEXT(GO4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="GP5" s="10">
+        <v>水</v>
+      </c>
+      <c r="GP5" s="10" t="str">
         <f>TEXT(GP4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="GQ5" s="10">
+        <v>木</v>
+      </c>
+      <c r="GQ5" s="10" t="str">
         <f>TEXT(GQ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="GR5" s="10">
+        <v>金</v>
+      </c>
+      <c r="GR5" s="10" t="str">
         <f>TEXT(GR4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="GS5" s="10">
+        <v>土</v>
+      </c>
+      <c r="GS5" s="10" t="str">
         <f>TEXT(GS4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="GT5" s="10">
+        <v>日</v>
+      </c>
+      <c r="GT5" s="10" t="str">
         <f>TEXT(GT4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="GU5" s="10">
+        <v>月</v>
+      </c>
+      <c r="GU5" s="10" t="str">
         <f>TEXT(GU4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="GV5" s="10">
+        <v>火</v>
+      </c>
+      <c r="GV5" s="10" t="str">
         <f>TEXT(GV4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="GW5" s="10">
+        <v>水</v>
+      </c>
+      <c r="GW5" s="10" t="str">
         <f>TEXT(GW4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="GX5" s="10">
+        <v>木</v>
+      </c>
+      <c r="GX5" s="10" t="str">
         <f>TEXT(GX4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="GY5" s="10">
+        <v>金</v>
+      </c>
+      <c r="GY5" s="10" t="str">
         <f>TEXT(GY4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="GZ5" s="10">
+        <v>土</v>
+      </c>
+      <c r="GZ5" s="10" t="str">
         <f>TEXT(GZ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="HA5" s="10">
+        <v>日</v>
+      </c>
+      <c r="HA5" s="10" t="str">
         <f>TEXT(HA4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="HB5" s="10">
+        <v>月</v>
+      </c>
+      <c r="HB5" s="10" t="str">
         <f>TEXT(HB4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="HC5" s="10">
+        <v>火</v>
+      </c>
+      <c r="HC5" s="10" t="str">
         <f>TEXT(HC4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="HD5" s="10">
+        <v>水</v>
+      </c>
+      <c r="HD5" s="10" t="str">
         <f>TEXT(HD4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="HE5" s="10">
+        <v>木</v>
+      </c>
+      <c r="HE5" s="10" t="str">
         <f>TEXT(HE4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="HF5" s="10">
+        <v>金</v>
+      </c>
+      <c r="HF5" s="10" t="str">
         <f>TEXT(HF4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="HG5" s="10">
+        <v>土</v>
+      </c>
+      <c r="HG5" s="10" t="str">
         <f>TEXT(HG4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="HH5" s="10">
+        <v>日</v>
+      </c>
+      <c r="HH5" s="10" t="str">
         <f>TEXT(HH4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="HI5" s="10">
+        <v>月</v>
+      </c>
+      <c r="HI5" s="10" t="str">
         <f>TEXT(HI4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="HJ5" s="10">
+        <v>火</v>
+      </c>
+      <c r="HJ5" s="10" t="str">
         <f>TEXT(HJ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="HK5" s="10">
+        <v>水</v>
+      </c>
+      <c r="HK5" s="10" t="str">
         <f>TEXT(HK4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="HL5" s="10">
+        <v>木</v>
+      </c>
+      <c r="HL5" s="10" t="str">
         <f>TEXT(HL4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="HM5" s="10">
+        <v>金</v>
+      </c>
+      <c r="HM5" s="10" t="str">
         <f>TEXT(HM4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="HN5" s="10">
+        <v>土</v>
+      </c>
+      <c r="HN5" s="10" t="str">
         <f>TEXT(HN4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="HO5" s="10">
+        <v>日</v>
+      </c>
+      <c r="HO5" s="10" t="str">
         <f>TEXT(HO4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="HP5" s="10">
+        <v>月</v>
+      </c>
+      <c r="HP5" s="10" t="str">
         <f>TEXT(HP4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="HQ5" s="10">
+        <v>火</v>
+      </c>
+      <c r="HQ5" s="10" t="str">
         <f>TEXT(HQ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="HR5" s="10">
+        <v>水</v>
+      </c>
+      <c r="HR5" s="10" t="str">
         <f>TEXT(HR4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="HS5" s="10">
+        <v>木</v>
+      </c>
+      <c r="HS5" s="10" t="str">
         <f>TEXT(HS4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="HT5" s="10">
+        <v>金</v>
+      </c>
+      <c r="HT5" s="10" t="str">
         <f>TEXT(HT4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="HU5" s="10">
+        <v>土</v>
+      </c>
+      <c r="HU5" s="10" t="str">
         <f>TEXT(HU4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="HV5" s="10">
+        <v>日</v>
+      </c>
+      <c r="HV5" s="10" t="str">
         <f>TEXT(HV4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="HW5" s="10">
+        <v>月</v>
+      </c>
+      <c r="HW5" s="10" t="str">
         <f>TEXT(HW4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="HX5" s="10">
+        <v>火</v>
+      </c>
+      <c r="HX5" s="10" t="str">
         <f>TEXT(HX4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="HY5" s="10">
+        <v>水</v>
+      </c>
+      <c r="HY5" s="10" t="str">
         <f>TEXT(HY4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="HZ5" s="10">
+        <v>木</v>
+      </c>
+      <c r="HZ5" s="10" t="str">
         <f>TEXT(HZ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="IA5" s="10">
+        <v>金</v>
+      </c>
+      <c r="IA5" s="10" t="str">
         <f>TEXT(IA4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="IB5" s="10">
+        <v>土</v>
+      </c>
+      <c r="IB5" s="10" t="str">
         <f>TEXT(IB4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="IC5" s="10">
+        <v>日</v>
+      </c>
+      <c r="IC5" s="10" t="str">
         <f>TEXT(IC4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="ID5" s="10">
+        <v>月</v>
+      </c>
+      <c r="ID5" s="10" t="str">
         <f>TEXT(ID4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="IE5" s="10">
+        <v>火</v>
+      </c>
+      <c r="IE5" s="10" t="str">
         <f>TEXT(IE4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="IF5" s="10">
+        <v>水</v>
+      </c>
+      <c r="IF5" s="10" t="str">
         <f>TEXT(IF4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="IG5" s="10">
+        <v>木</v>
+      </c>
+      <c r="IG5" s="10" t="str">
         <f>TEXT(IG4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="IH5" s="10">
+        <v>金</v>
+      </c>
+      <c r="IH5" s="10" t="str">
         <f>TEXT(IH4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="II5" s="10">
+        <v>土</v>
+      </c>
+      <c r="II5" s="10" t="str">
         <f>TEXT(II4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="IJ5" s="10">
+        <v>日</v>
+      </c>
+      <c r="IJ5" s="10" t="str">
         <f>TEXT(IJ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="IK5" s="10">
+        <v>月</v>
+      </c>
+      <c r="IK5" s="10" t="str">
         <f>TEXT(IK4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="IL5" s="10">
+        <v>火</v>
+      </c>
+      <c r="IL5" s="10" t="str">
         <f>TEXT(IL4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="IM5" s="10">
+        <v>水</v>
+      </c>
+      <c r="IM5" s="10" t="str">
         <f>TEXT(IM4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="IN5" s="10">
+        <v>木</v>
+      </c>
+      <c r="IN5" s="10" t="str">
         <f>TEXT(IN4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="IO5" s="10">
+        <v>金</v>
+      </c>
+      <c r="IO5" s="10" t="str">
         <f>TEXT(IO4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="IP5" s="10">
+        <v>土</v>
+      </c>
+      <c r="IP5" s="10" t="str">
         <f>TEXT(IP4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="IQ5" s="10">
+        <v>日</v>
+      </c>
+      <c r="IQ5" s="10" t="str">
         <f>TEXT(IQ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="IR5" s="10">
+        <v>月</v>
+      </c>
+      <c r="IR5" s="10" t="str">
         <f>TEXT(IR4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="IS5" s="10">
+        <v>火</v>
+      </c>
+      <c r="IS5" s="10" t="str">
         <f>TEXT(IS4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="IT5" s="10">
+        <v>水</v>
+      </c>
+      <c r="IT5" s="10" t="str">
         <f>TEXT(IT4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="IU5" s="10">
+        <v>木</v>
+      </c>
+      <c r="IU5" s="10" t="str">
         <f>TEXT(IU4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="IV5" s="10">
+        <v>金</v>
+      </c>
+      <c r="IV5" s="10" t="str">
         <f>TEXT(IV4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="IW5" s="10">
+        <v>土</v>
+      </c>
+      <c r="IW5" s="10" t="str">
         <f>TEXT(IW4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="IX5" s="10">
+        <v>日</v>
+      </c>
+      <c r="IX5" s="10" t="str">
         <f>TEXT(IX4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="IY5" s="10">
+        <v>月</v>
+      </c>
+      <c r="IY5" s="10" t="str">
         <f>TEXT(IY4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="IZ5" s="10">
+        <v>火</v>
+      </c>
+      <c r="IZ5" s="10" t="str">
         <f>TEXT(IZ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="JA5" s="10">
+        <v>水</v>
+      </c>
+      <c r="JA5" s="10" t="str">
         <f>TEXT(JA4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="JB5" s="10">
+        <v>木</v>
+      </c>
+      <c r="JB5" s="10" t="str">
         <f>TEXT(JB4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="JC5" s="10">
+        <v>金</v>
+      </c>
+      <c r="JC5" s="10" t="str">
         <f>TEXT(JC4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="JD5" s="10">
+        <v>土</v>
+      </c>
+      <c r="JD5" s="10" t="str">
         <f>TEXT(JD4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="JE5" s="10">
+        <v>日</v>
+      </c>
+      <c r="JE5" s="10" t="str">
         <f>TEXT(JE4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="JF5" s="10">
+        <v>月</v>
+      </c>
+      <c r="JF5" s="10" t="str">
         <f>TEXT(JF4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="JG5" s="10">
+        <v>火</v>
+      </c>
+      <c r="JG5" s="10" t="str">
         <f>TEXT(JG4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="JH5" s="10">
+        <v>水</v>
+      </c>
+      <c r="JH5" s="10" t="str">
         <f>TEXT(JH4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="JI5" s="10">
+        <v>木</v>
+      </c>
+      <c r="JI5" s="10" t="str">
         <f>TEXT(JI4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="JJ5" s="10">
+        <v>金</v>
+      </c>
+      <c r="JJ5" s="10" t="str">
         <f>TEXT(JJ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="JK5" s="10">
+        <v>土</v>
+      </c>
+      <c r="JK5" s="10" t="str">
         <f>TEXT(JK4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="JL5" s="10">
+        <v>日</v>
+      </c>
+      <c r="JL5" s="10" t="str">
         <f>TEXT(JL4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="JM5" s="10">
+        <v>月</v>
+      </c>
+      <c r="JM5" s="10" t="str">
         <f>TEXT(JM4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="JN5" s="10">
+        <v>火</v>
+      </c>
+      <c r="JN5" s="10" t="str">
         <f>TEXT(JN4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="JO5" s="10">
+        <v>水</v>
+      </c>
+      <c r="JO5" s="10" t="str">
         <f>TEXT(JO4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="JP5" s="10">
+        <v>木</v>
+      </c>
+      <c r="JP5" s="10" t="str">
         <f>TEXT(JP4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="JQ5" s="10">
+        <v>金</v>
+      </c>
+      <c r="JQ5" s="10" t="str">
         <f>TEXT(JQ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="JR5" s="10">
+        <v>土</v>
+      </c>
+      <c r="JR5" s="10" t="str">
         <f>TEXT(JR4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="JS5" s="10">
+        <v>日</v>
+      </c>
+      <c r="JS5" s="10" t="str">
         <f>TEXT(JS4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="JT5" s="10">
+        <v>月</v>
+      </c>
+      <c r="JT5" s="10" t="str">
         <f>TEXT(JT4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="JU5" s="10">
+        <v>火</v>
+      </c>
+      <c r="JU5" s="10" t="str">
         <f>TEXT(JU4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="JV5" s="10">
+        <v>水</v>
+      </c>
+      <c r="JV5" s="10" t="str">
         <f>TEXT(JV4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="JW5" s="10">
+        <v>木</v>
+      </c>
+      <c r="JW5" s="10" t="str">
         <f>TEXT(JW4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="JX5" s="10">
+        <v>金</v>
+      </c>
+      <c r="JX5" s="10" t="str">
         <f>TEXT(JX4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="JY5" s="10">
+        <v>土</v>
+      </c>
+      <c r="JY5" s="10" t="str">
         <f>TEXT(JY4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="JZ5" s="10">
+        <v>日</v>
+      </c>
+      <c r="JZ5" s="10" t="str">
         <f>TEXT(JZ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="KA5" s="10">
+        <v>月</v>
+      </c>
+      <c r="KA5" s="10" t="str">
         <f>TEXT(KA4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="KB5" s="10">
+        <v>火</v>
+      </c>
+      <c r="KB5" s="10" t="str">
         <f>TEXT(KB4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="KC5" s="10">
+        <v>水</v>
+      </c>
+      <c r="KC5" s="10" t="str">
         <f>TEXT(KC4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="KD5" s="10">
+        <v>木</v>
+      </c>
+      <c r="KD5" s="10" t="str">
         <f>TEXT(KD4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="KE5" s="10">
+        <v>金</v>
+      </c>
+      <c r="KE5" s="10" t="str">
         <f>TEXT(KE4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="KF5" s="10">
+        <v>土</v>
+      </c>
+      <c r="KF5" s="10" t="str">
         <f>TEXT(KF4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="KG5" s="10">
+        <v>日</v>
+      </c>
+      <c r="KG5" s="10" t="str">
         <f>TEXT(KG4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="KH5" s="10">
+        <v>月</v>
+      </c>
+      <c r="KH5" s="10" t="str">
         <f>TEXT(KH4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="KI5" s="10">
+        <v>火</v>
+      </c>
+      <c r="KI5" s="10" t="str">
         <f>TEXT(KI4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="KJ5" s="10">
+        <v>水</v>
+      </c>
+      <c r="KJ5" s="10" t="str">
         <f>TEXT(KJ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="KK5" s="10">
+        <v>木</v>
+      </c>
+      <c r="KK5" s="10" t="str">
         <f>TEXT(KK4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="KL5" s="10">
+        <v>金</v>
+      </c>
+      <c r="KL5" s="10" t="str">
         <f>TEXT(KL4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="KM5" s="10">
+        <v>土</v>
+      </c>
+      <c r="KM5" s="10" t="str">
         <f>TEXT(KM4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="KN5" s="10">
+        <v>日</v>
+      </c>
+      <c r="KN5" s="10" t="str">
         <f>TEXT(KN4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="KO5" s="10">
+        <v>月</v>
+      </c>
+      <c r="KO5" s="10" t="str">
         <f>TEXT(KO4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="KP5" s="10">
+        <v>火</v>
+      </c>
+      <c r="KP5" s="10" t="str">
         <f>TEXT(KP4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="KQ5" s="10">
+        <v>水</v>
+      </c>
+      <c r="KQ5" s="10" t="str">
         <f>TEXT(KQ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="KR5" s="10">
+        <v>木</v>
+      </c>
+      <c r="KR5" s="10" t="str">
         <f>TEXT(KR4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="KS5" s="10">
+        <v>金</v>
+      </c>
+      <c r="KS5" s="10" t="str">
         <f>TEXT(KS4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="KT5" s="10">
+        <v>土</v>
+      </c>
+      <c r="KT5" s="10" t="str">
         <f>TEXT(KT4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="KU5" s="10">
+        <v>日</v>
+      </c>
+      <c r="KU5" s="10" t="str">
         <f>TEXT(KU4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="KV5" s="10">
+        <v>月</v>
+      </c>
+      <c r="KV5" s="10" t="str">
         <f>TEXT(KV4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="KW5" s="10">
+        <v>火</v>
+      </c>
+      <c r="KW5" s="10" t="str">
         <f>TEXT(KW4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="KX5" s="10">
+        <v>水</v>
+      </c>
+      <c r="KX5" s="10" t="str">
         <f>TEXT(KX4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="KY5" s="10">
+        <v>木</v>
+      </c>
+      <c r="KY5" s="10" t="str">
         <f>TEXT(KY4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="KZ5" s="10">
+        <v>金</v>
+      </c>
+      <c r="KZ5" s="10" t="str">
         <f>TEXT(KZ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="LA5" s="10">
+        <v>土</v>
+      </c>
+      <c r="LA5" s="10" t="str">
         <f>TEXT(LA4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="LB5" s="10">
+        <v>日</v>
+      </c>
+      <c r="LB5" s="10" t="str">
         <f>TEXT(LB4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="LC5" s="10">
+        <v>月</v>
+      </c>
+      <c r="LC5" s="10" t="str">
         <f>TEXT(LC4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="LD5" s="10">
+        <v>火</v>
+      </c>
+      <c r="LD5" s="10" t="str">
         <f>TEXT(LD4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="LE5" s="10">
+        <v>水</v>
+      </c>
+      <c r="LE5" s="10" t="str">
         <f>TEXT(LE4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="LF5" s="10">
+        <v>木</v>
+      </c>
+      <c r="LF5" s="10" t="str">
         <f>TEXT(LF4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="LG5" s="10">
+        <v>金</v>
+      </c>
+      <c r="LG5" s="10" t="str">
         <f>TEXT(LG4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="LH5" s="10">
+        <v>土</v>
+      </c>
+      <c r="LH5" s="10" t="str">
         <f>TEXT(LH4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="LI5" s="10">
+        <v>日</v>
+      </c>
+      <c r="LI5" s="10" t="str">
         <f>TEXT(LI4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="LJ5" s="10">
+        <v>月</v>
+      </c>
+      <c r="LJ5" s="10" t="str">
         <f>TEXT(LJ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="LK5" s="10">
+        <v>火</v>
+      </c>
+      <c r="LK5" s="10" t="str">
         <f>TEXT(LK4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="LL5" s="10">
+        <v>水</v>
+      </c>
+      <c r="LL5" s="10" t="str">
         <f>TEXT(LL4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="LM5" s="10">
+        <v>木</v>
+      </c>
+      <c r="LM5" s="10" t="str">
         <f>TEXT(LM4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="LN5" s="10">
+        <v>金</v>
+      </c>
+      <c r="LN5" s="10" t="str">
         <f>TEXT(LN4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="LO5" s="10">
+        <v>土</v>
+      </c>
+      <c r="LO5" s="10" t="str">
         <f>TEXT(LO4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="LP5" s="10">
+        <v>日</v>
+      </c>
+      <c r="LP5" s="10" t="str">
         <f>TEXT(LP4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="LQ5" s="10">
+        <v>月</v>
+      </c>
+      <c r="LQ5" s="10" t="str">
         <f>TEXT(LQ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="LR5" s="10">
+        <v>火</v>
+      </c>
+      <c r="LR5" s="10" t="str">
         <f>TEXT(LR4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="LS5" s="10">
+        <v>水</v>
+      </c>
+      <c r="LS5" s="10" t="str">
         <f>TEXT(LS4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="LT5" s="10">
+        <v>木</v>
+      </c>
+      <c r="LT5" s="10" t="str">
         <f>TEXT(LT4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="LU5" s="10">
+        <v>金</v>
+      </c>
+      <c r="LU5" s="10" t="str">
         <f>TEXT(LU4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="LV5" s="10">
+        <v>土</v>
+      </c>
+      <c r="LV5" s="10" t="str">
         <f>TEXT(LV4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="LW5" s="10">
+        <v>日</v>
+      </c>
+      <c r="LW5" s="10" t="str">
         <f>TEXT(LW4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="LX5" s="10">
+        <v>月</v>
+      </c>
+      <c r="LX5" s="10" t="str">
         <f>TEXT(LX4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="LY5" s="10">
+        <v>火</v>
+      </c>
+      <c r="LY5" s="10" t="str">
         <f>TEXT(LY4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="LZ5" s="10">
+        <v>水</v>
+      </c>
+      <c r="LZ5" s="10" t="str">
         <f>TEXT(LZ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="MA5" s="10">
+        <v>木</v>
+      </c>
+      <c r="MA5" s="10" t="str">
         <f>TEXT(MA4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="MB5" s="10">
+        <v>金</v>
+      </c>
+      <c r="MB5" s="10" t="str">
         <f>TEXT(MB4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="MC5" s="10">
+        <v>土</v>
+      </c>
+      <c r="MC5" s="10" t="str">
         <f>TEXT(MC4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="MD5" s="10">
+        <v>日</v>
+      </c>
+      <c r="MD5" s="10" t="str">
         <f>TEXT(MD4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="ME5" s="10">
+        <v>月</v>
+      </c>
+      <c r="ME5" s="10" t="str">
         <f>TEXT(ME4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="MF5" s="10">
+        <v>火</v>
+      </c>
+      <c r="MF5" s="10" t="str">
         <f>TEXT(MF4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="MG5" s="10">
+        <v>水</v>
+      </c>
+      <c r="MG5" s="10" t="str">
         <f>TEXT(MG4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="MH5" s="10">
+        <v>木</v>
+      </c>
+      <c r="MH5" s="10" t="str">
         <f>TEXT(MH4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="MI5" s="10">
+        <v>金</v>
+      </c>
+      <c r="MI5" s="10" t="str">
         <f>TEXT(MI4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="MJ5" s="10">
+        <v>土</v>
+      </c>
+      <c r="MJ5" s="10" t="str">
         <f>TEXT(MJ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="MK5" s="10">
+        <v>日</v>
+      </c>
+      <c r="MK5" s="10" t="str">
         <f>TEXT(MK4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="ML5" s="10">
+        <v>月</v>
+      </c>
+      <c r="ML5" s="10" t="str">
         <f>TEXT(ML4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="MM5" s="10">
+        <v>火</v>
+      </c>
+      <c r="MM5" s="10" t="str">
         <f>TEXT(MM4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="MN5" s="10">
+        <v>水</v>
+      </c>
+      <c r="MN5" s="10" t="str">
         <f>TEXT(MN4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="MO5" s="10">
+        <v>木</v>
+      </c>
+      <c r="MO5" s="10" t="str">
         <f>TEXT(MO4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="MP5" s="10">
+        <v>金</v>
+      </c>
+      <c r="MP5" s="10" t="str">
         <f>TEXT(MP4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="MQ5" s="10">
+        <v>土</v>
+      </c>
+      <c r="MQ5" s="10" t="str">
         <f>TEXT(MQ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="MR5" s="10">
+        <v>日</v>
+      </c>
+      <c r="MR5" s="10" t="str">
         <f>TEXT(MR4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="MS5" s="10">
+        <v>月</v>
+      </c>
+      <c r="MS5" s="10" t="str">
         <f>TEXT(MS4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="MT5" s="10">
+        <v>火</v>
+      </c>
+      <c r="MT5" s="10" t="str">
         <f>TEXT(MT4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="MU5" s="10">
+        <v>水</v>
+      </c>
+      <c r="MU5" s="10" t="str">
         <f>TEXT(MU4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="MV5" s="10">
+        <v>木</v>
+      </c>
+      <c r="MV5" s="10" t="str">
         <f>TEXT(MV4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="MW5" s="10">
+        <v>金</v>
+      </c>
+      <c r="MW5" s="10" t="str">
         <f>TEXT(MW4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="MX5" s="10">
+        <v>土</v>
+      </c>
+      <c r="MX5" s="10" t="str">
         <f>TEXT(MX4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="MY5" s="10">
+        <v>日</v>
+      </c>
+      <c r="MY5" s="10" t="str">
         <f>TEXT(MY4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="MZ5" s="10">
+        <v>月</v>
+      </c>
+      <c r="MZ5" s="10" t="str">
         <f>TEXT(MZ4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="NA5" s="10">
+        <v>火</v>
+      </c>
+      <c r="NA5" s="10" t="str">
         <f>TEXT(NA4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="NB5" s="10">
+        <v>水</v>
+      </c>
+      <c r="NB5" s="10" t="str">
         <f>TEXT(NB4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="NC5" s="10">
+        <v>木</v>
+      </c>
+      <c r="NC5" s="10" t="str">
         <f>TEXT(NC4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="ND5" s="10">
+        <v>金</v>
+      </c>
+      <c r="ND5" s="10" t="str">
         <f>TEXT(ND4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="NE5" s="10">
+        <v>土</v>
+      </c>
+      <c r="NE5" s="10" t="str">
         <f>TEXT(NE4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="NF5" s="10">
+        <v>日</v>
+      </c>
+      <c r="NF5" s="10" t="str">
         <f>TEXT(NF4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="NG5" s="10">
+        <v>月</v>
+      </c>
+      <c r="NG5" s="10" t="str">
         <f>TEXT(NG4,"aaa")</f>
-        <v/>
-      </c>
-      <c r="NH5" s="10">
+        <v>火</v>
+      </c>
+      <c r="NH5" s="10" t="str">
         <f>TEXT(NH4,"aaa")</f>
-        <v/>
+        <v>水</v>
       </c>
     </row>
-    <row r="6" ht="14" customHeight="1">
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="11" t="n">
         <v>1</v>
       </c>
       <c r="B6" s="12" t="n"/>
       <c r="C6" s="12" t="n"/>
-      <c r="D6" s="20" t="n"/>
-      <c r="E6" s="20" t="n"/>
-      <c r="F6" s="20" t="n"/>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="13" t="n"/>
       <c r="G6" s="14" t="inlineStr">
         <is>
           <t>予定</t>
@@ -5810,13 +5753,7 @@
       <c r="NG6" s="15" t="n"/>
       <c r="NH6" s="15" t="n"/>
     </row>
-    <row r="7" ht="14" customHeight="1">
-      <c r="A7" s="19" t="n"/>
-      <c r="B7" s="19" t="n"/>
-      <c r="C7" s="19" t="n"/>
-      <c r="D7" s="19" t="n"/>
-      <c r="E7" s="19" t="n"/>
-      <c r="F7" s="19" t="n"/>
+    <row r="7" ht="15" customHeight="1">
       <c r="G7" s="14" t="inlineStr">
         <is>
           <t>実績</t>
@@ -6188,15 +6125,15 @@
       <c r="NG7" s="15" t="n"/>
       <c r="NH7" s="15" t="n"/>
     </row>
-    <row r="8" ht="14" customHeight="1">
+    <row r="8" ht="15" customHeight="1">
       <c r="A8" s="11" t="n">
         <v>2</v>
       </c>
       <c r="B8" s="12" t="n"/>
       <c r="C8" s="12" t="n"/>
-      <c r="D8" s="20" t="n"/>
-      <c r="E8" s="20" t="n"/>
-      <c r="F8" s="20" t="n"/>
+      <c r="D8" s="13" t="n"/>
+      <c r="E8" s="13" t="n"/>
+      <c r="F8" s="13" t="n"/>
       <c r="G8" s="14" t="inlineStr">
         <is>
           <t>予定</t>
@@ -6568,13 +6505,7 @@
       <c r="NG8" s="15" t="n"/>
       <c r="NH8" s="15" t="n"/>
     </row>
-    <row r="9" ht="14" customHeight="1">
-      <c r="A9" s="19" t="n"/>
-      <c r="B9" s="19" t="n"/>
-      <c r="C9" s="19" t="n"/>
-      <c r="D9" s="19" t="n"/>
-      <c r="E9" s="19" t="n"/>
-      <c r="F9" s="19" t="n"/>
+    <row r="9" ht="15" customHeight="1">
       <c r="G9" s="14" t="inlineStr">
         <is>
           <t>実績</t>
@@ -6946,15 +6877,15 @@
       <c r="NG9" s="15" t="n"/>
       <c r="NH9" s="15" t="n"/>
     </row>
-    <row r="10" ht="14" customHeight="1">
+    <row r="10" ht="15" customHeight="1">
       <c r="A10" s="11" t="n">
         <v>3</v>
       </c>
       <c r="B10" s="12" t="n"/>
       <c r="C10" s="12" t="n"/>
-      <c r="D10" s="20" t="n"/>
-      <c r="E10" s="20" t="n"/>
-      <c r="F10" s="20" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
       <c r="G10" s="14" t="inlineStr">
         <is>
           <t>予定</t>
@@ -7326,13 +7257,7 @@
       <c r="NG10" s="15" t="n"/>
       <c r="NH10" s="15" t="n"/>
     </row>
-    <row r="11" ht="14" customHeight="1">
-      <c r="A11" s="19" t="n"/>
-      <c r="B11" s="19" t="n"/>
-      <c r="C11" s="19" t="n"/>
-      <c r="D11" s="19" t="n"/>
-      <c r="E11" s="19" t="n"/>
-      <c r="F11" s="19" t="n"/>
+    <row r="11" ht="15" customHeight="1">
       <c r="G11" s="14" t="inlineStr">
         <is>
           <t>実績</t>
@@ -7704,15 +7629,15 @@
       <c r="NG11" s="15" t="n"/>
       <c r="NH11" s="15" t="n"/>
     </row>
-    <row r="12" ht="14" customHeight="1">
+    <row r="12" ht="15" customHeight="1">
       <c r="A12" s="11" t="n">
         <v>4</v>
       </c>
       <c r="B12" s="12" t="n"/>
       <c r="C12" s="12" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="20" t="n"/>
-      <c r="F12" s="20" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
       <c r="G12" s="14" t="inlineStr">
         <is>
           <t>予定</t>
@@ -8084,13 +8009,7 @@
       <c r="NG12" s="15" t="n"/>
       <c r="NH12" s="15" t="n"/>
     </row>
-    <row r="13" ht="14" customHeight="1">
-      <c r="A13" s="19" t="n"/>
-      <c r="B13" s="19" t="n"/>
-      <c r="C13" s="19" t="n"/>
-      <c r="D13" s="19" t="n"/>
-      <c r="E13" s="19" t="n"/>
-      <c r="F13" s="19" t="n"/>
+    <row r="13" ht="15" customHeight="1">
       <c r="G13" s="14" t="inlineStr">
         <is>
           <t>実績</t>
@@ -8462,15 +8381,15 @@
       <c r="NG13" s="15" t="n"/>
       <c r="NH13" s="15" t="n"/>
     </row>
-    <row r="14" ht="14" customHeight="1">
+    <row r="14" ht="15" customHeight="1">
       <c r="A14" s="11" t="n">
         <v>5</v>
       </c>
       <c r="B14" s="12" t="n"/>
       <c r="C14" s="12" t="n"/>
-      <c r="D14" s="20" t="n"/>
-      <c r="E14" s="20" t="n"/>
-      <c r="F14" s="20" t="n"/>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
       <c r="G14" s="14" t="inlineStr">
         <is>
           <t>予定</t>
@@ -8842,13 +8761,7 @@
       <c r="NG14" s="15" t="n"/>
       <c r="NH14" s="15" t="n"/>
     </row>
-    <row r="15" ht="14" customHeight="1">
-      <c r="A15" s="19" t="n"/>
-      <c r="B15" s="19" t="n"/>
-      <c r="C15" s="19" t="n"/>
-      <c r="D15" s="19" t="n"/>
-      <c r="E15" s="19" t="n"/>
-      <c r="F15" s="19" t="n"/>
+    <row r="15" ht="15" customHeight="1">
       <c r="G15" s="14" t="inlineStr">
         <is>
           <t>実績</t>
@@ -9220,15 +9133,15 @@
       <c r="NG15" s="15" t="n"/>
       <c r="NH15" s="15" t="n"/>
     </row>
-    <row r="16" ht="14" customHeight="1">
+    <row r="16" ht="15" customHeight="1">
       <c r="A16" s="11" t="n">
         <v>6</v>
       </c>
       <c r="B16" s="12" t="n"/>
       <c r="C16" s="12" t="n"/>
-      <c r="D16" s="20" t="n"/>
-      <c r="E16" s="20" t="n"/>
-      <c r="F16" s="20" t="n"/>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
       <c r="G16" s="14" t="inlineStr">
         <is>
           <t>予定</t>
@@ -9600,13 +9513,7 @@
       <c r="NG16" s="15" t="n"/>
       <c r="NH16" s="15" t="n"/>
     </row>
-    <row r="17" ht="14" customHeight="1">
-      <c r="A17" s="19" t="n"/>
-      <c r="B17" s="19" t="n"/>
-      <c r="C17" s="19" t="n"/>
-      <c r="D17" s="19" t="n"/>
-      <c r="E17" s="19" t="n"/>
-      <c r="F17" s="19" t="n"/>
+    <row r="17" ht="15" customHeight="1">
       <c r="G17" s="14" t="inlineStr">
         <is>
           <t>実績</t>
@@ -9978,15 +9885,15 @@
       <c r="NG17" s="15" t="n"/>
       <c r="NH17" s="15" t="n"/>
     </row>
-    <row r="18" ht="14" customHeight="1">
+    <row r="18" ht="15" customHeight="1">
       <c r="A18" s="11" t="n">
         <v>7</v>
       </c>
       <c r="B18" s="12" t="n"/>
       <c r="C18" s="12" t="n"/>
-      <c r="D18" s="20" t="n"/>
-      <c r="E18" s="20" t="n"/>
-      <c r="F18" s="20" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
           <t>予定</t>
@@ -10358,13 +10265,7 @@
       <c r="NG18" s="15" t="n"/>
       <c r="NH18" s="15" t="n"/>
     </row>
-    <row r="19" ht="14" customHeight="1">
-      <c r="A19" s="19" t="n"/>
-      <c r="B19" s="19" t="n"/>
-      <c r="C19" s="19" t="n"/>
-      <c r="D19" s="19" t="n"/>
-      <c r="E19" s="19" t="n"/>
-      <c r="F19" s="19" t="n"/>
+    <row r="19" ht="15" customHeight="1">
       <c r="G19" s="14" t="inlineStr">
         <is>
           <t>実績</t>
@@ -10736,15 +10637,15 @@
       <c r="NG19" s="15" t="n"/>
       <c r="NH19" s="15" t="n"/>
     </row>
-    <row r="20" ht="14" customHeight="1">
+    <row r="20" ht="15" customHeight="1">
       <c r="A20" s="11" t="n">
         <v>8</v>
       </c>
       <c r="B20" s="12" t="n"/>
       <c r="C20" s="12" t="n"/>
-      <c r="D20" s="20" t="n"/>
-      <c r="E20" s="20" t="n"/>
-      <c r="F20" s="20" t="n"/>
+      <c r="D20" s="13" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="13" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
           <t>予定</t>
@@ -11116,13 +11017,7 @@
       <c r="NG20" s="15" t="n"/>
       <c r="NH20" s="15" t="n"/>
     </row>
-    <row r="21" ht="14" customHeight="1">
-      <c r="A21" s="19" t="n"/>
-      <c r="B21" s="19" t="n"/>
-      <c r="C21" s="19" t="n"/>
-      <c r="D21" s="19" t="n"/>
-      <c r="E21" s="19" t="n"/>
-      <c r="F21" s="19" t="n"/>
+    <row r="21" ht="15" customHeight="1">
       <c r="G21" s="14" t="inlineStr">
         <is>
           <t>実績</t>
@@ -11494,15 +11389,15 @@
       <c r="NG21" s="15" t="n"/>
       <c r="NH21" s="15" t="n"/>
     </row>
-    <row r="22" ht="14" customHeight="1">
+    <row r="22" ht="15" customHeight="1">
       <c r="A22" s="11" t="n">
         <v>9</v>
       </c>
       <c r="B22" s="12" t="n"/>
       <c r="C22" s="12" t="n"/>
-      <c r="D22" s="20" t="n"/>
-      <c r="E22" s="20" t="n"/>
-      <c r="F22" s="20" t="n"/>
+      <c r="D22" s="13" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="13" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
           <t>予定</t>
@@ -11874,13 +11769,7 @@
       <c r="NG22" s="15" t="n"/>
       <c r="NH22" s="15" t="n"/>
     </row>
-    <row r="23" ht="14" customHeight="1">
-      <c r="A23" s="19" t="n"/>
-      <c r="B23" s="19" t="n"/>
-      <c r="C23" s="19" t="n"/>
-      <c r="D23" s="19" t="n"/>
-      <c r="E23" s="19" t="n"/>
-      <c r="F23" s="19" t="n"/>
+    <row r="23" ht="15" customHeight="1">
       <c r="G23" s="14" t="inlineStr">
         <is>
           <t>実績</t>
@@ -12252,15 +12141,15 @@
       <c r="NG23" s="15" t="n"/>
       <c r="NH23" s="15" t="n"/>
     </row>
-    <row r="24" ht="14" customHeight="1">
+    <row r="24" ht="15" customHeight="1">
       <c r="A24" s="11" t="n">
         <v>10</v>
       </c>
       <c r="B24" s="12" t="n"/>
       <c r="C24" s="12" t="n"/>
-      <c r="D24" s="20" t="n"/>
-      <c r="E24" s="20" t="n"/>
-      <c r="F24" s="20" t="n"/>
+      <c r="D24" s="13" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="13" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
           <t>予定</t>
@@ -12632,13 +12521,7 @@
       <c r="NG24" s="15" t="n"/>
       <c r="NH24" s="15" t="n"/>
     </row>
-    <row r="25" ht="14" customHeight="1">
-      <c r="A25" s="19" t="n"/>
-      <c r="B25" s="19" t="n"/>
-      <c r="C25" s="19" t="n"/>
-      <c r="D25" s="19" t="n"/>
-      <c r="E25" s="19" t="n"/>
-      <c r="F25" s="19" t="n"/>
+    <row r="25" ht="15" customHeight="1">
       <c r="G25" s="14" t="inlineStr">
         <is>
           <t>実績</t>
@@ -13010,15 +12893,15 @@
       <c r="NG25" s="15" t="n"/>
       <c r="NH25" s="15" t="n"/>
     </row>
-    <row r="26" ht="14" customHeight="1">
+    <row r="26" ht="15" customHeight="1">
       <c r="A26" s="11" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="12" t="n"/>
       <c r="C26" s="12" t="n"/>
-      <c r="D26" s="20" t="n"/>
-      <c r="E26" s="20" t="n"/>
-      <c r="F26" s="20" t="n"/>
+      <c r="D26" s="13" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="13" t="n"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
           <t>予定</t>
@@ -13390,13 +13273,7 @@
       <c r="NG26" s="15" t="n"/>
       <c r="NH26" s="15" t="n"/>
     </row>
-    <row r="27" ht="14" customHeight="1">
-      <c r="A27" s="19" t="n"/>
-      <c r="B27" s="19" t="n"/>
-      <c r="C27" s="19" t="n"/>
-      <c r="D27" s="19" t="n"/>
-      <c r="E27" s="19" t="n"/>
-      <c r="F27" s="19" t="n"/>
+    <row r="27" ht="15" customHeight="1">
       <c r="G27" s="14" t="inlineStr">
         <is>
           <t>実績</t>
@@ -13768,15 +13645,15 @@
       <c r="NG27" s="15" t="n"/>
       <c r="NH27" s="15" t="n"/>
     </row>
-    <row r="28" ht="14" customHeight="1">
+    <row r="28" ht="15" customHeight="1">
       <c r="A28" s="11" t="n">
         <v>12</v>
       </c>
       <c r="B28" s="12" t="n"/>
       <c r="C28" s="12" t="n"/>
-      <c r="D28" s="20" t="n"/>
-      <c r="E28" s="20" t="n"/>
-      <c r="F28" s="20" t="n"/>
+      <c r="D28" s="13" t="n"/>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="13" t="n"/>
       <c r="G28" s="14" t="inlineStr">
         <is>
           <t>予定</t>
@@ -14148,13 +14025,7 @@
       <c r="NG28" s="15" t="n"/>
       <c r="NH28" s="15" t="n"/>
     </row>
-    <row r="29" ht="14" customHeight="1">
-      <c r="A29" s="19" t="n"/>
-      <c r="B29" s="19" t="n"/>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="19" t="n"/>
-      <c r="E29" s="19" t="n"/>
-      <c r="F29" s="19" t="n"/>
+    <row r="29" ht="15" customHeight="1">
       <c r="G29" s="14" t="inlineStr">
         <is>
           <t>実績</t>
@@ -14526,15 +14397,15 @@
       <c r="NG29" s="15" t="n"/>
       <c r="NH29" s="15" t="n"/>
     </row>
-    <row r="30" ht="14" customHeight="1">
+    <row r="30" ht="15" customHeight="1">
       <c r="A30" s="11" t="n">
         <v>13</v>
       </c>
       <c r="B30" s="12" t="n"/>
       <c r="C30" s="12" t="n"/>
-      <c r="D30" s="20" t="n"/>
-      <c r="E30" s="20" t="n"/>
-      <c r="F30" s="20" t="n"/>
+      <c r="D30" s="13" t="n"/>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="13" t="n"/>
       <c r="G30" s="14" t="inlineStr">
         <is>
           <t>予定</t>
@@ -14906,13 +14777,7 @@
       <c r="NG30" s="15" t="n"/>
       <c r="NH30" s="15" t="n"/>
     </row>
-    <row r="31" ht="14" customHeight="1">
-      <c r="A31" s="19" t="n"/>
-      <c r="B31" s="19" t="n"/>
-      <c r="C31" s="19" t="n"/>
-      <c r="D31" s="19" t="n"/>
-      <c r="E31" s="19" t="n"/>
-      <c r="F31" s="19" t="n"/>
+    <row r="31" ht="15" customHeight="1">
       <c r="G31" s="14" t="inlineStr">
         <is>
           <t>実績</t>
@@ -15284,15 +15149,15 @@
       <c r="NG31" s="15" t="n"/>
       <c r="NH31" s="15" t="n"/>
     </row>
-    <row r="32" ht="14" customHeight="1">
+    <row r="32" ht="15" customHeight="1">
       <c r="A32" s="11" t="n">
         <v>14</v>
       </c>
       <c r="B32" s="12" t="n"/>
       <c r="C32" s="12" t="n"/>
-      <c r="D32" s="20" t="n"/>
-      <c r="E32" s="20" t="n"/>
-      <c r="F32" s="20" t="n"/>
+      <c r="D32" s="13" t="n"/>
+      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="13" t="n"/>
       <c r="G32" s="14" t="inlineStr">
         <is>
           <t>予定</t>
@@ -15664,13 +15529,7 @@
       <c r="NG32" s="15" t="n"/>
       <c r="NH32" s="15" t="n"/>
     </row>
-    <row r="33" ht="14" customHeight="1">
-      <c r="A33" s="19" t="n"/>
-      <c r="B33" s="19" t="n"/>
-      <c r="C33" s="19" t="n"/>
-      <c r="D33" s="19" t="n"/>
-      <c r="E33" s="19" t="n"/>
-      <c r="F33" s="19" t="n"/>
+    <row r="33" ht="15" customHeight="1">
       <c r="G33" s="14" t="inlineStr">
         <is>
           <t>実績</t>
@@ -16042,15 +15901,15 @@
       <c r="NG33" s="15" t="n"/>
       <c r="NH33" s="15" t="n"/>
     </row>
-    <row r="34" ht="14" customHeight="1">
+    <row r="34" ht="15" customHeight="1">
       <c r="A34" s="11" t="n">
         <v>15</v>
       </c>
       <c r="B34" s="12" t="n"/>
       <c r="C34" s="12" t="n"/>
-      <c r="D34" s="20" t="n"/>
-      <c r="E34" s="20" t="n"/>
-      <c r="F34" s="20" t="n"/>
+      <c r="D34" s="13" t="n"/>
+      <c r="E34" s="13" t="n"/>
+      <c r="F34" s="13" t="n"/>
       <c r="G34" s="14" t="inlineStr">
         <is>
           <t>予定</t>
@@ -16422,13 +16281,7 @@
       <c r="NG34" s="15" t="n"/>
       <c r="NH34" s="15" t="n"/>
     </row>
-    <row r="35" ht="14" customHeight="1">
-      <c r="A35" s="19" t="n"/>
-      <c r="B35" s="19" t="n"/>
-      <c r="C35" s="19" t="n"/>
-      <c r="D35" s="19" t="n"/>
-      <c r="E35" s="19" t="n"/>
-      <c r="F35" s="19" t="n"/>
+    <row r="35" ht="15" customHeight="1">
       <c r="G35" s="14" t="inlineStr">
         <is>
           <t>実績</t>
@@ -16800,15 +16653,15 @@
       <c r="NG35" s="15" t="n"/>
       <c r="NH35" s="15" t="n"/>
     </row>
-    <row r="36" ht="14" customHeight="1">
+    <row r="36" ht="15" customHeight="1">
       <c r="A36" s="11" t="n">
         <v>16</v>
       </c>
       <c r="B36" s="12" t="n"/>
       <c r="C36" s="12" t="n"/>
-      <c r="D36" s="20" t="n"/>
-      <c r="E36" s="20" t="n"/>
-      <c r="F36" s="20" t="n"/>
+      <c r="D36" s="13" t="n"/>
+      <c r="E36" s="13" t="n"/>
+      <c r="F36" s="13" t="n"/>
       <c r="G36" s="14" t="inlineStr">
         <is>
           <t>予定</t>
@@ -17180,13 +17033,7 @@
       <c r="NG36" s="15" t="n"/>
       <c r="NH36" s="15" t="n"/>
     </row>
-    <row r="37" ht="14" customHeight="1">
-      <c r="A37" s="19" t="n"/>
-      <c r="B37" s="19" t="n"/>
-      <c r="C37" s="19" t="n"/>
-      <c r="D37" s="19" t="n"/>
-      <c r="E37" s="19" t="n"/>
-      <c r="F37" s="19" t="n"/>
+    <row r="37" ht="15" customHeight="1">
       <c r="G37" s="14" t="inlineStr">
         <is>
           <t>実績</t>
@@ -17558,15 +17405,15 @@
       <c r="NG37" s="15" t="n"/>
       <c r="NH37" s="15" t="n"/>
     </row>
-    <row r="38" ht="14" customHeight="1">
+    <row r="38" ht="15" customHeight="1">
       <c r="A38" s="11" t="n">
         <v>17</v>
       </c>
       <c r="B38" s="12" t="n"/>
       <c r="C38" s="12" t="n"/>
-      <c r="D38" s="20" t="n"/>
-      <c r="E38" s="20" t="n"/>
-      <c r="F38" s="20" t="n"/>
+      <c r="D38" s="13" t="n"/>
+      <c r="E38" s="13" t="n"/>
+      <c r="F38" s="13" t="n"/>
       <c r="G38" s="14" t="inlineStr">
         <is>
           <t>予定</t>
@@ -17938,13 +17785,7 @@
       <c r="NG38" s="15" t="n"/>
       <c r="NH38" s="15" t="n"/>
     </row>
-    <row r="39" ht="14" customHeight="1">
-      <c r="A39" s="19" t="n"/>
-      <c r="B39" s="19" t="n"/>
-      <c r="C39" s="19" t="n"/>
-      <c r="D39" s="19" t="n"/>
-      <c r="E39" s="19" t="n"/>
-      <c r="F39" s="19" t="n"/>
+    <row r="39" ht="15" customHeight="1">
       <c r="G39" s="14" t="inlineStr">
         <is>
           <t>実績</t>
@@ -18316,15 +18157,15 @@
       <c r="NG39" s="15" t="n"/>
       <c r="NH39" s="15" t="n"/>
     </row>
-    <row r="40" ht="14" customHeight="1">
+    <row r="40" ht="15" customHeight="1">
       <c r="A40" s="11" t="n">
         <v>18</v>
       </c>
       <c r="B40" s="12" t="n"/>
       <c r="C40" s="12" t="n"/>
-      <c r="D40" s="20" t="n"/>
-      <c r="E40" s="20" t="n"/>
-      <c r="F40" s="20" t="n"/>
+      <c r="D40" s="13" t="n"/>
+      <c r="E40" s="13" t="n"/>
+      <c r="F40" s="13" t="n"/>
       <c r="G40" s="14" t="inlineStr">
         <is>
           <t>予定</t>
@@ -18696,13 +18537,7 @@
       <c r="NG40" s="15" t="n"/>
       <c r="NH40" s="15" t="n"/>
     </row>
-    <row r="41" ht="14" customHeight="1">
-      <c r="A41" s="19" t="n"/>
-      <c r="B41" s="19" t="n"/>
-      <c r="C41" s="19" t="n"/>
-      <c r="D41" s="19" t="n"/>
-      <c r="E41" s="19" t="n"/>
-      <c r="F41" s="19" t="n"/>
+    <row r="41" ht="15" customHeight="1">
       <c r="G41" s="14" t="inlineStr">
         <is>
           <t>実績</t>
@@ -19074,15 +18909,15 @@
       <c r="NG41" s="15" t="n"/>
       <c r="NH41" s="15" t="n"/>
     </row>
-    <row r="42" ht="14" customHeight="1">
+    <row r="42" ht="15" customHeight="1">
       <c r="A42" s="11" t="n">
         <v>19</v>
       </c>
       <c r="B42" s="12" t="n"/>
       <c r="C42" s="12" t="n"/>
-      <c r="D42" s="20" t="n"/>
-      <c r="E42" s="20" t="n"/>
-      <c r="F42" s="20" t="n"/>
+      <c r="D42" s="13" t="n"/>
+      <c r="E42" s="13" t="n"/>
+      <c r="F42" s="13" t="n"/>
       <c r="G42" s="14" t="inlineStr">
         <is>
           <t>予定</t>
@@ -19454,13 +19289,7 @@
       <c r="NG42" s="15" t="n"/>
       <c r="NH42" s="15" t="n"/>
     </row>
-    <row r="43" ht="14" customHeight="1">
-      <c r="A43" s="19" t="n"/>
-      <c r="B43" s="19" t="n"/>
-      <c r="C43" s="19" t="n"/>
-      <c r="D43" s="19" t="n"/>
-      <c r="E43" s="19" t="n"/>
-      <c r="F43" s="19" t="n"/>
+    <row r="43" ht="15" customHeight="1">
       <c r="G43" s="14" t="inlineStr">
         <is>
           <t>実績</t>
@@ -19832,15 +19661,15 @@
       <c r="NG43" s="15" t="n"/>
       <c r="NH43" s="15" t="n"/>
     </row>
-    <row r="44" ht="14" customHeight="1">
+    <row r="44" ht="15" customHeight="1">
       <c r="A44" s="11" t="n">
         <v>20</v>
       </c>
       <c r="B44" s="12" t="n"/>
       <c r="C44" s="12" t="n"/>
-      <c r="D44" s="20" t="n"/>
-      <c r="E44" s="20" t="n"/>
-      <c r="F44" s="20" t="n"/>
+      <c r="D44" s="13" t="n"/>
+      <c r="E44" s="13" t="n"/>
+      <c r="F44" s="13" t="n"/>
       <c r="G44" s="14" t="inlineStr">
         <is>
           <t>予定</t>
@@ -20212,13 +20041,7 @@
       <c r="NG44" s="15" t="n"/>
       <c r="NH44" s="15" t="n"/>
     </row>
-    <row r="45" ht="14" customHeight="1">
-      <c r="A45" s="19" t="n"/>
-      <c r="B45" s="19" t="n"/>
-      <c r="C45" s="19" t="n"/>
-      <c r="D45" s="19" t="n"/>
-      <c r="E45" s="19" t="n"/>
-      <c r="F45" s="19" t="n"/>
+    <row r="45" ht="15" customHeight="1">
       <c r="G45" s="14" t="inlineStr">
         <is>
           <t>実績</t>

--- a/スケジュール_365日.xlsx
+++ b/スケジュール_365日.xlsx
@@ -70,21 +70,25 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002E5395"/>
+        <bgColor rgb="002E5395"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="005BA72B"/>
+        <bgColor rgb="005BA72B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00404040"/>
+        <bgColor rgb="00404040"/>
       </patternFill>
     </fill>
   </fills>
@@ -164,6 +168,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="002E5395"/>
+          <bgColor rgb="002E5395"/>
         </patternFill>
       </fill>
     </dxf>
@@ -171,6 +176,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="005BA72B"/>
+          <bgColor rgb="005BA72B"/>
         </patternFill>
       </fill>
     </dxf>
@@ -178,6 +184,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00E4E7F0"/>
+          <bgColor rgb="00E4E7F0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -553,371 +560,371 @@
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="2.6" customWidth="1" min="8" max="8"/>
-    <col width="2.6" customWidth="1" min="9" max="9"/>
-    <col width="2.6" customWidth="1" min="10" max="10"/>
-    <col width="2.6" customWidth="1" min="11" max="11"/>
-    <col width="2.6" customWidth="1" min="12" max="12"/>
-    <col width="2.6" customWidth="1" min="13" max="13"/>
-    <col width="2.6" customWidth="1" min="14" max="14"/>
-    <col width="2.6" customWidth="1" min="15" max="15"/>
-    <col width="2.6" customWidth="1" min="16" max="16"/>
-    <col width="2.6" customWidth="1" min="17" max="17"/>
-    <col width="2.6" customWidth="1" min="18" max="18"/>
-    <col width="2.6" customWidth="1" min="19" max="19"/>
-    <col width="2.6" customWidth="1" min="20" max="20"/>
-    <col width="2.6" customWidth="1" min="21" max="21"/>
-    <col width="2.6" customWidth="1" min="22" max="22"/>
-    <col width="2.6" customWidth="1" min="23" max="23"/>
-    <col width="2.6" customWidth="1" min="24" max="24"/>
-    <col width="2.6" customWidth="1" min="25" max="25"/>
-    <col width="2.6" customWidth="1" min="26" max="26"/>
-    <col width="2.6" customWidth="1" min="27" max="27"/>
-    <col width="2.6" customWidth="1" min="28" max="28"/>
-    <col width="2.6" customWidth="1" min="29" max="29"/>
-    <col width="2.6" customWidth="1" min="30" max="30"/>
-    <col width="2.6" customWidth="1" min="31" max="31"/>
-    <col width="2.6" customWidth="1" min="32" max="32"/>
-    <col width="2.6" customWidth="1" min="33" max="33"/>
-    <col width="2.6" customWidth="1" min="34" max="34"/>
-    <col width="2.6" customWidth="1" min="35" max="35"/>
-    <col width="2.6" customWidth="1" min="36" max="36"/>
-    <col width="2.6" customWidth="1" min="37" max="37"/>
-    <col width="2.6" customWidth="1" min="38" max="38"/>
-    <col width="2.6" customWidth="1" min="39" max="39"/>
-    <col width="2.6" customWidth="1" min="40" max="40"/>
-    <col width="2.6" customWidth="1" min="41" max="41"/>
-    <col width="2.6" customWidth="1" min="42" max="42"/>
-    <col width="2.6" customWidth="1" min="43" max="43"/>
-    <col width="2.6" customWidth="1" min="44" max="44"/>
-    <col width="2.6" customWidth="1" min="45" max="45"/>
-    <col width="2.6" customWidth="1" min="46" max="46"/>
-    <col width="2.6" customWidth="1" min="47" max="47"/>
-    <col width="2.6" customWidth="1" min="48" max="48"/>
-    <col width="2.6" customWidth="1" min="49" max="49"/>
-    <col width="2.6" customWidth="1" min="50" max="50"/>
-    <col width="2.6" customWidth="1" min="51" max="51"/>
-    <col width="2.6" customWidth="1" min="52" max="52"/>
-    <col width="2.6" customWidth="1" min="53" max="53"/>
-    <col width="2.6" customWidth="1" min="54" max="54"/>
-    <col width="2.6" customWidth="1" min="55" max="55"/>
-    <col width="2.6" customWidth="1" min="56" max="56"/>
-    <col width="2.6" customWidth="1" min="57" max="57"/>
-    <col width="2.6" customWidth="1" min="58" max="58"/>
-    <col width="2.6" customWidth="1" min="59" max="59"/>
-    <col width="2.6" customWidth="1" min="60" max="60"/>
-    <col width="2.6" customWidth="1" min="61" max="61"/>
-    <col width="2.6" customWidth="1" min="62" max="62"/>
-    <col width="2.6" customWidth="1" min="63" max="63"/>
-    <col width="2.6" customWidth="1" min="64" max="64"/>
-    <col width="2.6" customWidth="1" min="65" max="65"/>
-    <col width="2.6" customWidth="1" min="66" max="66"/>
-    <col width="2.6" customWidth="1" min="67" max="67"/>
-    <col width="2.6" customWidth="1" min="68" max="68"/>
-    <col width="2.6" customWidth="1" min="69" max="69"/>
-    <col width="2.6" customWidth="1" min="70" max="70"/>
-    <col width="2.6" customWidth="1" min="71" max="71"/>
-    <col width="2.6" customWidth="1" min="72" max="72"/>
-    <col width="2.6" customWidth="1" min="73" max="73"/>
-    <col width="2.6" customWidth="1" min="74" max="74"/>
-    <col width="2.6" customWidth="1" min="75" max="75"/>
-    <col width="2.6" customWidth="1" min="76" max="76"/>
-    <col width="2.6" customWidth="1" min="77" max="77"/>
-    <col width="2.6" customWidth="1" min="78" max="78"/>
-    <col width="2.6" customWidth="1" min="79" max="79"/>
-    <col width="2.6" customWidth="1" min="80" max="80"/>
-    <col width="2.6" customWidth="1" min="81" max="81"/>
-    <col width="2.6" customWidth="1" min="82" max="82"/>
-    <col width="2.6" customWidth="1" min="83" max="83"/>
-    <col width="2.6" customWidth="1" min="84" max="84"/>
-    <col width="2.6" customWidth="1" min="85" max="85"/>
-    <col width="2.6" customWidth="1" min="86" max="86"/>
-    <col width="2.6" customWidth="1" min="87" max="87"/>
-    <col width="2.6" customWidth="1" min="88" max="88"/>
-    <col width="2.6" customWidth="1" min="89" max="89"/>
-    <col width="2.6" customWidth="1" min="90" max="90"/>
-    <col width="2.6" customWidth="1" min="91" max="91"/>
-    <col width="2.6" customWidth="1" min="92" max="92"/>
-    <col width="2.6" customWidth="1" min="93" max="93"/>
-    <col width="2.6" customWidth="1" min="94" max="94"/>
-    <col width="2.6" customWidth="1" min="95" max="95"/>
-    <col width="2.6" customWidth="1" min="96" max="96"/>
-    <col width="2.6" customWidth="1" min="97" max="97"/>
-    <col width="2.6" customWidth="1" min="98" max="98"/>
-    <col width="2.6" customWidth="1" min="99" max="99"/>
-    <col width="2.6" customWidth="1" min="100" max="100"/>
-    <col width="2.6" customWidth="1" min="101" max="101"/>
-    <col width="2.6" customWidth="1" min="102" max="102"/>
-    <col width="2.6" customWidth="1" min="103" max="103"/>
-    <col width="2.6" customWidth="1" min="104" max="104"/>
-    <col width="2.6" customWidth="1" min="105" max="105"/>
-    <col width="2.6" customWidth="1" min="106" max="106"/>
-    <col width="2.6" customWidth="1" min="107" max="107"/>
-    <col width="2.6" customWidth="1" min="108" max="108"/>
-    <col width="2.6" customWidth="1" min="109" max="109"/>
-    <col width="2.6" customWidth="1" min="110" max="110"/>
-    <col width="2.6" customWidth="1" min="111" max="111"/>
-    <col width="2.6" customWidth="1" min="112" max="112"/>
-    <col width="2.6" customWidth="1" min="113" max="113"/>
-    <col width="2.6" customWidth="1" min="114" max="114"/>
-    <col width="2.6" customWidth="1" min="115" max="115"/>
-    <col width="2.6" customWidth="1" min="116" max="116"/>
-    <col width="2.6" customWidth="1" min="117" max="117"/>
-    <col width="2.6" customWidth="1" min="118" max="118"/>
-    <col width="2.6" customWidth="1" min="119" max="119"/>
-    <col width="2.6" customWidth="1" min="120" max="120"/>
-    <col width="2.6" customWidth="1" min="121" max="121"/>
-    <col width="2.6" customWidth="1" min="122" max="122"/>
-    <col width="2.6" customWidth="1" min="123" max="123"/>
-    <col width="2.6" customWidth="1" min="124" max="124"/>
-    <col width="2.6" customWidth="1" min="125" max="125"/>
-    <col width="2.6" customWidth="1" min="126" max="126"/>
-    <col width="2.6" customWidth="1" min="127" max="127"/>
-    <col width="2.6" customWidth="1" min="128" max="128"/>
-    <col width="2.6" customWidth="1" min="129" max="129"/>
-    <col width="2.6" customWidth="1" min="130" max="130"/>
-    <col width="2.6" customWidth="1" min="131" max="131"/>
-    <col width="2.6" customWidth="1" min="132" max="132"/>
-    <col width="2.6" customWidth="1" min="133" max="133"/>
-    <col width="2.6" customWidth="1" min="134" max="134"/>
-    <col width="2.6" customWidth="1" min="135" max="135"/>
-    <col width="2.6" customWidth="1" min="136" max="136"/>
-    <col width="2.6" customWidth="1" min="137" max="137"/>
-    <col width="2.6" customWidth="1" min="138" max="138"/>
-    <col width="2.6" customWidth="1" min="139" max="139"/>
-    <col width="2.6" customWidth="1" min="140" max="140"/>
-    <col width="2.6" customWidth="1" min="141" max="141"/>
-    <col width="2.6" customWidth="1" min="142" max="142"/>
-    <col width="2.6" customWidth="1" min="143" max="143"/>
-    <col width="2.6" customWidth="1" min="144" max="144"/>
-    <col width="2.6" customWidth="1" min="145" max="145"/>
-    <col width="2.6" customWidth="1" min="146" max="146"/>
-    <col width="2.6" customWidth="1" min="147" max="147"/>
-    <col width="2.6" customWidth="1" min="148" max="148"/>
-    <col width="2.6" customWidth="1" min="149" max="149"/>
-    <col width="2.6" customWidth="1" min="150" max="150"/>
-    <col width="2.6" customWidth="1" min="151" max="151"/>
-    <col width="2.6" customWidth="1" min="152" max="152"/>
-    <col width="2.6" customWidth="1" min="153" max="153"/>
-    <col width="2.6" customWidth="1" min="154" max="154"/>
-    <col width="2.6" customWidth="1" min="155" max="155"/>
-    <col width="2.6" customWidth="1" min="156" max="156"/>
-    <col width="2.6" customWidth="1" min="157" max="157"/>
-    <col width="2.6" customWidth="1" min="158" max="158"/>
-    <col width="2.6" customWidth="1" min="159" max="159"/>
-    <col width="2.6" customWidth="1" min="160" max="160"/>
-    <col width="2.6" customWidth="1" min="161" max="161"/>
-    <col width="2.6" customWidth="1" min="162" max="162"/>
-    <col width="2.6" customWidth="1" min="163" max="163"/>
-    <col width="2.6" customWidth="1" min="164" max="164"/>
-    <col width="2.6" customWidth="1" min="165" max="165"/>
-    <col width="2.6" customWidth="1" min="166" max="166"/>
-    <col width="2.6" customWidth="1" min="167" max="167"/>
-    <col width="2.6" customWidth="1" min="168" max="168"/>
-    <col width="2.6" customWidth="1" min="169" max="169"/>
-    <col width="2.6" customWidth="1" min="170" max="170"/>
-    <col width="2.6" customWidth="1" min="171" max="171"/>
-    <col width="2.6" customWidth="1" min="172" max="172"/>
-    <col width="2.6" customWidth="1" min="173" max="173"/>
-    <col width="2.6" customWidth="1" min="174" max="174"/>
-    <col width="2.6" customWidth="1" min="175" max="175"/>
-    <col width="2.6" customWidth="1" min="176" max="176"/>
-    <col width="2.6" customWidth="1" min="177" max="177"/>
-    <col width="2.6" customWidth="1" min="178" max="178"/>
-    <col width="2.6" customWidth="1" min="179" max="179"/>
-    <col width="2.6" customWidth="1" min="180" max="180"/>
-    <col width="2.6" customWidth="1" min="181" max="181"/>
-    <col width="2.6" customWidth="1" min="182" max="182"/>
-    <col width="2.6" customWidth="1" min="183" max="183"/>
-    <col width="2.6" customWidth="1" min="184" max="184"/>
-    <col width="2.6" customWidth="1" min="185" max="185"/>
-    <col width="2.6" customWidth="1" min="186" max="186"/>
-    <col width="2.6" customWidth="1" min="187" max="187"/>
-    <col width="2.6" customWidth="1" min="188" max="188"/>
-    <col width="2.6" customWidth="1" min="189" max="189"/>
-    <col width="2.6" customWidth="1" min="190" max="190"/>
-    <col width="2.6" customWidth="1" min="191" max="191"/>
-    <col width="2.6" customWidth="1" min="192" max="192"/>
-    <col width="2.6" customWidth="1" min="193" max="193"/>
-    <col width="2.6" customWidth="1" min="194" max="194"/>
-    <col width="2.6" customWidth="1" min="195" max="195"/>
-    <col width="2.6" customWidth="1" min="196" max="196"/>
-    <col width="2.6" customWidth="1" min="197" max="197"/>
-    <col width="2.6" customWidth="1" min="198" max="198"/>
-    <col width="2.6" customWidth="1" min="199" max="199"/>
-    <col width="2.6" customWidth="1" min="200" max="200"/>
-    <col width="2.6" customWidth="1" min="201" max="201"/>
-    <col width="2.6" customWidth="1" min="202" max="202"/>
-    <col width="2.6" customWidth="1" min="203" max="203"/>
-    <col width="2.6" customWidth="1" min="204" max="204"/>
-    <col width="2.6" customWidth="1" min="205" max="205"/>
-    <col width="2.6" customWidth="1" min="206" max="206"/>
-    <col width="2.6" customWidth="1" min="207" max="207"/>
-    <col width="2.6" customWidth="1" min="208" max="208"/>
-    <col width="2.6" customWidth="1" min="209" max="209"/>
-    <col width="2.6" customWidth="1" min="210" max="210"/>
-    <col width="2.6" customWidth="1" min="211" max="211"/>
-    <col width="2.6" customWidth="1" min="212" max="212"/>
-    <col width="2.6" customWidth="1" min="213" max="213"/>
-    <col width="2.6" customWidth="1" min="214" max="214"/>
-    <col width="2.6" customWidth="1" min="215" max="215"/>
-    <col width="2.6" customWidth="1" min="216" max="216"/>
-    <col width="2.6" customWidth="1" min="217" max="217"/>
-    <col width="2.6" customWidth="1" min="218" max="218"/>
-    <col width="2.6" customWidth="1" min="219" max="219"/>
-    <col width="2.6" customWidth="1" min="220" max="220"/>
-    <col width="2.6" customWidth="1" min="221" max="221"/>
-    <col width="2.6" customWidth="1" min="222" max="222"/>
-    <col width="2.6" customWidth="1" min="223" max="223"/>
-    <col width="2.6" customWidth="1" min="224" max="224"/>
-    <col width="2.6" customWidth="1" min="225" max="225"/>
-    <col width="2.6" customWidth="1" min="226" max="226"/>
-    <col width="2.6" customWidth="1" min="227" max="227"/>
-    <col width="2.6" customWidth="1" min="228" max="228"/>
-    <col width="2.6" customWidth="1" min="229" max="229"/>
-    <col width="2.6" customWidth="1" min="230" max="230"/>
-    <col width="2.6" customWidth="1" min="231" max="231"/>
-    <col width="2.6" customWidth="1" min="232" max="232"/>
-    <col width="2.6" customWidth="1" min="233" max="233"/>
-    <col width="2.6" customWidth="1" min="234" max="234"/>
-    <col width="2.6" customWidth="1" min="235" max="235"/>
-    <col width="2.6" customWidth="1" min="236" max="236"/>
-    <col width="2.6" customWidth="1" min="237" max="237"/>
-    <col width="2.6" customWidth="1" min="238" max="238"/>
-    <col width="2.6" customWidth="1" min="239" max="239"/>
-    <col width="2.6" customWidth="1" min="240" max="240"/>
-    <col width="2.6" customWidth="1" min="241" max="241"/>
-    <col width="2.6" customWidth="1" min="242" max="242"/>
-    <col width="2.6" customWidth="1" min="243" max="243"/>
-    <col width="2.6" customWidth="1" min="244" max="244"/>
-    <col width="2.6" customWidth="1" min="245" max="245"/>
-    <col width="2.6" customWidth="1" min="246" max="246"/>
-    <col width="2.6" customWidth="1" min="247" max="247"/>
-    <col width="2.6" customWidth="1" min="248" max="248"/>
-    <col width="2.6" customWidth="1" min="249" max="249"/>
-    <col width="2.6" customWidth="1" min="250" max="250"/>
-    <col width="2.6" customWidth="1" min="251" max="251"/>
-    <col width="2.6" customWidth="1" min="252" max="252"/>
-    <col width="2.6" customWidth="1" min="253" max="253"/>
-    <col width="2.6" customWidth="1" min="254" max="254"/>
-    <col width="2.6" customWidth="1" min="255" max="255"/>
-    <col width="2.6" customWidth="1" min="256" max="256"/>
-    <col width="2.6" customWidth="1" min="257" max="257"/>
-    <col width="2.6" customWidth="1" min="258" max="258"/>
-    <col width="2.6" customWidth="1" min="259" max="259"/>
-    <col width="2.6" customWidth="1" min="260" max="260"/>
-    <col width="2.6" customWidth="1" min="261" max="261"/>
-    <col width="2.6" customWidth="1" min="262" max="262"/>
-    <col width="2.6" customWidth="1" min="263" max="263"/>
-    <col width="2.6" customWidth="1" min="264" max="264"/>
-    <col width="2.6" customWidth="1" min="265" max="265"/>
-    <col width="2.6" customWidth="1" min="266" max="266"/>
-    <col width="2.6" customWidth="1" min="267" max="267"/>
-    <col width="2.6" customWidth="1" min="268" max="268"/>
-    <col width="2.6" customWidth="1" min="269" max="269"/>
-    <col width="2.6" customWidth="1" min="270" max="270"/>
-    <col width="2.6" customWidth="1" min="271" max="271"/>
-    <col width="2.6" customWidth="1" min="272" max="272"/>
-    <col width="2.6" customWidth="1" min="273" max="273"/>
-    <col width="2.6" customWidth="1" min="274" max="274"/>
-    <col width="2.6" customWidth="1" min="275" max="275"/>
-    <col width="2.6" customWidth="1" min="276" max="276"/>
-    <col width="2.6" customWidth="1" min="277" max="277"/>
-    <col width="2.6" customWidth="1" min="278" max="278"/>
-    <col width="2.6" customWidth="1" min="279" max="279"/>
-    <col width="2.6" customWidth="1" min="280" max="280"/>
-    <col width="2.6" customWidth="1" min="281" max="281"/>
-    <col width="2.6" customWidth="1" min="282" max="282"/>
-    <col width="2.6" customWidth="1" min="283" max="283"/>
-    <col width="2.6" customWidth="1" min="284" max="284"/>
-    <col width="2.6" customWidth="1" min="285" max="285"/>
-    <col width="2.6" customWidth="1" min="286" max="286"/>
-    <col width="2.6" customWidth="1" min="287" max="287"/>
-    <col width="2.6" customWidth="1" min="288" max="288"/>
-    <col width="2.6" customWidth="1" min="289" max="289"/>
-    <col width="2.6" customWidth="1" min="290" max="290"/>
-    <col width="2.6" customWidth="1" min="291" max="291"/>
-    <col width="2.6" customWidth="1" min="292" max="292"/>
-    <col width="2.6" customWidth="1" min="293" max="293"/>
-    <col width="2.6" customWidth="1" min="294" max="294"/>
-    <col width="2.6" customWidth="1" min="295" max="295"/>
-    <col width="2.6" customWidth="1" min="296" max="296"/>
-    <col width="2.6" customWidth="1" min="297" max="297"/>
-    <col width="2.6" customWidth="1" min="298" max="298"/>
-    <col width="2.6" customWidth="1" min="299" max="299"/>
-    <col width="2.6" customWidth="1" min="300" max="300"/>
-    <col width="2.6" customWidth="1" min="301" max="301"/>
-    <col width="2.6" customWidth="1" min="302" max="302"/>
-    <col width="2.6" customWidth="1" min="303" max="303"/>
-    <col width="2.6" customWidth="1" min="304" max="304"/>
-    <col width="2.6" customWidth="1" min="305" max="305"/>
-    <col width="2.6" customWidth="1" min="306" max="306"/>
-    <col width="2.6" customWidth="1" min="307" max="307"/>
-    <col width="2.6" customWidth="1" min="308" max="308"/>
-    <col width="2.6" customWidth="1" min="309" max="309"/>
-    <col width="2.6" customWidth="1" min="310" max="310"/>
-    <col width="2.6" customWidth="1" min="311" max="311"/>
-    <col width="2.6" customWidth="1" min="312" max="312"/>
-    <col width="2.6" customWidth="1" min="313" max="313"/>
-    <col width="2.6" customWidth="1" min="314" max="314"/>
-    <col width="2.6" customWidth="1" min="315" max="315"/>
-    <col width="2.6" customWidth="1" min="316" max="316"/>
-    <col width="2.6" customWidth="1" min="317" max="317"/>
-    <col width="2.6" customWidth="1" min="318" max="318"/>
-    <col width="2.6" customWidth="1" min="319" max="319"/>
-    <col width="2.6" customWidth="1" min="320" max="320"/>
-    <col width="2.6" customWidth="1" min="321" max="321"/>
-    <col width="2.6" customWidth="1" min="322" max="322"/>
-    <col width="2.6" customWidth="1" min="323" max="323"/>
-    <col width="2.6" customWidth="1" min="324" max="324"/>
-    <col width="2.6" customWidth="1" min="325" max="325"/>
-    <col width="2.6" customWidth="1" min="326" max="326"/>
-    <col width="2.6" customWidth="1" min="327" max="327"/>
-    <col width="2.6" customWidth="1" min="328" max="328"/>
-    <col width="2.6" customWidth="1" min="329" max="329"/>
-    <col width="2.6" customWidth="1" min="330" max="330"/>
-    <col width="2.6" customWidth="1" min="331" max="331"/>
-    <col width="2.6" customWidth="1" min="332" max="332"/>
-    <col width="2.6" customWidth="1" min="333" max="333"/>
-    <col width="2.6" customWidth="1" min="334" max="334"/>
-    <col width="2.6" customWidth="1" min="335" max="335"/>
-    <col width="2.6" customWidth="1" min="336" max="336"/>
-    <col width="2.6" customWidth="1" min="337" max="337"/>
-    <col width="2.6" customWidth="1" min="338" max="338"/>
-    <col width="2.6" customWidth="1" min="339" max="339"/>
-    <col width="2.6" customWidth="1" min="340" max="340"/>
-    <col width="2.6" customWidth="1" min="341" max="341"/>
-    <col width="2.6" customWidth="1" min="342" max="342"/>
-    <col width="2.6" customWidth="1" min="343" max="343"/>
-    <col width="2.6" customWidth="1" min="344" max="344"/>
-    <col width="2.6" customWidth="1" min="345" max="345"/>
-    <col width="2.6" customWidth="1" min="346" max="346"/>
-    <col width="2.6" customWidth="1" min="347" max="347"/>
-    <col width="2.6" customWidth="1" min="348" max="348"/>
-    <col width="2.6" customWidth="1" min="349" max="349"/>
-    <col width="2.6" customWidth="1" min="350" max="350"/>
-    <col width="2.6" customWidth="1" min="351" max="351"/>
-    <col width="2.6" customWidth="1" min="352" max="352"/>
-    <col width="2.6" customWidth="1" min="353" max="353"/>
-    <col width="2.6" customWidth="1" min="354" max="354"/>
-    <col width="2.6" customWidth="1" min="355" max="355"/>
-    <col width="2.6" customWidth="1" min="356" max="356"/>
-    <col width="2.6" customWidth="1" min="357" max="357"/>
-    <col width="2.6" customWidth="1" min="358" max="358"/>
-    <col width="2.6" customWidth="1" min="359" max="359"/>
-    <col width="2.6" customWidth="1" min="360" max="360"/>
-    <col width="2.6" customWidth="1" min="361" max="361"/>
-    <col width="2.6" customWidth="1" min="362" max="362"/>
-    <col width="2.6" customWidth="1" min="363" max="363"/>
-    <col width="2.6" customWidth="1" min="364" max="364"/>
-    <col width="2.6" customWidth="1" min="365" max="365"/>
-    <col width="2.6" customWidth="1" min="366" max="366"/>
-    <col width="2.6" customWidth="1" min="367" max="367"/>
-    <col width="2.6" customWidth="1" min="368" max="368"/>
-    <col width="2.6" customWidth="1" min="369" max="369"/>
-    <col width="2.6" customWidth="1" min="370" max="370"/>
-    <col width="2.6" customWidth="1" min="371" max="371"/>
-    <col width="2.6" customWidth="1" min="372" max="372"/>
+    <col width="3.4" customWidth="1" min="8" max="8"/>
+    <col width="3.4" customWidth="1" min="9" max="9"/>
+    <col width="3.4" customWidth="1" min="10" max="10"/>
+    <col width="3.4" customWidth="1" min="11" max="11"/>
+    <col width="3.4" customWidth="1" min="12" max="12"/>
+    <col width="3.4" customWidth="1" min="13" max="13"/>
+    <col width="3.4" customWidth="1" min="14" max="14"/>
+    <col width="3.4" customWidth="1" min="15" max="15"/>
+    <col width="3.4" customWidth="1" min="16" max="16"/>
+    <col width="3.4" customWidth="1" min="17" max="17"/>
+    <col width="3.4" customWidth="1" min="18" max="18"/>
+    <col width="3.4" customWidth="1" min="19" max="19"/>
+    <col width="3.4" customWidth="1" min="20" max="20"/>
+    <col width="3.4" customWidth="1" min="21" max="21"/>
+    <col width="3.4" customWidth="1" min="22" max="22"/>
+    <col width="3.4" customWidth="1" min="23" max="23"/>
+    <col width="3.4" customWidth="1" min="24" max="24"/>
+    <col width="3.4" customWidth="1" min="25" max="25"/>
+    <col width="3.4" customWidth="1" min="26" max="26"/>
+    <col width="3.4" customWidth="1" min="27" max="27"/>
+    <col width="3.4" customWidth="1" min="28" max="28"/>
+    <col width="3.4" customWidth="1" min="29" max="29"/>
+    <col width="3.4" customWidth="1" min="30" max="30"/>
+    <col width="3.4" customWidth="1" min="31" max="31"/>
+    <col width="3.4" customWidth="1" min="32" max="32"/>
+    <col width="3.4" customWidth="1" min="33" max="33"/>
+    <col width="3.4" customWidth="1" min="34" max="34"/>
+    <col width="3.4" customWidth="1" min="35" max="35"/>
+    <col width="3.4" customWidth="1" min="36" max="36"/>
+    <col width="3.4" customWidth="1" min="37" max="37"/>
+    <col width="3.4" customWidth="1" min="38" max="38"/>
+    <col width="3.4" customWidth="1" min="39" max="39"/>
+    <col width="3.4" customWidth="1" min="40" max="40"/>
+    <col width="3.4" customWidth="1" min="41" max="41"/>
+    <col width="3.4" customWidth="1" min="42" max="42"/>
+    <col width="3.4" customWidth="1" min="43" max="43"/>
+    <col width="3.4" customWidth="1" min="44" max="44"/>
+    <col width="3.4" customWidth="1" min="45" max="45"/>
+    <col width="3.4" customWidth="1" min="46" max="46"/>
+    <col width="3.4" customWidth="1" min="47" max="47"/>
+    <col width="3.4" customWidth="1" min="48" max="48"/>
+    <col width="3.4" customWidth="1" min="49" max="49"/>
+    <col width="3.4" customWidth="1" min="50" max="50"/>
+    <col width="3.4" customWidth="1" min="51" max="51"/>
+    <col width="3.4" customWidth="1" min="52" max="52"/>
+    <col width="3.4" customWidth="1" min="53" max="53"/>
+    <col width="3.4" customWidth="1" min="54" max="54"/>
+    <col width="3.4" customWidth="1" min="55" max="55"/>
+    <col width="3.4" customWidth="1" min="56" max="56"/>
+    <col width="3.4" customWidth="1" min="57" max="57"/>
+    <col width="3.4" customWidth="1" min="58" max="58"/>
+    <col width="3.4" customWidth="1" min="59" max="59"/>
+    <col width="3.4" customWidth="1" min="60" max="60"/>
+    <col width="3.4" customWidth="1" min="61" max="61"/>
+    <col width="3.4" customWidth="1" min="62" max="62"/>
+    <col width="3.4" customWidth="1" min="63" max="63"/>
+    <col width="3.4" customWidth="1" min="64" max="64"/>
+    <col width="3.4" customWidth="1" min="65" max="65"/>
+    <col width="3.4" customWidth="1" min="66" max="66"/>
+    <col width="3.4" customWidth="1" min="67" max="67"/>
+    <col width="3.4" customWidth="1" min="68" max="68"/>
+    <col width="3.4" customWidth="1" min="69" max="69"/>
+    <col width="3.4" customWidth="1" min="70" max="70"/>
+    <col width="3.4" customWidth="1" min="71" max="71"/>
+    <col width="3.4" customWidth="1" min="72" max="72"/>
+    <col width="3.4" customWidth="1" min="73" max="73"/>
+    <col width="3.4" customWidth="1" min="74" max="74"/>
+    <col width="3.4" customWidth="1" min="75" max="75"/>
+    <col width="3.4" customWidth="1" min="76" max="76"/>
+    <col width="3.4" customWidth="1" min="77" max="77"/>
+    <col width="3.4" customWidth="1" min="78" max="78"/>
+    <col width="3.4" customWidth="1" min="79" max="79"/>
+    <col width="3.4" customWidth="1" min="80" max="80"/>
+    <col width="3.4" customWidth="1" min="81" max="81"/>
+    <col width="3.4" customWidth="1" min="82" max="82"/>
+    <col width="3.4" customWidth="1" min="83" max="83"/>
+    <col width="3.4" customWidth="1" min="84" max="84"/>
+    <col width="3.4" customWidth="1" min="85" max="85"/>
+    <col width="3.4" customWidth="1" min="86" max="86"/>
+    <col width="3.4" customWidth="1" min="87" max="87"/>
+    <col width="3.4" customWidth="1" min="88" max="88"/>
+    <col width="3.4" customWidth="1" min="89" max="89"/>
+    <col width="3.4" customWidth="1" min="90" max="90"/>
+    <col width="3.4" customWidth="1" min="91" max="91"/>
+    <col width="3.4" customWidth="1" min="92" max="92"/>
+    <col width="3.4" customWidth="1" min="93" max="93"/>
+    <col width="3.4" customWidth="1" min="94" max="94"/>
+    <col width="3.4" customWidth="1" min="95" max="95"/>
+    <col width="3.4" customWidth="1" min="96" max="96"/>
+    <col width="3.4" customWidth="1" min="97" max="97"/>
+    <col width="3.4" customWidth="1" min="98" max="98"/>
+    <col width="3.4" customWidth="1" min="99" max="99"/>
+    <col width="3.4" customWidth="1" min="100" max="100"/>
+    <col width="3.4" customWidth="1" min="101" max="101"/>
+    <col width="3.4" customWidth="1" min="102" max="102"/>
+    <col width="3.4" customWidth="1" min="103" max="103"/>
+    <col width="3.4" customWidth="1" min="104" max="104"/>
+    <col width="3.4" customWidth="1" min="105" max="105"/>
+    <col width="3.4" customWidth="1" min="106" max="106"/>
+    <col width="3.4" customWidth="1" min="107" max="107"/>
+    <col width="3.4" customWidth="1" min="108" max="108"/>
+    <col width="3.4" customWidth="1" min="109" max="109"/>
+    <col width="3.4" customWidth="1" min="110" max="110"/>
+    <col width="3.4" customWidth="1" min="111" max="111"/>
+    <col width="3.4" customWidth="1" min="112" max="112"/>
+    <col width="3.4" customWidth="1" min="113" max="113"/>
+    <col width="3.4" customWidth="1" min="114" max="114"/>
+    <col width="3.4" customWidth="1" min="115" max="115"/>
+    <col width="3.4" customWidth="1" min="116" max="116"/>
+    <col width="3.4" customWidth="1" min="117" max="117"/>
+    <col width="3.4" customWidth="1" min="118" max="118"/>
+    <col width="3.4" customWidth="1" min="119" max="119"/>
+    <col width="3.4" customWidth="1" min="120" max="120"/>
+    <col width="3.4" customWidth="1" min="121" max="121"/>
+    <col width="3.4" customWidth="1" min="122" max="122"/>
+    <col width="3.4" customWidth="1" min="123" max="123"/>
+    <col width="3.4" customWidth="1" min="124" max="124"/>
+    <col width="3.4" customWidth="1" min="125" max="125"/>
+    <col width="3.4" customWidth="1" min="126" max="126"/>
+    <col width="3.4" customWidth="1" min="127" max="127"/>
+    <col width="3.4" customWidth="1" min="128" max="128"/>
+    <col width="3.4" customWidth="1" min="129" max="129"/>
+    <col width="3.4" customWidth="1" min="130" max="130"/>
+    <col width="3.4" customWidth="1" min="131" max="131"/>
+    <col width="3.4" customWidth="1" min="132" max="132"/>
+    <col width="3.4" customWidth="1" min="133" max="133"/>
+    <col width="3.4" customWidth="1" min="134" max="134"/>
+    <col width="3.4" customWidth="1" min="135" max="135"/>
+    <col width="3.4" customWidth="1" min="136" max="136"/>
+    <col width="3.4" customWidth="1" min="137" max="137"/>
+    <col width="3.4" customWidth="1" min="138" max="138"/>
+    <col width="3.4" customWidth="1" min="139" max="139"/>
+    <col width="3.4" customWidth="1" min="140" max="140"/>
+    <col width="3.4" customWidth="1" min="141" max="141"/>
+    <col width="3.4" customWidth="1" min="142" max="142"/>
+    <col width="3.4" customWidth="1" min="143" max="143"/>
+    <col width="3.4" customWidth="1" min="144" max="144"/>
+    <col width="3.4" customWidth="1" min="145" max="145"/>
+    <col width="3.4" customWidth="1" min="146" max="146"/>
+    <col width="3.4" customWidth="1" min="147" max="147"/>
+    <col width="3.4" customWidth="1" min="148" max="148"/>
+    <col width="3.4" customWidth="1" min="149" max="149"/>
+    <col width="3.4" customWidth="1" min="150" max="150"/>
+    <col width="3.4" customWidth="1" min="151" max="151"/>
+    <col width="3.4" customWidth="1" min="152" max="152"/>
+    <col width="3.4" customWidth="1" min="153" max="153"/>
+    <col width="3.4" customWidth="1" min="154" max="154"/>
+    <col width="3.4" customWidth="1" min="155" max="155"/>
+    <col width="3.4" customWidth="1" min="156" max="156"/>
+    <col width="3.4" customWidth="1" min="157" max="157"/>
+    <col width="3.4" customWidth="1" min="158" max="158"/>
+    <col width="3.4" customWidth="1" min="159" max="159"/>
+    <col width="3.4" customWidth="1" min="160" max="160"/>
+    <col width="3.4" customWidth="1" min="161" max="161"/>
+    <col width="3.4" customWidth="1" min="162" max="162"/>
+    <col width="3.4" customWidth="1" min="163" max="163"/>
+    <col width="3.4" customWidth="1" min="164" max="164"/>
+    <col width="3.4" customWidth="1" min="165" max="165"/>
+    <col width="3.4" customWidth="1" min="166" max="166"/>
+    <col width="3.4" customWidth="1" min="167" max="167"/>
+    <col width="3.4" customWidth="1" min="168" max="168"/>
+    <col width="3.4" customWidth="1" min="169" max="169"/>
+    <col width="3.4" customWidth="1" min="170" max="170"/>
+    <col width="3.4" customWidth="1" min="171" max="171"/>
+    <col width="3.4" customWidth="1" min="172" max="172"/>
+    <col width="3.4" customWidth="1" min="173" max="173"/>
+    <col width="3.4" customWidth="1" min="174" max="174"/>
+    <col width="3.4" customWidth="1" min="175" max="175"/>
+    <col width="3.4" customWidth="1" min="176" max="176"/>
+    <col width="3.4" customWidth="1" min="177" max="177"/>
+    <col width="3.4" customWidth="1" min="178" max="178"/>
+    <col width="3.4" customWidth="1" min="179" max="179"/>
+    <col width="3.4" customWidth="1" min="180" max="180"/>
+    <col width="3.4" customWidth="1" min="181" max="181"/>
+    <col width="3.4" customWidth="1" min="182" max="182"/>
+    <col width="3.4" customWidth="1" min="183" max="183"/>
+    <col width="3.4" customWidth="1" min="184" max="184"/>
+    <col width="3.4" customWidth="1" min="185" max="185"/>
+    <col width="3.4" customWidth="1" min="186" max="186"/>
+    <col width="3.4" customWidth="1" min="187" max="187"/>
+    <col width="3.4" customWidth="1" min="188" max="188"/>
+    <col width="3.4" customWidth="1" min="189" max="189"/>
+    <col width="3.4" customWidth="1" min="190" max="190"/>
+    <col width="3.4" customWidth="1" min="191" max="191"/>
+    <col width="3.4" customWidth="1" min="192" max="192"/>
+    <col width="3.4" customWidth="1" min="193" max="193"/>
+    <col width="3.4" customWidth="1" min="194" max="194"/>
+    <col width="3.4" customWidth="1" min="195" max="195"/>
+    <col width="3.4" customWidth="1" min="196" max="196"/>
+    <col width="3.4" customWidth="1" min="197" max="197"/>
+    <col width="3.4" customWidth="1" min="198" max="198"/>
+    <col width="3.4" customWidth="1" min="199" max="199"/>
+    <col width="3.4" customWidth="1" min="200" max="200"/>
+    <col width="3.4" customWidth="1" min="201" max="201"/>
+    <col width="3.4" customWidth="1" min="202" max="202"/>
+    <col width="3.4" customWidth="1" min="203" max="203"/>
+    <col width="3.4" customWidth="1" min="204" max="204"/>
+    <col width="3.4" customWidth="1" min="205" max="205"/>
+    <col width="3.4" customWidth="1" min="206" max="206"/>
+    <col width="3.4" customWidth="1" min="207" max="207"/>
+    <col width="3.4" customWidth="1" min="208" max="208"/>
+    <col width="3.4" customWidth="1" min="209" max="209"/>
+    <col width="3.4" customWidth="1" min="210" max="210"/>
+    <col width="3.4" customWidth="1" min="211" max="211"/>
+    <col width="3.4" customWidth="1" min="212" max="212"/>
+    <col width="3.4" customWidth="1" min="213" max="213"/>
+    <col width="3.4" customWidth="1" min="214" max="214"/>
+    <col width="3.4" customWidth="1" min="215" max="215"/>
+    <col width="3.4" customWidth="1" min="216" max="216"/>
+    <col width="3.4" customWidth="1" min="217" max="217"/>
+    <col width="3.4" customWidth="1" min="218" max="218"/>
+    <col width="3.4" customWidth="1" min="219" max="219"/>
+    <col width="3.4" customWidth="1" min="220" max="220"/>
+    <col width="3.4" customWidth="1" min="221" max="221"/>
+    <col width="3.4" customWidth="1" min="222" max="222"/>
+    <col width="3.4" customWidth="1" min="223" max="223"/>
+    <col width="3.4" customWidth="1" min="224" max="224"/>
+    <col width="3.4" customWidth="1" min="225" max="225"/>
+    <col width="3.4" customWidth="1" min="226" max="226"/>
+    <col width="3.4" customWidth="1" min="227" max="227"/>
+    <col width="3.4" customWidth="1" min="228" max="228"/>
+    <col width="3.4" customWidth="1" min="229" max="229"/>
+    <col width="3.4" customWidth="1" min="230" max="230"/>
+    <col width="3.4" customWidth="1" min="231" max="231"/>
+    <col width="3.4" customWidth="1" min="232" max="232"/>
+    <col width="3.4" customWidth="1" min="233" max="233"/>
+    <col width="3.4" customWidth="1" min="234" max="234"/>
+    <col width="3.4" customWidth="1" min="235" max="235"/>
+    <col width="3.4" customWidth="1" min="236" max="236"/>
+    <col width="3.4" customWidth="1" min="237" max="237"/>
+    <col width="3.4" customWidth="1" min="238" max="238"/>
+    <col width="3.4" customWidth="1" min="239" max="239"/>
+    <col width="3.4" customWidth="1" min="240" max="240"/>
+    <col width="3.4" customWidth="1" min="241" max="241"/>
+    <col width="3.4" customWidth="1" min="242" max="242"/>
+    <col width="3.4" customWidth="1" min="243" max="243"/>
+    <col width="3.4" customWidth="1" min="244" max="244"/>
+    <col width="3.4" customWidth="1" min="245" max="245"/>
+    <col width="3.4" customWidth="1" min="246" max="246"/>
+    <col width="3.4" customWidth="1" min="247" max="247"/>
+    <col width="3.4" customWidth="1" min="248" max="248"/>
+    <col width="3.4" customWidth="1" min="249" max="249"/>
+    <col width="3.4" customWidth="1" min="250" max="250"/>
+    <col width="3.4" customWidth="1" min="251" max="251"/>
+    <col width="3.4" customWidth="1" min="252" max="252"/>
+    <col width="3.4" customWidth="1" min="253" max="253"/>
+    <col width="3.4" customWidth="1" min="254" max="254"/>
+    <col width="3.4" customWidth="1" min="255" max="255"/>
+    <col width="3.4" customWidth="1" min="256" max="256"/>
+    <col width="3.4" customWidth="1" min="257" max="257"/>
+    <col width="3.4" customWidth="1" min="258" max="258"/>
+    <col width="3.4" customWidth="1" min="259" max="259"/>
+    <col width="3.4" customWidth="1" min="260" max="260"/>
+    <col width="3.4" customWidth="1" min="261" max="261"/>
+    <col width="3.4" customWidth="1" min="262" max="262"/>
+    <col width="3.4" customWidth="1" min="263" max="263"/>
+    <col width="3.4" customWidth="1" min="264" max="264"/>
+    <col width="3.4" customWidth="1" min="265" max="265"/>
+    <col width="3.4" customWidth="1" min="266" max="266"/>
+    <col width="3.4" customWidth="1" min="267" max="267"/>
+    <col width="3.4" customWidth="1" min="268" max="268"/>
+    <col width="3.4" customWidth="1" min="269" max="269"/>
+    <col width="3.4" customWidth="1" min="270" max="270"/>
+    <col width="3.4" customWidth="1" min="271" max="271"/>
+    <col width="3.4" customWidth="1" min="272" max="272"/>
+    <col width="3.4" customWidth="1" min="273" max="273"/>
+    <col width="3.4" customWidth="1" min="274" max="274"/>
+    <col width="3.4" customWidth="1" min="275" max="275"/>
+    <col width="3.4" customWidth="1" min="276" max="276"/>
+    <col width="3.4" customWidth="1" min="277" max="277"/>
+    <col width="3.4" customWidth="1" min="278" max="278"/>
+    <col width="3.4" customWidth="1" min="279" max="279"/>
+    <col width="3.4" customWidth="1" min="280" max="280"/>
+    <col width="3.4" customWidth="1" min="281" max="281"/>
+    <col width="3.4" customWidth="1" min="282" max="282"/>
+    <col width="3.4" customWidth="1" min="283" max="283"/>
+    <col width="3.4" customWidth="1" min="284" max="284"/>
+    <col width="3.4" customWidth="1" min="285" max="285"/>
+    <col width="3.4" customWidth="1" min="286" max="286"/>
+    <col width="3.4" customWidth="1" min="287" max="287"/>
+    <col width="3.4" customWidth="1" min="288" max="288"/>
+    <col width="3.4" customWidth="1" min="289" max="289"/>
+    <col width="3.4" customWidth="1" min="290" max="290"/>
+    <col width="3.4" customWidth="1" min="291" max="291"/>
+    <col width="3.4" customWidth="1" min="292" max="292"/>
+    <col width="3.4" customWidth="1" min="293" max="293"/>
+    <col width="3.4" customWidth="1" min="294" max="294"/>
+    <col width="3.4" customWidth="1" min="295" max="295"/>
+    <col width="3.4" customWidth="1" min="296" max="296"/>
+    <col width="3.4" customWidth="1" min="297" max="297"/>
+    <col width="3.4" customWidth="1" min="298" max="298"/>
+    <col width="3.4" customWidth="1" min="299" max="299"/>
+    <col width="3.4" customWidth="1" min="300" max="300"/>
+    <col width="3.4" customWidth="1" min="301" max="301"/>
+    <col width="3.4" customWidth="1" min="302" max="302"/>
+    <col width="3.4" customWidth="1" min="303" max="303"/>
+    <col width="3.4" customWidth="1" min="304" max="304"/>
+    <col width="3.4" customWidth="1" min="305" max="305"/>
+    <col width="3.4" customWidth="1" min="306" max="306"/>
+    <col width="3.4" customWidth="1" min="307" max="307"/>
+    <col width="3.4" customWidth="1" min="308" max="308"/>
+    <col width="3.4" customWidth="1" min="309" max="309"/>
+    <col width="3.4" customWidth="1" min="310" max="310"/>
+    <col width="3.4" customWidth="1" min="311" max="311"/>
+    <col width="3.4" customWidth="1" min="312" max="312"/>
+    <col width="3.4" customWidth="1" min="313" max="313"/>
+    <col width="3.4" customWidth="1" min="314" max="314"/>
+    <col width="3.4" customWidth="1" min="315" max="315"/>
+    <col width="3.4" customWidth="1" min="316" max="316"/>
+    <col width="3.4" customWidth="1" min="317" max="317"/>
+    <col width="3.4" customWidth="1" min="318" max="318"/>
+    <col width="3.4" customWidth="1" min="319" max="319"/>
+    <col width="3.4" customWidth="1" min="320" max="320"/>
+    <col width="3.4" customWidth="1" min="321" max="321"/>
+    <col width="3.4" customWidth="1" min="322" max="322"/>
+    <col width="3.4" customWidth="1" min="323" max="323"/>
+    <col width="3.4" customWidth="1" min="324" max="324"/>
+    <col width="3.4" customWidth="1" min="325" max="325"/>
+    <col width="3.4" customWidth="1" min="326" max="326"/>
+    <col width="3.4" customWidth="1" min="327" max="327"/>
+    <col width="3.4" customWidth="1" min="328" max="328"/>
+    <col width="3.4" customWidth="1" min="329" max="329"/>
+    <col width="3.4" customWidth="1" min="330" max="330"/>
+    <col width="3.4" customWidth="1" min="331" max="331"/>
+    <col width="3.4" customWidth="1" min="332" max="332"/>
+    <col width="3.4" customWidth="1" min="333" max="333"/>
+    <col width="3.4" customWidth="1" min="334" max="334"/>
+    <col width="3.4" customWidth="1" min="335" max="335"/>
+    <col width="3.4" customWidth="1" min="336" max="336"/>
+    <col width="3.4" customWidth="1" min="337" max="337"/>
+    <col width="3.4" customWidth="1" min="338" max="338"/>
+    <col width="3.4" customWidth="1" min="339" max="339"/>
+    <col width="3.4" customWidth="1" min="340" max="340"/>
+    <col width="3.4" customWidth="1" min="341" max="341"/>
+    <col width="3.4" customWidth="1" min="342" max="342"/>
+    <col width="3.4" customWidth="1" min="343" max="343"/>
+    <col width="3.4" customWidth="1" min="344" max="344"/>
+    <col width="3.4" customWidth="1" min="345" max="345"/>
+    <col width="3.4" customWidth="1" min="346" max="346"/>
+    <col width="3.4" customWidth="1" min="347" max="347"/>
+    <col width="3.4" customWidth="1" min="348" max="348"/>
+    <col width="3.4" customWidth="1" min="349" max="349"/>
+    <col width="3.4" customWidth="1" min="350" max="350"/>
+    <col width="3.4" customWidth="1" min="351" max="351"/>
+    <col width="3.4" customWidth="1" min="352" max="352"/>
+    <col width="3.4" customWidth="1" min="353" max="353"/>
+    <col width="3.4" customWidth="1" min="354" max="354"/>
+    <col width="3.4" customWidth="1" min="355" max="355"/>
+    <col width="3.4" customWidth="1" min="356" max="356"/>
+    <col width="3.4" customWidth="1" min="357" max="357"/>
+    <col width="3.4" customWidth="1" min="358" max="358"/>
+    <col width="3.4" customWidth="1" min="359" max="359"/>
+    <col width="3.4" customWidth="1" min="360" max="360"/>
+    <col width="3.4" customWidth="1" min="361" max="361"/>
+    <col width="3.4" customWidth="1" min="362" max="362"/>
+    <col width="3.4" customWidth="1" min="363" max="363"/>
+    <col width="3.4" customWidth="1" min="364" max="364"/>
+    <col width="3.4" customWidth="1" min="365" max="365"/>
+    <col width="3.4" customWidth="1" min="366" max="366"/>
+    <col width="3.4" customWidth="1" min="367" max="367"/>
+    <col width="3.4" customWidth="1" min="368" max="368"/>
+    <col width="3.4" customWidth="1" min="369" max="369"/>
+    <col width="3.4" customWidth="1" min="370" max="370"/>
+    <col width="3.4" customWidth="1" min="371" max="371"/>
+    <col width="3.4" customWidth="1" min="372" max="372"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/スケジュール_365日.xlsx
+++ b/スケジュール_365日.xlsx
@@ -556,9 +556,9 @@
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="5" customWidth="1" min="7" max="7"/>
     <col width="3.4" customWidth="1" min="8" max="8"/>
     <col width="3.4" customWidth="1" min="9" max="9"/>
